--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="194">
   <si>
     <t xml:space="preserve">PETUNJUK PENGISIAN DATA — Website Kelurahan Lahendong</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve">1. Jangan mengganti nama tab maupun baris judul (baris pertama) di setiap tab.</t>
   </si>
   <si>
@@ -41,40 +44,46 @@
     <t xml:space="preserve">   Mengosongkan id adalah cara aman menyembunyikan data sementara tanpa menghapusnya.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Tulis angka tanpa pemisah ribuan: 3241, bukan 3.241. Desimal boleh memakai koma: 7,85.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Tulis nomor telepon dengan tanda hubung (0812-3456-7801) agar angka 0 di depan tidak hilang.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Kolom foto: nama file di folder img/ situs (mis. danau-linow.webp) atau URL gambar lengkap berawalan https://.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Dibiarkan kosong = situs memakai gambar pengganti.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Kolom maps_link: tautan Google Maps lengkap berawalan https://.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Id harus unik dalam satu tab. Id wisata menjadi alamat halaman detail (wisata-detail.html?id=W1),</t>
+    <t xml:space="preserve">3. Satu orang cukup ditulis sekali, di tab aparat. Isi kolom nomor bila nomornya boleh tampil di halaman Kontak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Tab kontak hanya untuk narahubung yang bukan aparat (kantor, pos kamling, puskesmas, dsb.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Nama aparat yang belum diketahui: kosongkan selnya (situs menampilkan "Nama belum tersedia").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Tulis angka tanpa pemisah ribuan: 3241, bukan 3.241. Desimal boleh memakai koma: 7,85.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Tulis nomor telepon dengan tanda hubung (0812-3456-7801) agar angka 0 di depan tidak hilang.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Kolom foto: nama file di folder img/ situs (mis. danau-linow.webp) atau URL gambar lengkap berawalan https://.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Dibiarkan kosong = situs memakai gambar pengganti (aparat: monogram inisial).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Kolom maps_link: tautan Google Maps lengkap berawalan https://.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Id harus unik dalam satu tab. Id wisata menjadi alamat halaman detail (wisata-detail.html?id=W1),</t>
   </si>
   <si>
     <t xml:space="preserve">   jadi jangan diubah setelah tautannya dibagikan.</t>
   </si>
   <si>
-    <t xml:space="preserve">8. Tab aparat diurutkan menurut kolom urutan (1 tampil paling awal).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Satu kolom, satu jenis isi: kolom angka jangan diisi teks seperti "-"; kosongkan saja.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Perubahan langsung tampil saat halaman situs dimuat ulang.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Sheet ini dapat dibaca publik — jangan simpan data pribadi (NIK, alamat rumah) di tab mana pun.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab ini hanya catatan dan tidak perlu dipublikasikan.</t>
+    <t xml:space="preserve">10. Tab aparat diurutkan menurut kolom urutan (1 tampil paling awal; urutan 1 tampil di beranda sebagai pimpinan).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Satu kolom, satu jenis isi: kolom angka jangan diisi teks seperti "-"; kosongkan saja.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. Perubahan langsung tampil saat halaman situs dimuat ulang.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Sheet ini dapat dibaca publik — jangan simpan data pribadi (NIK, alamat rumah) di tab mana pun.</t>
   </si>
   <si>
     <t xml:space="preserve">kunci</t>
@@ -434,6 +443,9 @@
     <t xml:space="preserve">urutan</t>
   </si>
   <si>
+    <t xml:space="preserve">nomor</t>
+  </si>
+  <si>
     <t xml:space="preserve">A1</t>
   </si>
   <si>
@@ -443,6 +455,9 @@
     <t xml:space="preserve">Lurah Lahendong</t>
   </si>
   <si>
+    <t xml:space="preserve">0431-123456</t>
+  </si>
+  <si>
     <t xml:space="preserve">A2</t>
   </si>
   <si>
@@ -452,6 +467,9 @@
     <t xml:space="preserve">Sekretaris Lurah</t>
   </si>
   <si>
+    <t xml:space="preserve">0812-1111-2222</t>
+  </si>
+  <si>
     <t xml:space="preserve">A3</t>
   </si>
   <si>
@@ -569,34 +587,19 @@
     <t xml:space="preserve">peran</t>
   </si>
   <si>
-    <t xml:space="preserve">nomor</t>
-  </si>
-  <si>
     <t xml:space="preserve">K1</t>
   </si>
   <si>
-    <t xml:space="preserve">0431-123456</t>
+    <t xml:space="preserve">Kantor Kelurahan Lahendong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layanan Administrasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0431-654321</t>
   </si>
   <si>
     <t xml:space="preserve">K2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0812-1111-2222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kantor Kelurahan Lahendong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layanan Administrasi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0431-654321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K4</t>
   </si>
   <si>
     <t xml:space="preserve">Pos Kamling Terpadu</t>
@@ -691,16 +694,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -887,90 +886,105 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="122.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="132.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="0" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
+      <c r="A4" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
+      <c r="A5" s="0" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
+      <c r="A6" s="0" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
+      <c r="A7" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
+      <c r="A8" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
+      <c r="A9" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
+      <c r="A10" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
+      <c r="A11" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
+      <c r="A12" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
+      <c r="A13" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
+      <c r="A14" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
+      <c r="A15" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
+      <c r="A16" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
+      <c r="A18" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -992,63 +1006,63 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="n">
+      <c r="A2" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <v>3241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="1" t="n">
+      <c r="A3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="0" t="n">
         <v>912</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="n">
+      <c r="A4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="0" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="1" t="n">
+      <c r="A5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="0" t="n">
         <v>7.85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1" t="n">
+      <c r="A6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <v>1628</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="1" t="n">
+      <c r="A7" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="0" t="n">
         <v>1613</v>
       </c>
     </row>
@@ -1071,215 +1085,215 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="13.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="1" t="n">
+      <c r="A2" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>118</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="0" t="n">
         <v>412</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="0" t="n">
         <v>207</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="0" t="n">
         <v>205</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="A3" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="0" t="n">
         <v>126</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="0" t="n">
         <v>441</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="0" t="n">
         <v>223</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="0" t="n">
         <v>218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="A4" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>104</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="0" t="n">
         <v>365</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="0" t="n">
         <v>180</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="0" t="n">
         <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="A5" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>97</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="0" t="n">
         <v>171</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="0" t="n">
         <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="A6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <v>132</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="0" t="n">
         <v>456</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="0" t="n">
         <v>228</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="0" t="n">
         <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="A7" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="0" t="n">
         <v>89</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="0" t="n">
         <v>312</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="0" t="n">
         <v>158</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="0" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="A8" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="0" t="n">
         <v>121</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="0" t="n">
         <v>428</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="0" t="n">
         <v>214</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="0" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="A9" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="0" t="n">
         <v>125</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="0" t="n">
         <v>489</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="0" t="n">
         <v>247</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="0" t="n">
         <v>242</v>
       </c>
     </row>
@@ -1302,188 +1316,188 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="51.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="51.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="51.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="51.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="51.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="51.07"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C2" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="D2" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="E2" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="F2" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="G2" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="H2" s="0" t="s">
         <v>71</v>
       </c>
+      <c r="I2" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="C3" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="F3" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="G3" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="H3" s="0" t="s">
         <v>82</v>
       </c>
+      <c r="I3" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="C4" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="D4" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="E4" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="F4" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="G4" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="H4" s="0" t="s">
         <v>93</v>
       </c>
+      <c r="I4" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="C5" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="D5" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="F5" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="G5" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="H5" s="0" t="s">
         <v>104</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1505,130 +1519,128 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="28.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>54</v>
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B2" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>127</v>
+      <c r="F5" s="0" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>132</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1647,99 +1659,108 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="28.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>54</v>
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="1" t="n">
+      <c r="A2" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F2" s="0" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="A3" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="F3" s="0" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="A4" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="A5" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="A6" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="0" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1762,130 +1783,130 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="51.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="51.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="13.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>154</v>
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>160</v>
+      <c r="A2" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="A3" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="F4" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>160</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>160</v>
+      <c r="A5" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>160</v>
+      <c r="A6" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -1904,82 +1925,53 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="28.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>180</v>
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>182</v>
+      <c r="A2" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="C3" s="0" t="s">
         <v>192</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="301">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">sumber_data</t>
   </si>
   <si>
-    <t xml:space="preserve">HUMAS</t>
+    <t xml:space="preserve">Kelurahan Lahendong</t>
   </si>
   <si>
     <t xml:space="preserve">Sumber data kependudukan. Halaman Penduduk.</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2235</t>
   </si>
   <si>
-    <t xml:space="preserve">Sumber: HUMAS 2026. Beranda dan Penduduk.</t>
+    <t xml:space="preserve">Sumber: Kelurahan Lahendong, 2026. Beranda dan Penduduk.</t>
   </si>
   <si>
     <t xml:space="preserve">laki</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">116</t>
   </si>
   <si>
-    <t xml:space="preserve">326</t>
+    <t xml:space="preserve">328</t>
   </si>
   <si>
     <t xml:space="preserve">172</t>
@@ -537,6 +537,9 @@
   </si>
   <si>
     <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222</t>
   </si>
   <si>
     <t xml:space="preserve">109</t>
@@ -1598,119 +1601,119 @@
         <v>112</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -2226,46 +2229,46 @@
         <v>167</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>151</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>131</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2300,67 +2303,67 @@
         <v>113</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F4" s="3"/>
     </row>
@@ -2396,64 +2399,64 @@
         <v>113</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>151</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2495,163 +2498,163 @@
         <v>113</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -2683,54 +2686,54 @@
         <v>112</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -2766,7 +2769,7 @@
         <v>113</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>17</v>

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -15,9 +15,8 @@
     <sheet name="aparat" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="kontak" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="wisata" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="potensi" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="umkm" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="layanan" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="umkm" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="layanan" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="291">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -49,7 +48,7 @@
     <t xml:space="preserve">profil</t>
   </si>
   <si>
-    <t xml:space="preserve">Profil, Legenda, Kontak, serta header &amp; footer semua halaman</t>
+    <t xml:space="preserve">Profil, Legenda, Kontak, Layanan, serta header &amp; footer semua halaman</t>
   </si>
   <si>
     <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; luas, ketinggian, suhu; batas wilayah; sejarah; legenda</t>
@@ -67,7 +66,7 @@
     <t xml:space="preserve">lingkungan</t>
   </si>
   <si>
-    <t xml:space="preserve">Penduduk (tabel &amp; grafik), Pemerintahan (kepala lingkungan)</t>
+    <t xml:space="preserve">Penduduk (tabel &amp; grafik), Pemerintahan (kartu lingkungan)</t>
   </si>
   <si>
     <t xml:space="preserve">Satu baris per lingkungan: KK, jiwa, laki-laki, perempuan, lansia, rumah, nama kepala lingkungan</t>
@@ -76,10 +75,10 @@
     <t xml:space="preserve">aparat</t>
   </si>
   <si>
-    <t xml:space="preserve">Pemerintahan (bagan &amp; profil), Beranda (pimpinan), Kontak (bila nomor diisi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satu baris per aparat. Kolom atasan = id aparat di atasnya; kosong = puncak bagan</t>
+    <t xml:space="preserve">Pemerintahan (struktur), Beranda (pimpinan), Kontak (bila nomor diisi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satu baris per aparat. Kolom atasan = id aparat di atasnya; kosong = pimpinan (puncak struktur)</t>
   </si>
   <si>
     <t xml:space="preserve">kontak</t>
@@ -100,19 +99,10 @@
     <t xml:space="preserve">Satu baris per destinasi</t>
   </si>
   <si>
-    <t xml:space="preserve">potensi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potensi, Beranda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satu baris per potensi</t>
-  </si>
-  <si>
     <t xml:space="preserve">umkm</t>
   </si>
   <si>
-    <t xml:space="preserve">Potensi (bagian UMKM), Galeri</t>
+    <t xml:space="preserve">UMKM, Galeri</t>
   </si>
   <si>
     <t xml:space="preserve">Satu baris per usaha</t>
@@ -121,10 +111,10 @@
     <t xml:space="preserve">layanan</t>
   </si>
   <si>
-    <t xml:space="preserve">Layanan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satu baris per jenis surat</t>
+    <t xml:space="preserve">Layanan, Beranda (daftar surat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satu baris per jenis surat. syarat &amp; alur: satu butir per baris dalam sel. kategori (opsional) mengelompokkan surat; catatan (opsional) tampil sebagai pemberitahuan</t>
   </si>
   <si>
     <t xml:space="preserve">ATURAN PENGISIAN</t>
@@ -133,34 +123,37 @@
     <t xml:space="preserve">1. Jangan mengganti nama tab maupun baris judul (baris pertama) di setiap tab.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Satu baris = satu data. Baris yang kolom pertamanya (id / kunci) kosong tidak ditampilkan — cara aman menyembunyikan data tanpa menghapusnya.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Sel yang kosong membuat bagian itu disembunyikan di situs. Situs tidak pernah mengisi data karangan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Id harus unik dalam satu tab dan jangan diubah: id wisata menjadi alamat halaman detail (wisata-detail.html?id=W1) sekaligus penentu fotonya.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Satu orang cukup ditulis sekali, di tab aparat. Isi kolom nomor bila nomornya boleh tampil di halaman Kontak.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Tulis angka tanpa pemisah ribuan: 2235, bukan 2.235. Desimal boleh memakai koma: 7,85.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Semua sel diformat Teks biasa agar Google tidak mengubah isian (mis. membuang angka 0 di depan nomor telepon). Jangan ubah formatnya.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Beberapa paragraf atau butir dalam satu sel: pisahkan dengan baris baru (Ctrl+Enter atau Alt+Enter; di Mac Cmd+Enter).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Kolom maps_link: tautan Google Maps lengkap berawalan https://.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Perubahan langsung tampil saat halaman situs dimuat ulang.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Spreadsheet ini dapat dibaca publik — jangan simpan data pribadi (NIK, alamat rumah, nomor pribadi) di tab mana pun.</t>
+    <t xml:space="preserve">2. Satu baris = satu data. Menambah atau menghapus baris (surat, wisata, UMKM, aparat, lingkungan) langsung menambah atau mengurangi isi situs; susunan tampilan menyesuaikan sendiri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Baris yang kolom pertamanya (id / kunci) kosong tidak ditampilkan — cara aman menyembunyikan data tanpa menghapusnya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Sel yang kosong membuat bagian itu disembunyikan di situs. Situs tidak pernah mengisi data karangan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Id harus unik dalam satu tab dan jangan diubah: id wisata menjadi alamat halaman detail (wisata-detail.html?id=W1) sekaligus penentu fotonya; id surat menjadi tautan langsung (layanan.html#surat-S2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Satu orang cukup ditulis sekali, di tab aparat. Isi kolom nomor bila nomornya boleh tampil di halaman Kontak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Tulis angka tanpa pemisah ribuan: 2235, bukan 2.235. Desimal boleh memakai koma: 7,85.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Semua sel diformat Teks biasa agar Google tidak mengubah isian (mis. membuang angka 0 di depan nomor telepon). Jangan ubah formatnya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Beberapa paragraf atau butir dalam satu sel: pisahkan dengan baris baru (Ctrl+Enter atau Alt+Enter; di Mac Cmd+Enter). Di tab layanan, satu syarat atau satu langkah alur per baris.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Kolom maps_link: tautan Google Maps lengkap berawalan https://.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Perubahan langsung tampil saat halaman situs dimuat ulang.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. Spreadsheet ini dapat dibaca publik — jangan simpan data pribadi (NIK, alamat rumah, nomor pribadi) di tab mana pun.</t>
   </si>
   <si>
     <t xml:space="preserve">TIDAK DIATUR DARI SPREADSHEET</t>
@@ -184,7 +177,7 @@
     <t xml:space="preserve">• Tab profil: jam_layanan, luas_wilayah, ketinggian, suhu, batas_utara/selatan/timur/barat, sejarah, legenda.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Tab layanan: syarat, alur, waktu, dan biaya setiap surat perlu dicocokkan dengan ketentuan kantor kelurahan.</t>
+    <t xml:space="preserve">• Tab layanan: syarat, alur, waktu, biaya, dan catatan setiap surat perlu dicocokkan dengan ketentuan kantor kelurahan.</t>
   </si>
   <si>
     <t xml:space="preserve">• Masih kosong: telepon_kantor, email, nama kepala lingkungan, nomor aparat, UMKM.</t>
@@ -827,45 +820,6 @@
     <t xml:space="preserve">https://maps.google.com/?q=Toulangkow+Hills+Tomohon</t>
   </si>
   <si>
-    <t xml:space="preserve">judul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisata Alam Hutan Pinus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salah satu potensi utama Lahendong adalah wisata alam, khususnya kawasan Hutan Pinus Lahendong. Kawasan ini memiliki hutan pinus yang cukup luas, udara pegunungan yang sejuk, serta pemandangan alam yang memberikan suasana tenang dan nyaman. Kondisi tersebut mendukung pengembangan kegiatan wisata alam, rekreasi, relaksasi, dan kegiatan luar ruangan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sumber Air Panas Alami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lahendong memiliki sumber air panas alami yang mengandung belerang. Keberadaan air panas menjadi salah satu daya tarik utama kawasan karena memberikan pengalaman relaksasi bagi pengunjung, dan dapat dikembangkan menjadi bagian dari wisata berbasis alam dan kesehatan. Kawasan ini telah dimanfaatkan masyarakat sebagai tempat pemandian air panas alami sejak tahun 1980-an.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panas Bumi (Geotermal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lahendong mempunyai potensi geotermal atau panas bumi. Potensi ini dapat dikembangkan bukan hanya sebagai daya tarik wisata, tetapi juga sebagai sarana edukasi bagi masyarakat dan wisatawan mengenai panas bumi, lingkungan, serta energi terbarukan, sehingga wisata di Lahendong memiliki nilai tambah berupa pengetahuan tentang kondisi alam dan sumber daya di wilayah ini.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keanekaragaman Flora dan Fauna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kawasan Hutan Pinus Lahendong memiliki vegetasi lokal serta beberapa jenis fauna, seperti burung, landak, dan babi hutan. Keanekaragaman hayati tersebut mendukung pengembangan ekowisata sekaligus menjadi sarana edukasi mengenai pentingnya menjaga kelestarian lingkungan.</t>
-  </si>
-  <si>
     <t xml:space="preserve">produk</t>
   </si>
   <si>
@@ -884,16 +838,27 @@
     <t xml:space="preserve">biaya</t>
   </si>
   <si>
+    <t xml:space="preserve">catatan</t>
+  </si>
+  <si>
     <t xml:space="preserve">S1</t>
   </si>
   <si>
     <t xml:space="preserve">Surat Keterangan Domisili</t>
   </si>
   <si>
-    <t xml:space="preserve">Fotokopi KTP, fotokopi KK, pengantar RT/lingkungan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajukan ke kantor lurah → verifikasi berkas → tanda tangan lurah → surat selesai</t>
+    <t xml:space="preserve">Kependudukan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotokopi KTP
+Fotokopi Kartu Keluarga
+Surat pengantar RT/lingkungan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
+Petugas memeriksa berkas
+Surat ditandatangani lurah
+Surat diambil pemohon</t>
   </si>
   <si>
     <t xml:space="preserve">1 hari kerja</t>
@@ -908,25 +873,41 @@
     <t xml:space="preserve">Surat Keterangan Tidak Mampu (SKTM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fotokopi KTP, KK, surat pengantar RT, keterangan penghasilan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajukan ke kantor lurah → survei singkat bila perlu → tanda tangan lurah</t>
+    <t xml:space="preserve">Sosial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotokopi KTP
+Fotokopi Kartu Keluarga
+Surat pengantar RT/lingkungan
+Keterangan penghasilan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
+Petugas memeriksa berkas dan, bila perlu, melakukan survei singkat
+Surat ditandatangani lurah</t>
   </si>
   <si>
     <t xml:space="preserve">1–2 hari kerja</t>
   </si>
   <si>
+    <t xml:space="preserve">Sebutkan keperluan SKTM (sekolah, kesehatan, atau bantuan sosial) saat mengajukan.</t>
+  </si>
+  <si>
     <t xml:space="preserve">S3</t>
   </si>
   <si>
     <t xml:space="preserve">Surat Pengantar Nikah</t>
   </si>
   <si>
-    <t xml:space="preserve">Fotokopi KTP kedua calon, KK, surat pengantar RT, pas foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajukan ke kantor lurah → verifikasi data → surat diteruskan ke KUA</t>
+    <t xml:space="preserve">Fotokopi KTP kedua calon mempelai
+Fotokopi Kartu Keluarga
+Surat pengantar RT/lingkungan
+Pas foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
+Petugas memeriksa data
+Surat diteruskan ke KUA atau Dinas Kependudukan</t>
   </si>
   <si>
     <t xml:space="preserve">S4</t>
@@ -935,10 +916,18 @@
     <t xml:space="preserve">Surat Keterangan Usaha</t>
   </si>
   <si>
-    <t xml:space="preserve">Fotokopi KTP, KK, foto lokasi usaha, pengantar RT/lingkungan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajukan ke kantor lurah → verifikasi lokasi usaha → tanda tangan lurah</t>
+    <t xml:space="preserve">Usaha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotokopi KTP
+Fotokopi Kartu Keluarga
+Foto lokasi usaha
+Surat pengantar RT/lingkungan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
+Petugas memeriksa lokasi usaha
+Surat ditandatangani lurah</t>
   </si>
   <si>
     <t xml:space="preserve">1–3 hari kerja</t>
@@ -950,10 +939,14 @@
     <t xml:space="preserve">Surat Keterangan Kelahiran</t>
   </si>
   <si>
-    <t xml:space="preserve">Fotokopi KTP orang tua, KK, surat keterangan bidan/rumah sakit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajukan ke kantor lurah → verifikasi berkas → tanda tangan lurah</t>
+    <t xml:space="preserve">Fotokopi KTP kedua orang tua
+Fotokopi Kartu Keluarga
+Surat keterangan lahir dari bidan atau rumah sakit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
+Petugas memeriksa berkas
+Surat ditandatangani lurah</t>
   </si>
 </sst>
 </file>
@@ -1007,8 +1000,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE2DC"/>
-        <bgColor rgb="FFCCFFCC"/>
+        <fgColor rgb="FFD3DDD8"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1046,7 +1039,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1059,16 +1052,8 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1105,7 +1090,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFDDE2DC"/>
+      <rgbColor rgb="FFD3DDD8"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1257,8 +1242,8 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="63.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="81.72"/>
   </cols>
   <sheetData>
@@ -1266,460 +1251,237 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
+      <c r="A3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="51.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="20.43"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1732,163 +1494,662 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="61.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="56.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="67.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="4" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="3" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="C11" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="C12" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>90</v>
-      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1906,101 +2167,601 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="61.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="56.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="65.17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>111</v>
-      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2018,258 +2779,1362 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H1" s="4" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="3" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H4" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H5" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H6" s="3" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="H7" s="3" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="3" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="G9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>178</v>
-      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2287,85 +4152,886 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="30.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="13.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="4" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F4" s="3"/>
+      <c r="E4" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2383,81 +5049,782 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="30.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
+      <c r="E4" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2475,187 +5842,1483 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="61.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="35.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="45.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="51.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="61.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="51.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="53.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="59.55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J1" s="4" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="J2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="J3" s="3" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="H4" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
-        <v>257</v>
-      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2673,68 +7336,728 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="61.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="13.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>270</v>
-      </c>
+      <c r="A1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2752,31 +8075,1166 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="41.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="67.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="C3" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -27,8 +27,1788 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Nama informasi yang dicari situs — jangan diubah.
+Contoh: jam_layanan</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Isi informasinya. Beberapa paragraf: pisahkan dengan baris baru (Ctrl+Enter).
+Contoh: Senin – Jumat, 08.00 – 15.00 WITA</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Catatan untuk admin; tidak tampil di situs.
+Contoh: CONTOH — ganti</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Nama angka yang dicari situs — jangan diubah.
+Contoh: jumlah_penduduk</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-42</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Angka tanpa titik pemisah ribuan.
+Contoh: 2235</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-350</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Catatan untuk admin; tidak tampil di situs.
+Contoh: Sumber: Kelurahan Lahendong, 2026</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Nama lingkungan. "Lingkungan 3" ditampilkan sebagai angka besar.
+Contoh: Lingkungan 3</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nama kepala lingkungan. Kosong = "Belum dicantumkan".
+Contoh: Nama lengkap</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jumlah kepala keluarga. Angka tanpa titik.
+Contoh: 124</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>24</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jumlah penduduk = laki + perempuan.
+Contoh: 345</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Penduduk laki-laki.
+Contoh: 169</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Penduduk perempuan.
+Contoh: 176</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>8</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jumlah lansia.
+Contoh: 37</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>16</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jumlah rumah.
+Contoh: 106</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Kode singkat bebas &amp; unik untuk orang ini. Dipakai di kolom atasan — jangan diubah setelah dipakai.
+Contoh: A4</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-142</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nama lengkap dengan gelar.
+Contoh: Reymon Stive Londok, S.T</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-92</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jabatan.
+Contoh: Kepala Seksi Pemerintahan</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Angka urut tampil. 1 = pimpinan (tampil di Beranda).
+Contoh: 3</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Kode (id) atasannya. Kosong = pimpinan. Atasan = Lurah → kolom tersendiri; atasan = Kasi → staf di kolom Kasi itu.
+Contoh: A1</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nomor telepon. Isi hanya bila boleh tampil di halaman Kontak.
+Contoh: 0812-3456-7890</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Nama layanan/kontak. Hapus baris untuk menghapus kontak.
+Contoh: Puskesmas Lahendong</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
+Contoh: Ya</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-101</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Keterangan singkat.
+Contoh: Layanan kesehatan</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nomor telepon. Kosong = kontak tidak ditampilkan.
+Contoh: 0431-123456</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Pilih dari daftar: darurat (polisi, damkar, ambulans) atau umum.
+Contoh: umum</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Kode singkat unik. Menjadi alamat halaman detail (wisata-detail.html?id=W4) dan penentu foto — jangan diubah.
+Contoh: W4</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-59</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>140</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nama destinasi.
+Contoh: Danau Linow</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>35</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
+Contoh: Ya</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>110</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Satu kalimat untuk kartu.
+Contoh: Danau vulkanik dengan warna air yang berubah.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>80</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Uraian lengkap. Satu paragraf per baris (Ctrl+Enter).
+Contoh: (paragraf)</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>-267</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>80</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jam buka. Baris pertama tampil di kartu.
+Contoh: Setiap hari, 08.00 – 18.00 WITA</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>80</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Harga tiket. Baris pertama tampil di kartu.
+Contoh: Rp10.000 per orang</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>80</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Dipisah koma.
+Contoh: Parkir, toilet, warung</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>35</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Saran waktu berkunjung, satu per baris.
+Contoh: Pagi hari</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>65</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Rute, satu langkah per baris.
+Contoh: Dari pusat Kota Tomohon …</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>80</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Pengelola, satu per baris.
+Contoh: Pemerintah Kota Tomohon</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>-284</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>65</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tautan Google Maps lengkap, diawali https://
+Contoh: https://maps.google.com/?q=Danau+Linow</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>12</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>13</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>95</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Nama usaha. Untuk menghapus usaha: hapus barisnya.
+Contoh: Kue Lapis Bu Ani</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
+Contoh: Ya</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Produk utama.
+Contoh: Kue lapis legit, kue kering</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nomor telepon/WA usaha — hanya bila pemilik setuju ditampilkan.
+Contoh: 0812-3456-7890</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Lokasi usaha, pilih dari daftar.
+Contoh: Lingkungan 2</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Nama surat. Untuk menghapus surat: hapus barisnya.
+Contoh: Surat Keterangan Tidak Mampu (SKTM)</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
+Contoh: Ya</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>16</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>48</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Kelompok surat: pilih dari daftar atau ketik kategori baru. Kosong = Lainnya.
+Contoh: Sosial</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>-300</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>33</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Berkas yang dibawa, satu per baris (Ctrl+Enter).
+Contoh: Fotokopi KTP ↵ Fotokopi Kartu Keluarga</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>33</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Langkah pengurusan, satu per baris (Ctrl+Enter).
+Contoh: Bawa berkas ke kantor kelurahan ↵ Surat ditandatangani lurah</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>-1</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Lama proses.
+Contoh: 1 hari kerja</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>35</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Biaya.
+Contoh: Gratis</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>20</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Pemberitahuan tambahan (opsional).
+Contoh: Bawa dokumen asli saat pengambilan.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>33</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="396">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -36,6 +1816,24 @@
     <t xml:space="preserve">Setiap tab di spreadsheet ini mengisi bagian tertentu di situs. Ubah isi sel (tersimpan otomatis), lalu muat ulang halaman situs untuk melihat hasilnya.</t>
   </si>
   <si>
+    <t xml:space="preserve">CARA MENAMBAH, MENGHAPUS &amp; MENYEMBUNYIKAN DATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Menambah data: isi baris kosong pertama di bawah data terakhir. Kolom pertama (judul hijau tua) wajib diisi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Menghapus data: klik kanan nomor baris di kiri → Hapus baris. Baris kosong yang tersisa di tengah tidak masalah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Menyembunyikan sementara: ubah kolom tampil menjadi Tidak (pilih dari daftar). Data tetap tersimpan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Arti setiap kolom: arahkan kursor ke judul kolom (ada segitiga kecil di pojok) — muncul penjelasan dan contoh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Urutan di situs = urutan baris di sheet (tab aparat: kolom urutan). Pindahkan baris untuk mengubah urutan.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TAB</t>
   </si>
   <si>
@@ -123,16 +1921,16 @@
     <t xml:space="preserve">1. Jangan mengganti nama tab maupun baris judul (baris pertama) di setiap tab.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Satu baris = satu data. Menambah atau menghapus baris (surat, wisata, UMKM, aparat, lingkungan) langsung menambah atau mengurangi isi situs; susunan tampilan menyesuaikan sendiri.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Baris yang kolom pertamanya (id / kunci) kosong tidak ditampilkan — cara aman menyembunyikan data tanpa menghapusnya.</t>
+    <t xml:space="preserve">2. Satu baris = satu data. Menambah atau menghapus baris langsung menambah atau mengurangi isi situs; susunan tampilan menyesuaikan sendiri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Baris yang kolom pertamanya kosong tidak ditampilkan.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Sel yang kosong membuat bagian itu disembunyikan di situs. Situs tidak pernah mengisi data karangan.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Id harus unik dalam satu tab dan jangan diubah: id wisata menjadi alamat halaman detail (wisata-detail.html?id=W1) sekaligus penentu fotonya; id surat menjadi tautan langsung (layanan.html#surat-S2).</t>
+    <t xml:space="preserve">5. Hanya tab wisata dan aparat yang memakai kolom id (kode singkat, mis. W4 / A4); id harus unik dan jangan diubah. Tab lain dikenali dari kolom pertamanya.</t>
   </si>
   <si>
     <t xml:space="preserve">6. Satu orang cukup ditulis sekali, di tab aparat. Isi kolom nomor bila nomornya boleh tampil di halaman Kontak.</t>
@@ -144,22 +1942,457 @@
     <t xml:space="preserve">8. Semua sel diformat Teks biasa agar Google tidak mengubah isian (mis. membuang angka 0 di depan nomor telepon). Jangan ubah formatnya.</t>
   </si>
   <si>
-    <t xml:space="preserve">9. Beberapa paragraf atau butir dalam satu sel: pisahkan dengan baris baru (Ctrl+Enter atau Alt+Enter; di Mac Cmd+Enter). Di tab layanan, satu syarat atau satu langkah alur per baris.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Kolom maps_link: tautan Google Maps lengkap berawalan https://.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Perubahan langsung tampil saat halaman situs dimuat ulang.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12. Spreadsheet ini dapat dibaca publik — jangan simpan data pribadi (NIK, alamat rumah, nomor pribadi) di tab mana pun.</t>
+    <t xml:space="preserve">9. Beberapa paragraf atau butir dalam satu sel: pisahkan dengan baris baru (Ctrl+Enter atau Alt+Enter; di Mac Cmd+Enter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Perubahan langsung tampil saat halaman situs dimuat ulang.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Spreadsheet ini dapat dibaca publik — jangan simpan data pribadi (NIK, alamat rumah, nomor pribadi) di tab mana pun.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTI SETIAP KOLOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAB · KOLOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTOH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profil · kunci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Nama informasi yang dicari situs — jangan diubah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jam_layanan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profil · nilai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isi informasinya. Beberapa paragraf: pisahkan dengan baris baru (Ctrl+Enter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senin – Jumat, 08.00 – 15.00 WITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profil · keterangan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catatan untuk admin; tidak tampil di situs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTOH — ganti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistik · kunci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Nama angka yang dicari situs — jangan diubah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumlah_penduduk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistik · nilai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angka tanpa titik pemisah ribuan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistik · keterangan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sumber: Kelurahan Lahendong, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · nama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Nama lingkungan. "Lingkungan 3" ditampilkan sebagai angka besar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · kepala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nama kepala lingkungan. Kosong = "Belum dicantumkan".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nama lengkap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · jumlah_kk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumlah kepala keluarga. Angka tanpa titik.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · jumlah_jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumlah penduduk = laki + perempuan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · laki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penduduk laki-laki.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · perempuan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penduduk perempuan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · jumlah_lansia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumlah lansia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · jumlah_rumah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumlah rumah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aparat · id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Kode singkat bebas &amp; unik untuk orang ini. Dipakai di kolom atasan — jangan diubah setelah dipakai.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aparat · nama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nama lengkap dengan gelar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reymon Stive Londok, S.T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aparat · jabatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabatan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kepala Seksi Pemerintahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aparat · urutan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angka urut tampil. 1 = pimpinan (tampil di Beranda).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aparat · atasan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kode (id) atasannya. Kosong = pimpinan. Atasan = Lurah → kolom tersendiri; atasan = Kasi → staf di kolom Kasi itu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aparat · nomor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nomor telepon. Isi hanya bila boleh tampil di halaman Kontak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0812-3456-7890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kontak · nama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Nama layanan/kontak. Hapus baris untuk menghapus kontak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puskesmas Lahendong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kontak · tampil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kontak · peran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keterangan singkat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layanan kesehatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kontak · nomor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nomor telepon. Kosong = kontak tidak ditampilkan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0431-123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kontak · kategori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilih dari daftar: darurat (polisi, damkar, ambulans) atau umum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Kode singkat unik. Menjadi alamat halaman detail (wisata-detail.html?id=W4) dan penentu foto — jangan diubah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · nama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nama destinasi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danau Linow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · tampil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · ringkas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satu kalimat untuk kartu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danau vulkanik dengan warna air yang berubah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · deskripsi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uraian lengkap. Satu paragraf per baris (Ctrl+Enter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(paragraf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · jam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jam buka. Baris pertama tampil di kartu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setiap hari, 08.00 – 18.00 WITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · tiket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harga tiket. Baris pertama tampil di kartu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rp10.000 per orang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · fasilitas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dipisah koma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parkir, toilet, warung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · waktu_terbaik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saran waktu berkunjung, satu per baris.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagi hari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · cara_kesana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rute, satu langkah per baris.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dari pusat Kota Tomohon …</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · pengelola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengelola, satu per baris.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemerintah Kota Tomohon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wisata · maps_link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tautan Google Maps lengkap, diawali https://</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maps.google.com/?q=Danau+Linow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umkm · nama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Nama usaha. Untuk menghapus usaha: hapus barisnya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kue Lapis Bu Ani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umkm · tampil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umkm · produk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produk utama.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kue lapis legit, kue kering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umkm · kontak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nomor telepon/WA usaha — hanya bila pemilik setuju ditampilkan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umkm · lingkungan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lokasi usaha, pilih dari daftar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layanan · nama_surat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Nama surat. Untuk menghapus surat: hapus barisnya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surat Keterangan Tidak Mampu (SKTM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layanan · tampil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layanan · kategori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelompok surat: pilih dari daftar atau ketik kategori baru. Kosong = Lainnya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sosial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layanan · syarat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berkas yang dibawa, satu per baris (Ctrl+Enter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotokopi KTP ↵ Fotokopi Kartu Keluarga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layanan · alur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langkah pengurusan, satu per baris (Ctrl+Enter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bawa berkas ke kantor kelurahan ↵ Surat ditandatangani lurah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layanan · waktu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lama proses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 hari kerja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layanan · biaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biaya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gratis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">layanan · catatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemberitahuan tambahan (opsional).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bawa dokumen asli saat pengambilan.</t>
   </si>
   <si>
     <t xml:space="preserve">TIDAK DIATUR DARI SPREADSHEET</t>
   </si>
   <si>
-    <t xml:space="preserve">• Foto: statis di folder img/ situs, dipetakan ke id baris di assets/js/komponen.js (bagian FOTO).</t>
+    <t xml:space="preserve">• Foto: statis di folder img/ situs, dipetakan di assets/js/komponen.js (bagian FOTO).</t>
   </si>
   <si>
     <t xml:space="preserve">• Peta wilayah (gambar): file img/peta-wilayah.png — halaman Profil menampilkannya otomatis bila file ada.</t>
@@ -174,7 +2407,7 @@
     <t xml:space="preserve">Nilai yang belum ada data resminya ditandai "CONTOH" di kolom keterangan dan wajib diganti sebelum situs diumumkan:</t>
   </si>
   <si>
-    <t xml:space="preserve">• Tab profil: jam_layanan, luas_wilayah, ketinggian, suhu, batas_utara/selatan/timur/barat, sejarah, legenda.</t>
+    <t xml:space="preserve">• Tab profil: jam_layanan, luas_wilayah, ketinggian, suhu, sejarah, legenda.</t>
   </si>
   <si>
     <t xml:space="preserve">• Tab layanan: syarat, alur, waktu, biaya, dan catatan setiap surat perlu dicocokkan dengan ketentuan kantor kelurahan.</t>
@@ -213,12 +2446,6 @@
     <t xml:space="preserve">Halaman Kontak. Kosong = tidak ditampilkan.</t>
   </si>
   <si>
-    <t xml:space="preserve">jam_layanan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senin – Jumat, 08.00 – 15.00 WITA</t>
-  </si>
-  <si>
     <t xml:space="preserve">CONTOH — ganti. Header, footer, halaman Kontak dan Layanan.</t>
   </si>
   <si>
@@ -252,31 +2479,28 @@
     <t xml:space="preserve">batas_utara</t>
   </si>
   <si>
-    <t xml:space="preserve">Kelurahan Kakaskasen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTOH — ganti. Profil, tabel batas wilayah.</t>
+    <t xml:space="preserve">Kelurahan Kampung Jawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil, tabel batas wilayah.</t>
   </si>
   <si>
     <t xml:space="preserve">batas_selatan</t>
   </si>
   <si>
-    <t xml:space="preserve">Kelurahan Kumelembuai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTOH — ganti.</t>
+    <t xml:space="preserve">Kabupaten Minahasa</t>
   </si>
   <si>
     <t xml:space="preserve">batas_timur</t>
   </si>
   <si>
-    <t xml:space="preserve">Kecamatan Tondano Selatan</t>
+    <t xml:space="preserve">Kecamatan Pangolombian</t>
   </si>
   <si>
     <t xml:space="preserve">batas_barat</t>
   </si>
   <si>
-    <t xml:space="preserve">Kelurahan Walian</t>
+    <t xml:space="preserve">Kelurahan Pinaras</t>
   </si>
   <si>
     <t xml:space="preserve">sejarah</t>
@@ -319,12 +2543,6 @@
     <t xml:space="preserve">Sumber data kependudukan. Halaman Penduduk.</t>
   </si>
   <si>
-    <t xml:space="preserve">jumlah_penduduk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sumber: Kelurahan Lahendong, 2026. Beranda dan Penduduk.</t>
   </si>
   <si>
@@ -364,207 +2582,159 @@
     <t xml:space="preserve">Beranda dan Profil.</t>
   </si>
   <si>
+    <t xml:space="preserve">nama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kepala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumlah_jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumlah_lansia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumlah_rumah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">nama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kepala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumlah_jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumlah_lansia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumlah_rumah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
     <t xml:space="preserve">jabatan</t>
   </si>
   <si>
@@ -577,12 +2747,6 @@
     <t xml:space="preserve">nomor</t>
   </si>
   <si>
-    <t xml:space="preserve">A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reymon Stive Londok, S.T</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lurah</t>
   </si>
   <si>
@@ -607,10 +2771,7 @@
     <t xml:space="preserve">Marthen J. Mende, ST</t>
   </si>
   <si>
-    <t xml:space="preserve">Kepala Seksi Pemerintahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
+    <t xml:space="preserve">tampil</t>
   </si>
   <si>
     <t xml:space="preserve">peran</t>
@@ -619,9 +2780,6 @@
     <t xml:space="preserve">kategori</t>
   </si>
   <si>
-    <t xml:space="preserve">K1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Polisi</t>
   </si>
   <si>
@@ -634,25 +2792,19 @@
     <t xml:space="preserve">darurat</t>
   </si>
   <si>
-    <t xml:space="preserve">K2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pemadam Kebakaran</t>
   </si>
   <si>
     <t xml:space="preserve">Kebakaran dan penyelamatan</t>
   </si>
   <si>
-    <t xml:space="preserve">K3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ambulans</t>
   </si>
   <si>
     <t xml:space="preserve">Gawat darurat medis</t>
   </si>
   <si>
-    <t xml:space="preserve">119</t>
+    <t xml:space="preserve">2005</t>
   </si>
   <si>
     <t xml:space="preserve">ringkas</t>
@@ -683,9 +2835,6 @@
   </si>
   <si>
     <t xml:space="preserve">W1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danau Linow</t>
   </si>
   <si>
     <t xml:space="preserve">Danau vulkanik dengan warna air yang dapat berubah — hijau, biru, hingga kekuningan.</t>
@@ -791,35 +2940,6 @@
     <t xml:space="preserve">https://maps.google.com/?q=Mahwatu+Tomohon</t>
   </si>
   <si>
-    <t xml:space="preserve">W4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toulangkow Hills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puncak berpanorama Gunung Lokon dan Danau Linow, favorit untuk berkemah dan berburu matahari terbenam.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puncak Toulangkow merupakan salah satu destinasi wisata alam yang berada di Kota Tomohon, Sulawesi Utara. Tempat ini menawarkan keindahan panorama alam yang dapat dinikmati dari ketinggian, dengan udara yang sejuk dan suasana yang tenang. Dari kawasan puncak, pengunjung dapat menikmati pemandangan alam sekitar yang indah, sehingga tempat ini cocok untuk bersantai, berfoto, maupun menghabiskan waktu bersama keluarga dan teman.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setiap hari, 08.30 – 18.00 WITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rp10.000 per pengunjung
-Rp50.000 per tenda (camping)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camping ground, spot foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagi hari (08.30 – 10.00 WITA): pas untuk memotret panorama Gunung Lokon dan Danau Linow dengan cahaya pagi yang cerah.
-Sore hari (16.00 – 18.00 WITA): paling populer bagi pemburu matahari terbenam.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://maps.google.com/?q=Toulangkow+Hills+Tomohon</t>
-  </si>
-  <si>
     <t xml:space="preserve">produk</t>
   </si>
   <si>
@@ -839,9 +2959,6 @@
   </si>
   <si>
     <t xml:space="preserve">catatan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S1</t>
   </si>
   <si>
     <t xml:space="preserve">Surat Keterangan Domisili</t>
@@ -861,21 +2978,6 @@
 Surat diambil pemohon</t>
   </si>
   <si>
-    <t xml:space="preserve">1 hari kerja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gratis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surat Keterangan Tidak Mampu (SKTM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sosial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fotokopi KTP
 Fotokopi Kartu Keluarga
 Surat pengantar RT/lingkungan
@@ -893,9 +2995,6 @@
     <t xml:space="preserve">Sebutkan keperluan SKTM (sekolah, kesehatan, atau bantuan sosial) saat mengajukan.</t>
   </si>
   <si>
-    <t xml:space="preserve">S3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Surat Pengantar Nikah</t>
   </si>
   <si>
@@ -910,9 +3009,6 @@
 Surat diteruskan ke KUA atau Dinas Kependudukan</t>
   </si>
   <si>
-    <t xml:space="preserve">S4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Surat Keterangan Usaha</t>
   </si>
   <si>
@@ -931,9 +3027,6 @@
   </si>
   <si>
     <t xml:space="preserve">1–3 hari kerja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S5</t>
   </si>
   <si>
     <t xml:space="preserve">Surat Keterangan Kelahiran</t>
@@ -957,7 +3050,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -990,8 +3083,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1002,6 +3102,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD3DDD8"/>
         <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B6B63"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
   </fills>
@@ -1039,7 +3145,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1053,6 +3159,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1080,7 +3198,7 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0B6B63"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
@@ -1239,12 +3357,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="63.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="81.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="71.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="61.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1260,182 +3378,182 @@
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+    <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
@@ -1450,32 +3568,629 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -1502,153 +4217,153 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>51</v>
+      <c r="A1" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>52</v>
+        <v>203</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>53</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>206</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>210</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>213</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>217</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>219</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>220</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>73</v>
+        <v>222</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>223</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>78</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>231</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>84</v>
+        <v>232</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>86</v>
+        <v>234</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>87</v>
+        <v>235</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2159,6 +4874,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2176,91 +4892,91 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>51</v>
+      <c r="A1" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>52</v>
+        <v>203</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>53</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>237</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>91</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>92</v>
+        <v>240</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>93</v>
+        <v>241</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>94</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>97</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>244</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>245</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>100</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>101</v>
+        <v>247</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>248</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>103</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>104</v>
+        <v>250</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>251</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>106</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
+        <v>254</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2771,6 +5487,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2779,261 +5496,233 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>110</v>
+      <c r="A1" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>112</v>
+        <v>250</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>104</v>
+        <v>258</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>98</v>
+        <v>247</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>101</v>
+        <v>259</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>115</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="D2" s="2" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>126</v>
+        <v>263</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>127</v>
+        <v>264</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>129</v>
+        <v>266</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>131</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>267</v>
+      </c>
       <c r="D4" s="2" t="s">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
+        <v>269</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>138</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="D5" s="2" t="s">
-        <v>141</v>
+        <v>275</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>142</v>
+        <v>276</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>143</v>
+        <v>277</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>144</v>
+        <v>278</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>146</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>149</v>
+        <v>282</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>150</v>
+        <v>283</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>151</v>
+        <v>284</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>152</v>
+        <v>285</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>288</v>
+      </c>
       <c r="D7" s="2" t="s">
-        <v>157</v>
+        <v>289</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>158</v>
+        <v>290</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>159</v>
+        <v>291</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>160</v>
+        <v>292</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>162</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>295</v>
+      </c>
       <c r="D8" s="2" t="s">
-        <v>165</v>
+        <v>296</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>166</v>
+        <v>297</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>167</v>
+        <v>281</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>149</v>
+        <v>298</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>301</v>
+      </c>
       <c r="D9" s="2" t="s">
-        <v>172</v>
+        <v>302</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>173</v>
+        <v>303</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>174</v>
+        <v>265</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>129</v>
+        <v>304</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>176</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3045,7 +5734,6 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -3056,7 +5744,6 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
@@ -3067,7 +5754,6 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
@@ -3078,7 +5764,6 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -3089,7 +5774,6 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
@@ -3100,7 +5784,6 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
@@ -3111,7 +5794,6 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -3122,7 +5804,6 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -3133,7 +5814,6 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -3144,7 +5824,6 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -3155,7 +5834,6 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
@@ -3166,7 +5844,6 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
@@ -3177,7 +5854,6 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -3188,7 +5864,6 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -3199,7 +5874,6 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -3210,7 +5884,6 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -3221,7 +5894,6 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
@@ -3232,7 +5904,6 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
@@ -3243,7 +5914,6 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
@@ -3254,7 +5924,6 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
@@ -3265,7 +5934,6 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -3276,7 +5944,6 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -3287,7 +5954,6 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
@@ -3298,7 +5964,6 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
@@ -3309,7 +5974,6 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -3320,7 +5984,6 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -3331,7 +5994,6 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
@@ -3342,7 +6004,6 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -3353,7 +6014,6 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
@@ -3364,7 +6024,6 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
@@ -3375,7 +6034,6 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
@@ -3386,7 +6044,6 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
@@ -3397,7 +6054,6 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
@@ -3408,7 +6064,6 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
@@ -3419,7 +6074,6 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
@@ -3430,7 +6084,6 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
@@ -3441,7 +6094,6 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
@@ -3452,7 +6104,6 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
@@ -3463,7 +6114,6 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
@@ -3474,7 +6124,6 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -3485,7 +6134,6 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -3496,7 +6144,6 @@
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -3507,7 +6154,6 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -3518,7 +6164,6 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -3529,7 +6174,6 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -3540,7 +6184,6 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -3551,7 +6194,6 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -3562,7 +6204,6 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -3573,7 +6214,6 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -3584,7 +6224,6 @@
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -3595,7 +6234,6 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -3606,7 +6244,6 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -3617,7 +6254,6 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -3628,7 +6264,6 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -3639,7 +6274,6 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -3650,7 +6284,6 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
@@ -3661,7 +6294,6 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
@@ -3672,7 +6304,6 @@
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
@@ -3683,7 +6314,6 @@
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
@@ -3694,7 +6324,6 @@
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
@@ -3705,7 +6334,6 @@
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
@@ -3716,7 +6344,6 @@
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
@@ -3727,7 +6354,6 @@
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
@@ -3738,7 +6364,6 @@
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
@@ -3749,7 +6374,6 @@
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
@@ -3760,7 +6384,6 @@
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
@@ -3771,7 +6394,6 @@
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
@@ -3782,7 +6404,6 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
@@ -3793,7 +6414,6 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
@@ -3804,7 +6424,6 @@
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
@@ -3815,7 +6434,6 @@
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
@@ -3826,7 +6444,6 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
@@ -3837,7 +6454,6 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
@@ -3848,7 +6464,6 @@
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
@@ -3859,7 +6474,6 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
@@ -3870,7 +6484,6 @@
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
@@ -3881,7 +6494,6 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
@@ -3892,7 +6504,6 @@
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
@@ -3903,7 +6514,6 @@
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
@@ -3914,7 +6524,6 @@
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
@@ -3925,7 +6534,6 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
@@ -3936,7 +6544,6 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
@@ -3947,7 +6554,6 @@
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
@@ -3958,7 +6564,6 @@
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
@@ -3969,7 +6574,6 @@
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
@@ -3980,7 +6584,6 @@
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
@@ -3991,7 +6594,6 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
@@ -4002,7 +6604,6 @@
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
@@ -4013,7 +6614,6 @@
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
@@ -4024,7 +6624,6 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
@@ -4035,7 +6634,6 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
@@ -4046,7 +6644,6 @@
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
@@ -4057,7 +6654,6 @@
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
@@ -4068,7 +6664,6 @@
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
@@ -4079,7 +6674,6 @@
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
@@ -4090,7 +6684,6 @@
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
@@ -4101,7 +6694,6 @@
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2"/>
@@ -4112,7 +6704,6 @@
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2"/>
@@ -4123,7 +6714,6 @@
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2"/>
@@ -4134,7 +6724,6 @@
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4144,6 +6733,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4162,74 +6752,74 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>110</v>
+      <c r="A1" s="5" t="s">
+        <v>306</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>111</v>
+        <v>256</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>177</v>
+        <v>307</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>178</v>
+        <v>308</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>179</v>
+        <v>309</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>180</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>182</v>
+        <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>183</v>
+        <v>311</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>184</v>
+        <v>312</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>185</v>
+        <v>313</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>186</v>
+        <v>314</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>187</v>
+        <v>315</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>188</v>
+        <v>316</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>190</v>
+        <v>318</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -5041,6 +7631,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5052,78 +7643,78 @@
   <dimension ref="A1:E104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>110</v>
+      <c r="A1" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>111</v>
+        <v>319</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>193</v>
+        <v>320</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>195</v>
+        <v>322</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>197</v>
+        <v>323</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>198</v>
+        <v>324</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>199</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>200</v>
+        <v>326</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>201</v>
+        <v>115</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>327</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>149</v>
+        <v>281</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>199</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>203</v>
+        <v>328</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>204</v>
+        <v>115</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>205</v>
+        <v>329</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>206</v>
+        <v>330</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>199</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5827,6 +8418,16 @@
       <c r="E104" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B104" type="list">
+      <formula1>"Ya,Tidak"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E104" type="list">
+      <formula1>"darurat,umum"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5834,6 +8435,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5842,183 +8444,179 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="67.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="53.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="67.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="59.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="53.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="7" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="56.18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>110</v>
+      <c r="A1" s="5" t="s">
+        <v>306</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>111</v>
+        <v>256</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>207</v>
+        <v>319</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>208</v>
+        <v>331</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>209</v>
+        <v>332</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>210</v>
+        <v>333</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>211</v>
+        <v>334</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>212</v>
+        <v>335</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>213</v>
+        <v>336</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>214</v>
+        <v>337</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>215</v>
+        <v>338</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>340</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>218</v>
+        <v>115</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>219</v>
+        <v>341</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>221</v>
+        <v>343</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>222</v>
+        <v>344</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>223</v>
+        <v>345</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>224</v>
+        <v>346</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>225</v>
+        <v>347</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>226</v>
+        <v>348</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>228</v>
+        <v>351</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>229</v>
+        <v>115</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>230</v>
+        <v>352</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>231</v>
+        <v>353</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>232</v>
+        <v>354</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>233</v>
+        <v>355</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>234</v>
+        <v>356</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>235</v>
+        <v>357</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>236</v>
+        <v>358</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>237</v>
+        <v>359</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>361</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>239</v>
+        <v>362</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>240</v>
+        <v>115</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>241</v>
+        <v>363</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>242</v>
+        <v>364</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>243</v>
+        <v>365</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>244</v>
+        <v>366</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="I4" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>368</v>
+      </c>
       <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>254</v>
-      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
@@ -6032,6 +8630,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
@@ -6045,6 +8644,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -6058,6 +8658,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
@@ -6071,6 +8672,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
@@ -6084,6 +8686,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -6097,6 +8700,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
@@ -6110,6 +8714,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
@@ -6123,6 +8728,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -6136,6 +8742,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
@@ -6149,6 +8756,7 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
@@ -6162,6 +8770,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -6175,6 +8784,7 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -6188,6 +8798,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -6201,6 +8812,7 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -6214,6 +8826,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
@@ -6227,6 +8840,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
@@ -6240,6 +8854,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -6253,6 +8868,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -6266,6 +8882,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -6279,6 +8896,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -6292,6 +8910,7 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
@@ -6305,6 +8924,7 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
@@ -6318,6 +8938,7 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
@@ -6331,6 +8952,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
@@ -6344,6 +8966,7 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -6357,6 +8980,7 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -6370,6 +8994,7 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
@@ -6383,6 +9008,7 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
@@ -6396,6 +9022,7 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -6409,6 +9036,7 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -6422,6 +9050,7 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
@@ -6435,6 +9064,7 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -6448,6 +9078,7 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
@@ -6461,6 +9092,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
@@ -6474,6 +9106,7 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
@@ -6487,6 +9120,7 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
@@ -6500,6 +9134,7 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
@@ -6513,6 +9148,7 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
@@ -6526,6 +9162,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
@@ -6539,6 +9176,7 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
@@ -6552,6 +9190,7 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
@@ -6565,6 +9204,7 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
@@ -6578,6 +9218,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
@@ -6591,6 +9232,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -6604,6 +9246,7 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -6617,6 +9260,7 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -6630,6 +9274,7 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -6643,6 +9288,7 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -6656,6 +9302,7 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -6669,6 +9316,7 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -6682,6 +9330,7 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -6695,6 +9344,7 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -6708,6 +9358,7 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -6721,6 +9372,7 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -6734,6 +9386,7 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -6747,6 +9400,7 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -6760,6 +9414,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -6773,6 +9428,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -6786,6 +9442,7 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -6799,6 +9456,7 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
@@ -6812,6 +9470,7 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
@@ -6825,6 +9484,7 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
@@ -6838,6 +9498,7 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
@@ -6851,6 +9512,7 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
@@ -6864,6 +9526,7 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
@@ -6877,6 +9540,7 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
@@ -6890,6 +9554,7 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
@@ -6903,6 +9568,7 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
@@ -6916,6 +9582,7 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
@@ -6929,6 +9596,7 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
@@ -6942,6 +9610,7 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
@@ -6955,6 +9624,7 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
@@ -6968,6 +9638,7 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
@@ -6981,6 +9652,7 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
@@ -6994,6 +9666,7 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
@@ -7007,6 +9680,7 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
@@ -7020,6 +9694,7 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
@@ -7033,6 +9708,7 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
@@ -7046,6 +9722,7 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
@@ -7059,6 +9736,7 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
@@ -7072,6 +9750,7 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
@@ -7085,6 +9764,7 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
@@ -7098,6 +9778,7 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
@@ -7111,6 +9792,7 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
@@ -7124,6 +9806,7 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
@@ -7137,6 +9820,7 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
@@ -7150,6 +9834,7 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
@@ -7163,6 +9848,7 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
@@ -7176,6 +9862,7 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
@@ -7189,6 +9876,7 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
@@ -7202,6 +9890,7 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
@@ -7215,6 +9904,7 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
@@ -7228,6 +9918,7 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
@@ -7241,6 +9932,7 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
@@ -7254,6 +9946,7 @@
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
@@ -7267,6 +9960,7 @@
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
@@ -7280,6 +9974,7 @@
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
@@ -7293,6 +9988,7 @@
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
@@ -7306,21 +10002,15 @@
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
+      <c r="L104" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C104" type="list">
+      <formula1>"Ya,Tidak"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7328,6 +10018,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7343,723 +10034,733 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>110</v>
+      <c r="A1" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>111</v>
+        <v>319</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>256</v>
+        <v>370</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
+      <c r="B2" s="6"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="B19" s="6"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+      <c r="E19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="B21" s="6"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="6"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="B24" s="6"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+      <c r="B25" s="6"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="E25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+      <c r="B26" s="6"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+      <c r="B27" s="6"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
+      <c r="B28" s="6"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+      <c r="B29" s="6"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="E29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
+      <c r="B30" s="6"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+      <c r="E30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="B31" s="6"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="E31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+      <c r="B32" s="6"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="E32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="B33" s="6"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="E33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
+      <c r="B34" s="6"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="E34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
+      <c r="B35" s="6"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+      <c r="E35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+      <c r="B36" s="6"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+      <c r="E36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
+      <c r="B37" s="6"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
+      <c r="E37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
+      <c r="B38" s="6"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+      <c r="E38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
+      <c r="B39" s="6"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+      <c r="E39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
+      <c r="B40" s="6"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+      <c r="E40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
+      <c r="B41" s="6"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
+      <c r="E41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
+      <c r="B42" s="6"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="E42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
+      <c r="B43" s="6"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="E43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
+      <c r="B44" s="6"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="E44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
+      <c r="B45" s="6"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="E45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
+      <c r="B46" s="6"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
+      <c r="E46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
+      <c r="B47" s="6"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="E47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
+      <c r="B48" s="6"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
+      <c r="E48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
+      <c r="B49" s="6"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+      <c r="E49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="B50" s="6"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+      <c r="E50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
+      <c r="B51" s="6"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
+      <c r="E51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
+      <c r="B52" s="6"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
+      <c r="E52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
+      <c r="B53" s="6"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
+      <c r="E53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
+      <c r="B54" s="6"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
+      <c r="E54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
+      <c r="B55" s="6"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
+      <c r="E55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="6"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
+      <c r="E56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="6"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
+      <c r="E57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="6"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
+      <c r="E58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
+      <c r="B59" s="6"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
+      <c r="E59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
+      <c r="B60" s="6"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
+      <c r="E60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
+      <c r="B61" s="6"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
+      <c r="E61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="6"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
+      <c r="E62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
+      <c r="B63" s="6"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
+      <c r="E63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
+      <c r="B64" s="6"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
+      <c r="E64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
+      <c r="B65" s="6"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="E65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="6"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
+      <c r="E66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
+      <c r="B67" s="6"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
+      <c r="E67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="6"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
+      <c r="E68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
+      <c r="B69" s="6"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
+      <c r="E69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
+      <c r="B70" s="6"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+      <c r="E70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
+      <c r="B71" s="6"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
+      <c r="E71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="6"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
+      <c r="E72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
+      <c r="B73" s="6"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
+      <c r="E73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
+      <c r="B74" s="6"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
+      <c r="E74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
+      <c r="B75" s="6"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
+      <c r="E75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
+      <c r="B76" s="6"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
+      <c r="E76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
+      <c r="B77" s="6"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
+      <c r="E77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
+      <c r="B78" s="6"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
+      <c r="E78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
+      <c r="B79" s="6"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
+      <c r="E79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
+      <c r="B80" s="6"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
+      <c r="E80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
+      <c r="B81" s="6"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
+      <c r="E81" s="6"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
+      <c r="B82" s="6"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
+      <c r="E82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
+      <c r="B83" s="6"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
+      <c r="E83" s="6"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
+      <c r="B84" s="6"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
+      <c r="E84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
+      <c r="B85" s="6"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
+      <c r="E85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
+      <c r="B86" s="6"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
+      <c r="E86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
+      <c r="B87" s="6"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
+      <c r="E87" s="6"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
+      <c r="B88" s="6"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
+      <c r="E88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
+      <c r="B89" s="6"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
+      <c r="E89" s="6"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
+      <c r="B90" s="6"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
+      <c r="E90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
+      <c r="B91" s="6"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="E91" s="6"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
+      <c r="B92" s="6"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="E92" s="6"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
+      <c r="B93" s="6"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
+      <c r="E93" s="6"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
+      <c r="B94" s="6"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
+      <c r="E94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
+      <c r="B95" s="6"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="E95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
+      <c r="B96" s="6"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
+      <c r="E96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
+      <c r="B97" s="6"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
+      <c r="E97" s="6"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
+      <c r="B98" s="6"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
+      <c r="E98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
+      <c r="B99" s="6"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
+      <c r="E99" s="6"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
+      <c r="B100" s="6"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
+      <c r="E100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
+      <c r="B101" s="6"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
+      <c r="E101" s="6"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B101" type="list">
+      <formula1>"Ya,Tidak"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Nilai ini belum ada di daftar. Tetap dipakai bila memang kategori baru." errorStyle="warning" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E101" type="list">
+      <formula1>"Lingkungan 1,Lingkungan 2,Lingkungan 3,Lingkungan 4,Lingkungan 5,Lingkungan 6,Lingkungan 7,Lingkungan 8"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8067,6 +10768,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -8078,8 +10780,8 @@
   <dimension ref="A1:H106"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="41.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="67.41"/>
@@ -8089,150 +10791,150 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>110</v>
+      <c r="A1" s="5" t="s">
+        <v>371</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>258</v>
+        <v>372</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>259</v>
+        <v>373</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>260</v>
+        <v>374</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>261</v>
+        <v>375</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>262</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>377</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>115</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>266</v>
+        <v>379</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>267</v>
+        <v>380</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>268</v>
+        <v>186</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>270</v>
+        <v>173</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>272</v>
+        <v>177</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>273</v>
+        <v>381</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>382</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>275</v>
+        <v>383</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>276</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>277</v>
+        <v>385</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>278</v>
+        <v>115</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>279</v>
+        <v>386</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>280</v>
+        <v>387</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>268</v>
+        <v>186</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>281</v>
+        <v>388</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>282</v>
+        <v>115</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>283</v>
+        <v>389</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>284</v>
+        <v>390</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>285</v>
+        <v>391</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>286</v>
+        <v>392</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>287</v>
+        <v>393</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>288</v>
+        <v>115</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>289</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>290</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>268</v>
+        <v>186</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -9237,6 +11939,16 @@
       <c r="H106" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B106" type="list">
+      <formula1>"Ya,Tidak"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Nilai ini belum ada di daftar. Tetap dipakai bila memang kategori baru." errorStyle="warning" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C106" type="list">
+      <formula1>"Kependudukan,Sosial,Usaha"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9244,5 +11956,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -10,13 +10,13 @@
   <sheets>
     <sheet name="petunjuk" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="profil" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="statistik" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="lingkungan" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="aparat" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="kontak" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="wisata" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="umkm" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="layanan" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="lingkungan" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="aparat" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="kontak" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="wisata" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="umkm" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="layanan" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="galeri" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -41,7 +41,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">WAJIB. Nama informasi yang dicari situs — jangan diubah.
+          <t xml:space="preserve">WAJIB. Nama informasi yang dicari situs — jangan diubah. Daftar kunci ada di tab petunjuk.
 Contoh: jam_layanan</t>
         </r>
       </text>
@@ -58,8 +58,8 @@
               <xdr:to>
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>14</xdr:rowOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -140,118 +140,6 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
-  <authors>
-    <author> </author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">WAJIB. Nama angka yang dicari situs — jangan diubah.
-Contoh: jumlah_penduduk</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>-42</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Angka tanpa titik pemisah ribuan.
-Contoh: 2235</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>-350</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Catatan untuk admin; tidak tampil di situs.
-Contoh: Sumber: Kelurahan Lahendong, 2026</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -349,288 +237,6 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>24</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Jumlah penduduk = laki + perempuan.
-Contoh: 345</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Penduduk laki-laki.
-Contoh: 169</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Penduduk perempuan.
-Contoh: 176</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>8</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Jumlah lansia.
-Contoh: 37</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
-                <xdr:row>2</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Jumlah rumah.
-Contoh: 106</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>2</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
-  <authors>
-    <author> </author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">WAJIB. Kode singkat bebas &amp; unik untuk orang ini. Dipakai di kolom atasan — jangan diubah setelah dipakai.
-Contoh: A4</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>-142</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Nama lengkap dengan gelar.
-Contoh: Reymon Stive Londok, S.T</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>-92</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>14</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Jabatan.
-Contoh: Kepala Seksi Pemerintahan</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>4</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>16</xdr:rowOff>
@@ -649,8 +255,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Angka urut tampil. 1 = pimpinan (tampil di Beranda).
-Contoh: 3</t>
+          <t xml:space="preserve">Penduduk laki-laki. Jumlah jiwa = laki + perempuan, dihitung otomatis.
+Contoh: 169</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -666,8 +272,8 @@
               <xdr:to>
                 <xdr:col>5</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>14</xdr:rowOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -683,8 +289,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Kode (id) atasannya. Kosong = pimpinan. Atasan = Lurah → kolom tersendiri; atasan = Kasi → staf di kolom Kasi itu.
-Contoh: A1</t>
+          <t xml:space="preserve">Penduduk perempuan.
+Contoh: 176</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -699,8 +305,8 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>6</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>10</xdr:row>
+                <xdr:colOff>8</xdr:colOff>
+                <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
@@ -717,8 +323,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Nomor telepon. Isi hanya bila boleh tampil di halaman Kontak.
-Contoh: 0812-3456-7890</t>
+          <t xml:space="preserve">Jumlah lansia.
+Contoh: 37</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -733,9 +339,43 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>7</xdr:col>
+                <xdr:colOff>16</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jumlah rumah.
+Contoh: 106</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>8</xdr:col>
                 <xdr:colOff>47</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -747,7 +387,187 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Nama jabatan. Urutan baris = urutan tampil.
+Contoh: Kepala Seksi Pemerintahan</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-142</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nama lengkap dengan gelar. Kosong = "Nama belum tersedia".
+Contoh: Reymon Stive Londok, S.T</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Jabatan atasannya — pilih dari daftar. Kosong = pimpinan (Lurah). Atasan = Lurah → kolom tersendiri; atasan = Kasi → staf di kolom Kasi itu.
+Contoh: Lurah</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nomor telepon. Isi hanya bila boleh tampil di halaman Kontak.
+Contoh: 0812-3456-7890</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Opsional. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link). Kosong = foto bawaan situs.
+Contoh: https://drive.google.com/file/d/…/view</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -927,7 +747,7 @@
 </comments>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -941,8 +761,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">WAJIB. Kode singkat unik. Menjadi alamat halaman detail (wisata-detail.html?id=W4) dan penentu foto — jangan diubah.
-Contoh: W4</t>
+          <t xml:space="preserve">WAJIB. Nama destinasi. Hapus baris untuk menghapus destinasi.
+Contoh: Danau Linow</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -957,9 +777,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-59</xdr:colOff>
+                <xdr:colOff>32</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>140</xdr:rowOff>
+                <xdr:rowOff>95</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -975,8 +795,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Nama destinasi.
-Contoh: Danau Linow</t>
+          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
+Contoh: Ya</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -993,7 +813,7 @@
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>35</xdr:rowOff>
+                <xdr:rowOff>110</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1009,8 +829,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
-Contoh: Ya</t>
+          <t xml:space="preserve">Opsional. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link). Kosong = foto bawaan situs.
+Contoh: https://drive.google.com/file/d/…/view</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -1026,8 +846,8 @@
               <xdr:to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>110</xdr:rowOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>33</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1345,7 +1165,7 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -1427,8 +1247,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Produk utama.
-Contoh: Kue lapis legit, kue kering</t>
+          <t xml:space="preserve">Opsional. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link). Kosong = foto bawaan situs.
+Contoh: https://drive.google.com/file/d/…/view</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -1444,6 +1264,40 @@
               <xdr:to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Produk utama.
+Contoh: Kue lapis legit, kue kering</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
@@ -1453,7 +1307,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1470,13 +1324,13 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>4</xdr:col>
+                <xdr:col>5</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>5</xdr:col>
+                <xdr:col>6</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
@@ -1487,7 +1341,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1495,7 +1349,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Lokasi usaha, pilih dari daftar.
+          <t xml:space="preserve">Lokasi usaha, pilih dari daftar (diambil dari tab lingkungan).
 Contoh: Lingkungan 2</t>
         </r>
       </text>
@@ -1504,16 +1358,16 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>5</xdr:col>
+                <xdr:col>6</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>6</xdr:col>
+                <xdr:col>7</xdr:col>
                 <xdr:colOff>47</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1525,7 +1379,7 @@
 </comments>
 </file>
 
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -1807,8 +1661,154 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Judul foto, tampil di bawah foto.
+Contoh: Pengucapan Syukur 2026</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
+Contoh: Ya</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB untuk galeri. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link).
+Contoh: https://drive.google.com/file/d/…/view</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>16</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Kelompok foto: pilih dari daftar atau ketik baru. Menjadi tombol penyaring di Galeri.
+Contoh: Kegiatan</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="391">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -1831,7 +1831,31 @@
     <t xml:space="preserve">• Arti setiap kolom: arahkan kursor ke judul kolom (ada segitiga kecil di pojok) — muncul penjelasan dan contoh.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Urutan di situs = urutan baris di sheet (tab aparat: kolom urutan). Pindahkan baris untuk mengubah urutan.</t>
+    <t xml:space="preserve">• Urutan di situs = urutan baris di sheet. Pindahkan baris untuk mengubah urutan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Angka total (jumlah penduduk, KK, jiwa per lingkungan) tidak perlu ditulis — situs menghitungnya dari tab lingkungan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Setelah mengubah data, buka halaman Cek Data: https://vercoooo.github.io/web-lahendong/cek-data.html — setiap isian yang keliru ditunjukkan beserta cara memperbaikinya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOTO DARI GOOGLE DRIVE (kolom foto &amp; kunci foto_hero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Unggah foto (JPG/PNG, sisi terpanjang sekitar 1600 piksel sudah cukup) ke folder Google Drive situs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Klik kanan foto → Bagikan → Akses umum: "Siapa saja yang memiliki link" sebagai Pelihat. (Atur sekali di folder agar semua foto di dalamnya ikut.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Klik kanan foto → Bagikan → Salin link, lalu tempel di kolom foto pada baris yang sesuai.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Buka halaman Cek Data: foto yang belum dibagikan atau tautannya salah akan ditandai.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Gunakan tautan satu foto, bukan tautan folder. Foto orang hanya dengan izin yang bersangkutan.</t>
   </si>
   <si>
     <t xml:space="preserve">TAB</t>
@@ -1846,28 +1870,19 @@
     <t xml:space="preserve">profil</t>
   </si>
   <si>
-    <t xml:space="preserve">Profil, Legenda, Kontak, Layanan, serta header &amp; footer semua halaman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; luas, ketinggian, suhu; batas wilayah; sejarah; legenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statistik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beranda (angka ringkas), Penduduk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jumlah penduduk, laki-laki, perempuan, KK, lingkungan; tahun &amp; sumber data</t>
+    <t xml:space="preserve">Profil, Legenda, Kontak, Layanan, Penduduk (tahun &amp; sumber), Beranda (foto besar), header &amp; footer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; luas, ketinggian, suhu; batas wilayah; sejarah; legenda; tahun &amp; sumber data; foto hero</t>
   </si>
   <si>
     <t xml:space="preserve">lingkungan</t>
   </si>
   <si>
-    <t xml:space="preserve">Penduduk (tabel &amp; grafik), Pemerintahan (kartu lingkungan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satu baris per lingkungan: KK, jiwa, laki-laki, perempuan, lansia, rumah, nama kepala lingkungan</t>
+    <t xml:space="preserve">Penduduk (angka, grafik &amp; tabel), Beranda (angka ringkas), Pemerintahan (kartu lingkungan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satu baris per lingkungan. Semua total (penduduk, KK, jiwa) dihitung otomatis dari tab ini</t>
   </si>
   <si>
     <t xml:space="preserve">aparat</t>
@@ -1876,7 +1891,7 @@
     <t xml:space="preserve">Pemerintahan (struktur), Beranda (pimpinan), Kontak (bila nomor diisi)</t>
   </si>
   <si>
-    <t xml:space="preserve">Satu baris per aparat. Kolom atasan = id aparat di atasnya; kosong = pimpinan (puncak struktur)</t>
+    <t xml:space="preserve">Satu baris per aparat. Kolom atasan = jabatan atasannya (pilih dari daftar); kosong = pimpinan</t>
   </si>
   <si>
     <t xml:space="preserve">kontak</t>
@@ -1912,7 +1927,16 @@
     <t xml:space="preserve">Layanan, Beranda (daftar surat)</t>
   </si>
   <si>
-    <t xml:space="preserve">Satu baris per jenis surat. syarat &amp; alur: satu butir per baris dalam sel. kategori (opsional) mengelompokkan surat; catatan (opsional) tampil sebagai pemberitahuan</t>
+    <t xml:space="preserve">Satu baris per jenis surat. syarat &amp; alur: satu butir per baris dalam sel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">galeri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galeri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foto tambahan (kegiatan, alam, budaya) selain foto wisata &amp; UMKM</t>
   </si>
   <si>
     <t xml:space="preserve">ATURAN PENGISIAN</t>
@@ -1930,7 +1954,7 @@
     <t xml:space="preserve">4. Sel yang kosong membuat bagian itu disembunyikan di situs. Situs tidak pernah mengisi data karangan.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Hanya tab wisata dan aparat yang memakai kolom id (kode singkat, mis. W4 / A4); id harus unik dan jangan diubah. Tab lain dikenali dari kolom pertamanya.</t>
+    <t xml:space="preserve">5. Tidak ada kode/id yang perlu dikarang: setiap baris dikenali dari kolom pertamanya (nama, jabatan, judul). Hindari dua baris dengan nama yang sama persis.</t>
   </si>
   <si>
     <t xml:space="preserve">6. Satu orang cukup ditulis sekali, di tab aparat. Isi kolom nomor bila nomornya boleh tampil di halaman Kontak.</t>
@@ -1966,7 +1990,7 @@
     <t xml:space="preserve">profil · kunci</t>
   </si>
   <si>
-    <t xml:space="preserve">WAJIB. Nama informasi yang dicari situs — jangan diubah.</t>
+    <t xml:space="preserve">WAJIB. Nama informasi yang dicari situs — jangan diubah. Daftar kunci ada di tab petunjuk.</t>
   </si>
   <si>
     <t xml:space="preserve">jam_layanan</t>
@@ -1990,30 +2014,6 @@
     <t xml:space="preserve">CONTOH — ganti</t>
   </si>
   <si>
-    <t xml:space="preserve">statistik · kunci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAJIB. Nama angka yang dicari situs — jangan diubah.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumlah_penduduk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statistik · nilai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angka tanpa titik pemisah ribuan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statistik · keterangan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sumber: Kelurahan Lahendong, 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">lingkungan · nama</t>
   </si>
   <si>
@@ -2041,19 +2041,10 @@
     <t xml:space="preserve">124</t>
   </si>
   <si>
-    <t xml:space="preserve">lingkungan · jumlah_jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jumlah penduduk = laki + perempuan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345</t>
-  </si>
-  <si>
     <t xml:space="preserve">lingkungan · laki</t>
   </si>
   <si>
-    <t xml:space="preserve">Penduduk laki-laki.</t>
+    <t xml:space="preserve">Penduduk laki-laki. Jumlah jiwa = laki + perempuan, dihitung otomatis.</t>
   </si>
   <si>
     <t xml:space="preserve">169</t>
@@ -2086,49 +2077,31 @@
     <t xml:space="preserve">106</t>
   </si>
   <si>
-    <t xml:space="preserve">aparat · id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAJIB. Kode singkat bebas &amp; unik untuk orang ini. Dipakai di kolom atasan — jangan diubah setelah dipakai.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A4</t>
+    <t xml:space="preserve">aparat · jabatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Nama jabatan. Urutan baris = urutan tampil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kepala Seksi Pemerintahan</t>
   </si>
   <si>
     <t xml:space="preserve">aparat · nama</t>
   </si>
   <si>
-    <t xml:space="preserve">Nama lengkap dengan gelar.</t>
+    <t xml:space="preserve">Nama lengkap dengan gelar. Kosong = "Nama belum tersedia".</t>
   </si>
   <si>
     <t xml:space="preserve">Reymon Stive Londok, S.T</t>
   </si>
   <si>
-    <t xml:space="preserve">aparat · jabatan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jabatan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kepala Seksi Pemerintahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aparat · urutan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angka urut tampil. 1 = pimpinan (tampil di Beranda).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
     <t xml:space="preserve">aparat · atasan</t>
   </si>
   <si>
-    <t xml:space="preserve">Kode (id) atasannya. Kosong = pimpinan. Atasan = Lurah → kolom tersendiri; atasan = Kasi → staf di kolom Kasi itu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1</t>
+    <t xml:space="preserve">Jabatan atasannya — pilih dari daftar. Kosong = pimpinan (Lurah). Atasan = Lurah → kolom tersendiri; atasan = Kasi → staf di kolom Kasi itu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lurah</t>
   </si>
   <si>
     <t xml:space="preserve">aparat · nomor</t>
@@ -2140,6 +2113,15 @@
     <t xml:space="preserve">0812-3456-7890</t>
   </si>
   <si>
+    <t xml:space="preserve">aparat · foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opsional. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link). Kosong = foto bawaan situs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/…/view</t>
+  </si>
+  <si>
     <t xml:space="preserve">kontak · nama</t>
   </si>
   <si>
@@ -2185,19 +2167,10 @@
     <t xml:space="preserve">umum</t>
   </si>
   <si>
-    <t xml:space="preserve">wisata · id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAJIB. Kode singkat unik. Menjadi alamat halaman detail (wisata-detail.html?id=W4) dan penentu foto — jangan diubah.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W4</t>
-  </si>
-  <si>
     <t xml:space="preserve">wisata · nama</t>
   </si>
   <si>
-    <t xml:space="preserve">Nama destinasi.</t>
+    <t xml:space="preserve">WAJIB. Nama destinasi. Hapus baris untuk menghapus destinasi.</t>
   </si>
   <si>
     <t xml:space="preserve">Danau Linow</t>
@@ -2206,6 +2179,9 @@
     <t xml:space="preserve">wisata · tampil</t>
   </si>
   <si>
+    <t xml:space="preserve">wisata · foto</t>
+  </si>
+  <si>
     <t xml:space="preserve">wisata · ringkas</t>
   </si>
   <si>
@@ -2299,6 +2275,9 @@
     <t xml:space="preserve">umkm · tampil</t>
   </si>
   <si>
+    <t xml:space="preserve">umkm · foto</t>
+  </si>
+  <si>
     <t xml:space="preserve">umkm · produk</t>
   </si>
   <si>
@@ -2317,7 +2296,7 @@
     <t xml:space="preserve">umkm · lingkungan</t>
   </si>
   <si>
-    <t xml:space="preserve">Lokasi usaha, pilih dari daftar.</t>
+    <t xml:space="preserve">Lokasi usaha, pilih dari daftar (diambil dari tab lingkungan).</t>
   </si>
   <si>
     <t xml:space="preserve">Lingkungan 2</t>
@@ -2389,18 +2368,141 @@
     <t xml:space="preserve">Bawa dokumen asli saat pengambilan.</t>
   </si>
   <si>
+    <t xml:space="preserve">galeri · judul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Judul foto, tampil di bawah foto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengucapan Syukur 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">galeri · tampil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">galeri · foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB untuk galeri. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">galeri · kategori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelompok foto: pilih dari daftar atau ketik baru. Menjadi tombol penyaring di Galeri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kegiatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KUNCI DI TAB PROFIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KUNCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alamat_kantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alamat kantor kelurahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">telepon_kantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telepon kantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email kantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jam layanan kantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luas_wilayah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luas wilayah, angka saja (km²)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ketinggian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ketinggian (mdpl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suhu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suhu rata-rata (°C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">batas_utara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batas utara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">batas_selatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batas selatan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">batas_timur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batas timur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">batas_barat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batas barat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sejarah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sejarah, satu paragraf per baris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legenda Danau Linow, satu paragraf per baris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tahun_data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahun data kependudukan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sumber_data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sumber data kependudukan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foto_hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foto besar di Beranda (tautan Google Drive, opsional)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TIDAK DIATUR DARI SPREADSHEET</t>
   </si>
   <si>
-    <t xml:space="preserve">• Foto: statis di folder img/ situs, dipetakan di assets/js/komponen.js (bagian FOTO).</t>
+    <t xml:space="preserve">• Judul dan kalimat pengantar tiap halaman, serta ilustrasi bawaan: di berkas situs (HTML &amp; folder img/).</t>
   </si>
   <si>
     <t xml:space="preserve">• Peta wilayah (gambar): file img/peta-wilayah.png — halaman Profil menampilkannya otomatis bila file ada.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Judul dan kalimat pengantar tiap halaman: di berkas HTML.</t>
-  </si>
-  <si>
     <t xml:space="preserve">DATA YANG MASIH CONTOH</t>
   </si>
   <si>
@@ -2413,7 +2515,7 @@
     <t xml:space="preserve">• Tab layanan: syarat, alur, waktu, biaya, dan catatan setiap surat perlu dicocokkan dengan ketentuan kantor kelurahan.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, nama kepala lingkungan, nomor aparat, UMKM.</t>
+    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, nama kepala lingkungan, nomor aparat, UMKM, galeri.</t>
   </si>
   <si>
     <t xml:space="preserve">kunci</t>
@@ -2425,85 +2527,52 @@
     <t xml:space="preserve">keterangan</t>
   </si>
   <si>
-    <t xml:space="preserve">alamat_kantor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kelurahan Lahendong, Kecamatan Tomohon Selatan, Kota Tomohon, Sulawesi Utara</t>
   </si>
   <si>
     <t xml:space="preserve">Footer dan halaman Kontak.</t>
   </si>
   <si>
-    <t xml:space="preserve">telepon_kantor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Header, footer, dan halaman Kontak. Kosong = tidak ditampilkan.</t>
   </si>
   <si>
-    <t xml:space="preserve">email</t>
-  </si>
-  <si>
     <t xml:space="preserve">Halaman Kontak. Kosong = tidak ditampilkan.</t>
   </si>
   <si>
     <t xml:space="preserve">CONTOH — ganti. Header, footer, halaman Kontak dan Layanan.</t>
   </si>
   <si>
-    <t xml:space="preserve">luas_wilayah</t>
-  </si>
-  <si>
     <t xml:space="preserve">7,85</t>
   </si>
   <si>
     <t xml:space="preserve">CONTOH — ganti. Angka saja, satuan km². Beranda dan Profil.</t>
   </si>
   <si>
-    <t xml:space="preserve">ketinggian</t>
-  </si>
-  <si>
     <t xml:space="preserve">800–950</t>
   </si>
   <si>
     <t xml:space="preserve">CONTOH — ganti. Satuan mdpl. Profil.</t>
   </si>
   <si>
-    <t xml:space="preserve">suhu</t>
-  </si>
-  <si>
     <t xml:space="preserve">22–26</t>
   </si>
   <si>
     <t xml:space="preserve">CONTOH — ganti. Satuan °C. Profil.</t>
   </si>
   <si>
-    <t xml:space="preserve">batas_utara</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kelurahan Kampung Jawa</t>
   </si>
   <si>
     <t xml:space="preserve">Profil, tabel batas wilayah.</t>
   </si>
   <si>
-    <t xml:space="preserve">batas_selatan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kabupaten Minahasa</t>
   </si>
   <si>
-    <t xml:space="preserve">batas_timur</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kecamatan Pangolombian</t>
   </si>
   <si>
-    <t xml:space="preserve">batas_barat</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kelurahan Pinaras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sejarah</t>
   </si>
   <si>
     <t xml:space="preserve">Lahendong tumbuh dari perkampungan kecil di sekitar sumber panas bumi alami di kaki pegunungan Tomohon.
@@ -2514,9 +2583,6 @@
     <t xml:space="preserve">CONTOH — ganti. Profil. Satu baris dalam sel = satu paragraf; paragraf pertama ditampilkan lebih besar.</t>
   </si>
   <si>
-    <t xml:space="preserve">legenda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Warga percaya kawasan Danau Linow adalah tempat bersemayamnya roh penjaga alam, dan uap belerang yang terus mengepul adalah napasnya.
 Cerita turun-temurun menyebutkan bahwa warna air danau yang berubah-ubah adalah pertanda suasana hati sang penjaga. Saat air berwarna cerah, warga meyakini alam sedang tenang dan hasil panen akan melimpah.
 Secara ilmiah, perubahan warna air danau dipengaruhi kandungan mineral dan aktivitas vulkanik di dasar danau. Namun kisah rakyat ini tetap diwariskan sebagai bagian dari kekayaan budaya setempat.</t>
@@ -2525,16 +2591,10 @@
     <t xml:space="preserve">CONTOH — ganti dengan cerita yang dituturkan warga. Halaman Legenda. Satu baris dalam sel = satu paragraf.</t>
   </si>
   <si>
-    <t xml:space="preserve">tahun_data</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Tahun data kependudukan. Halaman Penduduk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sumber_data</t>
+    <t xml:space="preserve">Tahun data kependudukan (tab lingkungan). Halaman Penduduk.</t>
   </si>
   <si>
     <t xml:space="preserve">Kelurahan Lahendong</t>
@@ -2543,54 +2603,24 @@
     <t xml:space="preserve">Sumber data kependudukan. Halaman Penduduk.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sumber: Kelurahan Lahendong, 2026. Beranda dan Penduduk.</t>
+    <t xml:space="preserve">Opsional. Tautan Google Drive foto lanskap untuk gambar besar di Beranda. Kosong = ilustrasi bawaan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kepala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jumlah_kk</t>
   </si>
   <si>
     <t xml:space="preserve">laki</t>
   </si>
   <si>
-    <t xml:space="preserve">1123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penduduk laki-laki. Halaman Penduduk.</t>
-  </si>
-  <si>
     <t xml:space="preserve">perempuan</t>
   </si>
   <si>
-    <t xml:space="preserve">1112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penduduk perempuan. Halaman Penduduk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumlah_kk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kepala keluarga. Beranda dan Penduduk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumlah_lingkungan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beranda dan Profil.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kepala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jumlah_jiwa</t>
-  </si>
-  <si>
     <t xml:space="preserve">jumlah_lansia</t>
   </si>
   <si>
@@ -2603,9 +2633,6 @@
     <t xml:space="preserve">116</t>
   </si>
   <si>
-    <t xml:space="preserve">328</t>
-  </si>
-  <si>
     <t xml:space="preserve">172</t>
   </si>
   <si>
@@ -2618,9 +2645,6 @@
     <t xml:space="preserve">80</t>
   </si>
   <si>
-    <t xml:space="preserve">221</t>
-  </si>
-  <si>
     <t xml:space="preserve">114</t>
   </si>
   <si>
@@ -2639,9 +2663,6 @@
     <t xml:space="preserve">67</t>
   </si>
   <si>
-    <t xml:space="preserve">210</t>
-  </si>
-  <si>
     <t xml:space="preserve">111</t>
   </si>
   <si>
@@ -2660,9 +2681,6 @@
     <t xml:space="preserve">113</t>
   </si>
   <si>
-    <t xml:space="preserve">330</t>
-  </si>
-  <si>
     <t xml:space="preserve">157</t>
   </si>
   <si>
@@ -2681,9 +2699,6 @@
     <t xml:space="preserve">96</t>
   </si>
   <si>
-    <t xml:space="preserve">271</t>
-  </si>
-  <si>
     <t xml:space="preserve">139</t>
   </si>
   <si>
@@ -2702,9 +2717,6 @@
     <t xml:space="preserve">69</t>
   </si>
   <si>
-    <t xml:space="preserve">222</t>
-  </si>
-  <si>
     <t xml:space="preserve">109</t>
   </si>
   <si>
@@ -2720,9 +2732,6 @@
     <t xml:space="preserve">97</t>
   </si>
   <si>
-    <t xml:space="preserve">308</t>
-  </si>
-  <si>
     <t xml:space="preserve">152</t>
   </si>
   <si>
@@ -2732,42 +2741,24 @@
     <t xml:space="preserve">75</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
     <t xml:space="preserve">jabatan</t>
   </si>
   <si>
-    <t xml:space="preserve">urutan</t>
-  </si>
-  <si>
     <t xml:space="preserve">atasan</t>
   </si>
   <si>
     <t xml:space="preserve">nomor</t>
   </si>
   <si>
-    <t xml:space="preserve">Lurah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2</t>
+    <t xml:space="preserve">foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sekretaris Kelurahan</t>
   </si>
   <si>
     <t xml:space="preserve">Cicilia M. Karamoy, S.ST, M.Kes</t>
   </si>
   <si>
-    <t xml:space="preserve">Sekretaris Kelurahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marthen J. Mende, ST</t>
   </si>
   <si>
@@ -2832,9 +2823,6 @@
   </si>
   <si>
     <t xml:space="preserve">maps_link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W1</t>
   </si>
   <si>
     <t xml:space="preserve">Danau vulkanik dengan warna air yang dapat berubah — hijau, biru, hingga kekuningan.</t>
@@ -2872,9 +2860,6 @@
     <t xml:space="preserve">https://maps.google.com/?q=Danau+Linow+Tomohon</t>
   </si>
   <si>
-    <t xml:space="preserve">W2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hutan Pinus Lahendong</t>
   </si>
   <si>
@@ -2909,9 +2894,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://maps.google.com/?q=Hutan+Pinus+Lahendong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3</t>
   </si>
   <si>
     <t xml:space="preserve">Mah’Watu</t>
@@ -3040,6 +3022,9 @@
     <t xml:space="preserve">Bawa berkas ke kantor kelurahan
 Petugas memeriksa berkas
 Surat ditandatangani lurah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">judul</t>
   </si>
 </sst>
 </file>
@@ -3357,7 +3342,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
@@ -3403,495 +3388,439 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+    <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+    <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="3" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="3" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+    <row r="38" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="4" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="4" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="2" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="2" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C44" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="2" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="B45" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="C45" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>88</v>
+      <c r="A48" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>94</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>109</v>
+      <c r="A55" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>127</v>
+      <c r="A60" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>114</v>
@@ -3902,295 +3831,533 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>137</v>
+      <c r="A65" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>161</v>
+      <c r="A73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>180</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>186</v>
+      <c r="A83" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C93" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-    </row>
-    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
+      <c r="C94" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2"/>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="3" t="s">
+      <c r="B97" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+      <c r="B98" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
+      <c r="B99" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
         <v>201</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2"/>
+    </row>
+    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4209,7 +4376,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.98"/>
@@ -4218,168 +4385,184 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -4865,6 +5048,21 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4883,601 +5081,1105 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="65.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>204</v>
+        <v>266</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>238</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>76</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>241</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>242</v>
+        <v>272</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>243</v>
+        <v>276</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>245</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>246</v>
+        <v>282</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>248</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>249</v>
+        <v>288</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>251</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>252</v>
+        <v>294</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>254</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>255</v>
+        <v>300</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>304</v>
+      </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5496,1236 +6198,775 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>256</v>
+        <v>309</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>260</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>91</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>267</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>272</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>273</v>
-      </c>
+      <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>279</v>
-      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>280</v>
-      </c>
+      <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>286</v>
-      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>293</v>
-      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>294</v>
-      </c>
+      <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>299</v>
-      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>300</v>
-      </c>
+      <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>305</v>
-      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="C10" s="6"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="C12" s="6"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="C14" s="6"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="C16" s="6"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="6"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="C20" s="6"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="C21" s="6"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="C22" s="6"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="C23" s="6"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="C24" s="6"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="C25" s="6"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="C26" s="6"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="C28" s="6"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="C29" s="6"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+      <c r="C30" s="6"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
+      <c r="C31" s="6"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="C32" s="6"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="C33" s="6"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+      <c r="C34" s="6"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+      <c r="C35" s="6"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
+      <c r="C36" s="6"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="C37" s="6"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
+      <c r="C38" s="6"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
+      <c r="C39" s="6"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
+      <c r="C40" s="6"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
+      <c r="C41" s="6"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
+      <c r="C42" s="6"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="C43" s="6"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="C44" s="6"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
+      <c r="C45" s="6"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
+      <c r="C46" s="6"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
+      <c r="C47" s="6"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
+      <c r="C48" s="6"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
+      <c r="C49" s="6"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
+      <c r="C50" s="6"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="C51" s="6"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
+      <c r="C52" s="6"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
+      <c r="C53" s="6"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
+      <c r="C54" s="6"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
+      <c r="C55" s="6"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
+      <c r="C56" s="6"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
+      <c r="C57" s="6"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
+      <c r="C58" s="6"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
+      <c r="C59" s="6"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
+      <c r="C60" s="6"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
+      <c r="C61" s="6"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
+      <c r="C62" s="6"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
+      <c r="C63" s="6"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
+      <c r="C64" s="6"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="C65" s="6"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
+      <c r="C66" s="6"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
+      <c r="C67" s="6"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
+      <c r="C68" s="6"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
+      <c r="C69" s="6"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
+      <c r="C70" s="6"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
+      <c r="C71" s="6"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
+      <c r="C72" s="6"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
+      <c r="C73" s="6"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
+      <c r="C74" s="6"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
+      <c r="C75" s="6"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
+      <c r="C76" s="6"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
+      <c r="C77" s="6"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
+      <c r="C78" s="6"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
+      <c r="C79" s="6"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
+      <c r="C80" s="6"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
+      <c r="C81" s="6"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
+      <c r="C82" s="6"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
+      <c r="C83" s="6"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
+      <c r="C84" s="6"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
+      <c r="C85" s="6"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
+      <c r="C86" s="6"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
+      <c r="C87" s="6"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
+      <c r="C88" s="6"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
+      <c r="C89" s="6"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
+      <c r="C90" s="6"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
+      <c r="C91" s="6"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
+      <c r="C92" s="6"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
+      <c r="C93" s="6"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
+      <c r="C94" s="6"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
+      <c r="C95" s="6"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
+      <c r="C96" s="6"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="C97" s="6"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
+      <c r="C98" s="6"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
+      <c r="C99" s="6"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
+      <c r="C100" s="6"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
+      <c r="C101" s="6"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
+      <c r="C102" s="6"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
+      <c r="C103" s="6"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
+      <c r="C104" s="6"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C104" type="list">
+      <formula1>aparat!$A$2:$A$500</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6742,904 +6983,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="13.49"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:E104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -7651,70 +6994,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8439,7 +7782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -8447,9 +7790,8 @@
   <dimension ref="A1:L104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="67.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="53.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="7" style="0" width="67.41"/>
@@ -8458,150 +7800,144 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10006,8 +9342,861 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C104" type="list">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B104" type="list">
       <formula1>"Ya,Tidak"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="13.49"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="6"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="6"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="6"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="6"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="6"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="6"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="6"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="6"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="6"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="6"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="6"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="6"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="6"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="6"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="6"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="6"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="6"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="6"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="6"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="6"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="6"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="6"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="6"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="6"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="6"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="6"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="6"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="6"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="6"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B101" type="list">
+      <formula1>"Ya,Tidak"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F101" type="list">
+      <formula1>lingkungan!$A$2:$A$500</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -10027,756 +10216,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="13.49"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="6"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="6"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="6"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="6"/>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="6"/>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="6"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="6"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="6"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="6"/>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="6"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="6"/>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="6"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="6"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="6"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="6"/>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="6"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="6"/>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="6"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="6"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="6"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="6"/>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="6"/>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="6"/>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="6"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="6"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="6"/>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="6"/>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="6"/>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="6"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="6"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="6"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="6"/>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="6"/>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="6"/>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="6"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="6"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="6"/>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="6"/>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="6"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="6"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="6"/>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="6"/>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="6"/>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="6"/>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="6"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="6"/>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="6"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B101" type="list">
-      <formula1>"Ya,Tidak"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Nilai ini belum ada di daftar. Tetap dipakai bila memang kategori baru." errorStyle="warning" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E101" type="list">
-      <formula1>"Lingkungan 1,Lingkungan 2,Lingkungan 3,Lingkungan 4,Lingkungan 5,Lingkungan 6,Lingkungan 7,Lingkungan 8"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:H106"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -10792,149 +10231,149 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -11958,4 +11397,651 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="13.49"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="6"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="6"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="6"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="6"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="6"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="6"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="6"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="6"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="6"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="6"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="6"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="6"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="6"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="6"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="6"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="6"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="6"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="6"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="6"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="6"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="6"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="6"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="6"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="6"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="6"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="6"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="6"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="6"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="6"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="6"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="6"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="6"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="6"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="6"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="6"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="6"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="6"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="6"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="6"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="6"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="6"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="6"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="6"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B101" type="list">
+      <formula1>"Ya,Tidak"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Nilai ini belum ada di daftar. Tetap dipakai bila memang kategori baru." errorStyle="warning" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D101" type="list">
+      <formula1>"Kegiatan,Alam,Budaya"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -2560,19 +2560,19 @@
     <t xml:space="preserve">CONTOH — ganti. Satuan °C. Profil.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kelurahan Kampung Jawa</t>
+    <t xml:space="preserve">Tumatangtang 1, Kampung Jawa</t>
   </si>
   <si>
     <t xml:space="preserve">Profil, tabel batas wilayah.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kabupaten Minahasa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kecamatan Pangolombian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelurahan Pinaras</t>
+    <t xml:space="preserve">Leilem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pangolombian, Tondangow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinaras, Rambunan</t>
   </si>
   <si>
     <t xml:space="preserve">Lahendong tumbuh dari perkampungan kecil di sekitar sumber panas bumi alami di kaki pegunungan Tomohon.

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -169,7 +169,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
+                <xdr:colOff>-76</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
               </xdr:to>
@@ -187,8 +187,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Nama kepala lingkungan. Kosong = "Belum dicantumkan".
-Contoh: Nama lengkap</t>
+          <t xml:space="preserve">Nama KEPALA lingkungan di baris lingkungannya. Kosong = tampil "Belum tersedia".
+Contoh: Julius Joni Rondonuwu</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -203,9 +203,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>3</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
+                <xdr:colOff>-84</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -214,6 +214,40 @@
       </mc:AlternateContent>
     </comment>
     <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nama WAKIL kepala lingkungan di baris lingkungannya. Kosong = tampil "Belum tersedia".
+Contoh: Jetni Vinsensia Poli</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -230,13 +264,13 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>3</xdr:col>
+                <xdr:col>4</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>4</xdr:col>
+                <xdr:col>5</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>16</xdr:rowOff>
@@ -247,7 +281,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -264,13 +298,13 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>4</xdr:col>
+                <xdr:col>5</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>5</xdr:col>
+                <xdr:col>6</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
                 <xdr:row>6</xdr:row>
                 <xdr:rowOff>10</xdr:rowOff>
@@ -281,7 +315,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -298,14 +332,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>5</xdr:col>
+                <xdr:col>6</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>8</xdr:colOff>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>7</xdr:colOff>
                 <xdr:row>3</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -315,7 +349,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -332,13 +366,13 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>6</xdr:col>
+                <xdr:col>7</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>7</xdr:col>
+                <xdr:col>8</xdr:col>
                 <xdr:colOff>16</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>3</xdr:rowOff>
@@ -349,7 +383,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -366,13 +400,13 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>7</xdr:col>
+                <xdr:col>8</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>8</xdr:col>
+                <xdr:col>9</xdr:col>
                 <xdr:colOff>47</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>3</xdr:rowOff>
@@ -1808,7 +1842,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="407">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -1882,7 +1916,7 @@
     <t xml:space="preserve">Penduduk (angka, grafik &amp; tabel), Beranda (angka ringkas), Pemerintahan (kartu lingkungan)</t>
   </si>
   <si>
-    <t xml:space="preserve">Satu baris per lingkungan. Semua total (penduduk, KK, jiwa) dihitung otomatis dari tab ini</t>
+    <t xml:space="preserve">Satu baris per lingkungan: kepala &amp; wakil kepala lingkungan, KK, laki-laki, perempuan, lansia, rumah. Semua total dihitung otomatis dari tab ini</t>
   </si>
   <si>
     <t xml:space="preserve">aparat</t>
@@ -2026,10 +2060,19 @@
     <t xml:space="preserve">lingkungan · kepala</t>
   </si>
   <si>
-    <t xml:space="preserve">Nama kepala lingkungan. Kosong = "Belum dicantumkan".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nama lengkap</t>
+    <t xml:space="preserve">Nama KEPALA lingkungan di baris lingkungannya. Kosong = tampil "Belum tersedia".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julius Joni Rondonuwu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lingkungan · wakil_kepala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nama WAKIL kepala lingkungan di baris lingkungannya. Kosong = tampil "Belum tersedia".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jetni Vinsensia Poli</t>
   </si>
   <si>
     <t xml:space="preserve">lingkungan · jumlah_kk</t>
@@ -2515,7 +2558,7 @@
     <t xml:space="preserve">• Tab layanan: syarat, alur, waktu, biaya, dan catatan setiap surat perlu dicocokkan dengan ketentuan kantor kelurahan.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, nama kepala lingkungan, nomor aparat, UMKM, galeri.</t>
+    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, kepala &amp; wakil kepala Lingkungan 7, nomor aparat, UMKM, galeri.</t>
   </si>
   <si>
     <t xml:space="preserve">kunci</t>
@@ -2612,6 +2655,9 @@
     <t xml:space="preserve">kepala</t>
   </si>
   <si>
+    <t xml:space="preserve">wakil_kepala</t>
+  </si>
+  <si>
     <t xml:space="preserve">jumlah_kk</t>
   </si>
   <si>
@@ -2630,6 +2676,12 @@
     <t xml:space="preserve">Lingkungan 1</t>
   </si>
   <si>
+    <t xml:space="preserve">Jonathan Tombuku Londok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Femmi Selvie Kowel</t>
+  </si>
+  <si>
     <t xml:space="preserve">116</t>
   </si>
   <si>
@@ -2645,6 +2697,12 @@
     <t xml:space="preserve">80</t>
   </si>
   <si>
+    <t xml:space="preserve">Reynold Happy Sondakh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jefry Hengky Mende</t>
+  </si>
+  <si>
     <t xml:space="preserve">114</t>
   </si>
   <si>
@@ -2660,6 +2718,12 @@
     <t xml:space="preserve">Lingkungan 4</t>
   </si>
   <si>
+    <t xml:space="preserve">Djerry Andreu Legi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fredy Ali</t>
+  </si>
+  <si>
     <t xml:space="preserve">67</t>
   </si>
   <si>
@@ -2678,6 +2742,12 @@
     <t xml:space="preserve">Lingkungan 5</t>
   </si>
   <si>
+    <t xml:space="preserve">Tombuku Costan Sumolang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trully Treyse Lalawi</t>
+  </si>
+  <si>
     <t xml:space="preserve">113</t>
   </si>
   <si>
@@ -2696,6 +2766,12 @@
     <t xml:space="preserve">Lingkungan 6</t>
   </si>
   <si>
+    <t xml:space="preserve">Marho Katotje Singal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marten Singal</t>
+  </si>
+  <si>
     <t xml:space="preserve">96</t>
   </si>
   <si>
@@ -2727,6 +2803,12 @@
   </si>
   <si>
     <t xml:space="preserve">Lingkungan 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jon Junus Mende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treisye Roisye Rondonuwu</t>
   </si>
   <si>
     <t xml:space="preserve">97</t>
@@ -3342,7 +3424,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
@@ -3675,7 +3757,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
         <v>74</v>
       </c>
@@ -3731,28 +3813,28 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>95</v>
       </c>
@@ -3763,7 +3845,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>98</v>
       </c>
@@ -3774,7 +3856,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>101</v>
       </c>
@@ -3785,25 +3867,25 @@
         <v>103</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="2" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="4" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3841,47 +3923,47 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3973,47 +4055,47 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4024,51 +4106,51 @@
         <v>160</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>109</v>
+      <c r="B84" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4127,237 +4209,248 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="2" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>194</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
+      <c r="A95" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3" t="s">
-        <v>195</v>
-      </c>
+      <c r="A96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B97" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>61</v>
+        <v>204</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>204</v>
+        <v>61</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2"/>
-    </row>
-    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
+      <c r="A114" s="2" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="117" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2"/>
+    </row>
+    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2"/>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4385,42 +4478,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4431,137 +4524,137 @@
         <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5081,43 +5174,50 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="C2" s="2" t="s">
         <v>76</v>
       </c>
@@ -5133,152 +5233,186 @@
       <c r="G2" s="2" t="s">
         <v>88</v>
       </c>
+      <c r="H2" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>276</v>
+      </c>
       <c r="C3" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>283</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>280</v>
+        <v>287</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>298</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>292</v>
+        <v>303</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>306</v>
+      </c>
       <c r="C7" s="2" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>298</v>
+        <v>311</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>303</v>
+        <v>316</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>319</v>
+      </c>
       <c r="C9" s="2" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>274</v>
+        <v>322</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>308</v>
+        <v>323</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,6 +5423,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -5298,6 +5433,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
@@ -5307,6 +5443,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
@@ -5316,6 +5453,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -5325,6 +5463,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
@@ -5334,6 +5473,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
@@ -5343,6 +5483,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -5352,6 +5493,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -5361,6 +5503,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -5370,6 +5513,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -5379,6 +5523,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
@@ -5388,6 +5533,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
@@ -5397,6 +5543,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -5406,6 +5553,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -5415,6 +5563,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -5424,6 +5573,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -5433,6 +5583,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
@@ -5442,6 +5593,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
@@ -5451,6 +5603,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
@@ -5460,6 +5613,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
@@ -5469,6 +5623,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -5478,6 +5633,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -5487,6 +5643,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
@@ -5496,6 +5653,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
@@ -5505,6 +5663,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -5514,6 +5673,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -5523,6 +5683,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
@@ -5532,6 +5693,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -5541,6 +5703,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
@@ -5550,6 +5713,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
@@ -5559,6 +5723,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
@@ -5568,6 +5733,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
@@ -5577,6 +5743,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
@@ -5586,6 +5753,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
@@ -5595,6 +5763,7 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
@@ -5604,6 +5773,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
@@ -5613,6 +5783,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
@@ -5622,6 +5793,7 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
@@ -5631,6 +5803,7 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
@@ -5640,6 +5813,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -5649,6 +5823,7 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -5658,6 +5833,7 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -5667,6 +5843,7 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -5676,6 +5853,7 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -5685,6 +5863,7 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -5694,6 +5873,7 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -5703,6 +5883,7 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -5712,6 +5893,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -5721,6 +5903,7 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -5730,6 +5913,7 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -5739,6 +5923,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -5748,6 +5933,7 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -5757,6 +5943,7 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -5766,6 +5953,7 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -5775,6 +5963,7 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -5784,6 +5973,7 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
@@ -5793,6 +5983,7 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
@@ -5802,6 +5993,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
@@ -5811,6 +6003,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
@@ -5820,6 +6013,7 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
@@ -5829,6 +6023,7 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
@@ -5838,6 +6033,7 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
@@ -5847,6 +6043,7 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
@@ -5856,6 +6053,7 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
@@ -5865,6 +6063,7 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
@@ -5874,6 +6073,7 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
@@ -5883,6 +6083,7 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
@@ -5892,6 +6093,7 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
@@ -5901,6 +6103,7 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
@@ -5910,6 +6113,7 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
@@ -5919,6 +6123,7 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
@@ -5928,6 +6133,7 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
@@ -5937,6 +6143,7 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
@@ -5946,6 +6153,7 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
@@ -5955,6 +6163,7 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
@@ -5964,6 +6173,7 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
@@ -5973,6 +6183,7 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
@@ -5982,6 +6193,7 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
@@ -5991,6 +6203,7 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
@@ -6000,6 +6213,7 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
@@ -6009,6 +6223,7 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
@@ -6018,6 +6233,7 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
@@ -6027,6 +6243,7 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
@@ -6036,6 +6253,7 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
@@ -6045,6 +6263,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
@@ -6054,6 +6273,7 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
@@ -6063,6 +6283,7 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
@@ -6072,6 +6293,7 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
@@ -6081,6 +6303,7 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
@@ -6090,6 +6313,7 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
@@ -6099,6 +6323,7 @@
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
@@ -6108,6 +6333,7 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
@@ -6117,6 +6343,7 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
@@ -6126,6 +6353,7 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
@@ -6135,6 +6363,7 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
@@ -6144,6 +6373,7 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
@@ -6153,6 +6383,7 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2"/>
@@ -6162,6 +6393,7 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2"/>
@@ -6171,6 +6403,7 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2"/>
@@ -6180,6 +6413,7 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6208,27 +6442,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
@@ -6236,26 +6470,26 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -6994,70 +7228,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7800,144 +8034,144 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9371,16 +9605,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>28</v>
@@ -10231,149 +10465,149 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -11412,16 +11646,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -14,9 +14,8 @@
     <sheet name="aparat" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="kontak" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="wisata" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="umkm" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="layanan" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="galeri" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="layanan" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="galeri" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -1213,220 +1212,6 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">WAJIB. Nama usaha. Untuk menghapus usaha: hapus barisnya.
-Contoh: Kue Lapis Bu Ani</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
-Contoh: Ya</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Opsional. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link). Kosong = foto bawaan situs.
-Contoh: https://drive.google.com/file/d/…/view</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>11</xdr:row>
-                <xdr:rowOff>14</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Produk utama.
-Contoh: Kue lapis legit, kue kering</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Nomor telepon/WA usaha — hanya bila pemilik setuju ditampilkan.
-Contoh: 0812-3456-7890</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Lokasi usaha, pilih dari daftar (diambil dari tab lingkungan).
-Contoh: Lingkungan 2</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
-  <authors>
-    <author> </author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
           <t xml:space="preserve">WAJIB. Nama surat. Untuk menghapus surat: hapus barisnya.
 Contoh: Surat Keterangan Tidak Mampu (SKTM)</t>
         </r>
@@ -1695,7 +1480,7 @@
 </comments>
 </file>
 
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -1842,7 +1627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="387">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -1904,10 +1689,10 @@
     <t xml:space="preserve">profil</t>
   </si>
   <si>
-    <t xml:space="preserve">Profil, Legenda, Kontak, Layanan, Penduduk (tahun &amp; sumber), Beranda (foto besar), header &amp; footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; luas, ketinggian, suhu; batas wilayah; sejarah; legenda; tahun &amp; sumber data; foto hero</t>
+    <t xml:space="preserve">Profil, Kontak, Layanan, Penduduk (tahun &amp; sumber), Beranda (foto besar), header &amp; footer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; luas, ketinggian, suhu; batas wilayah; sejarah; tahun &amp; sumber data; foto hero</t>
   </si>
   <si>
     <t xml:space="preserve">lingkungan</t>
@@ -1946,15 +1731,6 @@
     <t xml:space="preserve">Satu baris per destinasi</t>
   </si>
   <si>
-    <t xml:space="preserve">umkm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UMKM, Galeri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satu baris per usaha</t>
-  </si>
-  <si>
     <t xml:space="preserve">layanan</t>
   </si>
   <si>
@@ -1970,7 +1746,7 @@
     <t xml:space="preserve">Galeri</t>
   </si>
   <si>
-    <t xml:space="preserve">Foto tambahan (kegiatan, alam, budaya) selain foto wisata &amp; UMKM</t>
+    <t xml:space="preserve">Foto tambahan (kegiatan, alam, budaya) selain foto wisata</t>
   </si>
   <si>
     <t xml:space="preserve">ATURAN PENGISIAN</t>
@@ -2306,45 +2082,6 @@
     <t xml:space="preserve">https://maps.google.com/?q=Danau+Linow</t>
   </si>
   <si>
-    <t xml:space="preserve">umkm · nama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAJIB. Nama usaha. Untuk menghapus usaha: hapus barisnya.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kue Lapis Bu Ani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">umkm · tampil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">umkm · foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">umkm · produk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produk utama.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kue lapis legit, kue kering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">umkm · kontak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nomor telepon/WA usaha — hanya bila pemilik setuju ditampilkan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">umkm · lingkungan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lokasi usaha, pilih dari daftar (diambil dari tab lingkungan).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingkungan 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">layanan · nama_surat</t>
   </si>
   <si>
@@ -2513,12 +2250,6 @@
     <t xml:space="preserve">Sejarah, satu paragraf per baris</t>
   </si>
   <si>
-    <t xml:space="preserve">legenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legenda Danau Linow, satu paragraf per baris</t>
-  </si>
-  <si>
     <t xml:space="preserve">tahun_data</t>
   </si>
   <si>
@@ -2552,13 +2283,13 @@
     <t xml:space="preserve">Nilai yang belum ada data resminya ditandai "CONTOH" di kolom keterangan dan wajib diganti sebelum situs diumumkan:</t>
   </si>
   <si>
-    <t xml:space="preserve">• Tab profil: jam_layanan, luas_wilayah, ketinggian, suhu, sejarah, legenda.</t>
+    <t xml:space="preserve">• Tab profil: jam_layanan, luas_wilayah, ketinggian, suhu, sejarah.</t>
   </si>
   <si>
     <t xml:space="preserve">• Tab layanan: syarat, alur, waktu, biaya, dan catatan setiap surat perlu dicocokkan dengan ketentuan kantor kelurahan.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, kepala &amp; wakil kepala Lingkungan 7, nomor aparat, UMKM, galeri.</t>
+    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, kepala &amp; wakil kepala Lingkungan 7, nomor aparat, galeri.</t>
   </si>
   <si>
     <t xml:space="preserve">kunci</t>
@@ -2626,14 +2357,6 @@
     <t xml:space="preserve">CONTOH — ganti. Profil. Satu baris dalam sel = satu paragraf; paragraf pertama ditampilkan lebih besar.</t>
   </si>
   <si>
-    <t xml:space="preserve">Warga percaya kawasan Danau Linow adalah tempat bersemayamnya roh penjaga alam, dan uap belerang yang terus mengepul adalah napasnya.
-Cerita turun-temurun menyebutkan bahwa warna air danau yang berubah-ubah adalah pertanda suasana hati sang penjaga. Saat air berwarna cerah, warga meyakini alam sedang tenang dan hasil panen akan melimpah.
-Secara ilmiah, perubahan warna air danau dipengaruhi kandungan mineral dan aktivitas vulkanik di dasar danau. Namun kisah rakyat ini tetap diwariskan sebagai bagian dari kekayaan budaya setempat.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTOH — ganti dengan cerita yang dituturkan warga. Halaman Legenda. Satu baris dalam sel = satu paragraf.</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026</t>
   </si>
   <si>
@@ -2674,6 +2397,9 @@
   </si>
   <si>
     <t xml:space="preserve">Lingkungan 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lingkungan 2</t>
   </si>
   <si>
     <t xml:space="preserve">Jonathan Tombuku Londok</t>
@@ -3002,9 +2728,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://maps.google.com/?q=Mahwatu+Tomohon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">produk</t>
   </si>
   <si>
     <t xml:space="preserve">nama_surat</t>
@@ -3424,7 +3147,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
@@ -3610,106 +3333,106 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="2" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="2" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+    <row r="34" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="2" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3725,28 +3448,28 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
         <v>71</v>
       </c>
@@ -3757,7 +3480,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
         <v>74</v>
       </c>
@@ -3813,28 +3536,28 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>95</v>
       </c>
@@ -3845,7 +3568,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>98</v>
       </c>
@@ -3856,7 +3579,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>101</v>
       </c>
@@ -3867,25 +3590,25 @@
         <v>103</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3923,47 +3646,47 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="B67" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
+      <c r="B68" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4055,402 +3778,317 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>156</v>
+      <c r="B78" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>169</v>
+      <c r="A84" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>112</v>
+      <c r="A85" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>176</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C89" s="2" t="s">
+      <c r="A89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B91" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B98" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>61</v>
+        <v>203</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B106" s="2" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="s">
+    <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B107" s="2" t="s">
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="s">
+    <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B108" s="2" t="s">
+    </row>
+    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="s">
+    <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B109" s="2" t="s">
+    </row>
+    <row r="116" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2"/>
-    </row>
-    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2"/>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4469,7 +4107,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.98"/>
@@ -4478,184 +4116,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>264</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>229</v>
-      </c>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="2" t="s">
-        <v>266</v>
-      </c>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -5151,11 +4783,6 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5187,232 +4814,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6442,27 +6069,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
@@ -6470,26 +6097,26 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -7228,70 +6855,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8034,144 +7661,144 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>351</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9597,859 +9224,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="13.49"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="6"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="6"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="6"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="6"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="6"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="6"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="6"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="6"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="6"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="6"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="6"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="6"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="6"/>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="6"/>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="6"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="6"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="6"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="6"/>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="6"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="6"/>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="6"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="6"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="6"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="6"/>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="6"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="6"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="6"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="6"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="6"/>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="6"/>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="6"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="6"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="6"/>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="6"/>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="6"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="6"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="6"/>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="6"/>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="6"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="6"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="6"/>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="6"/>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="6"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="6"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="6"/>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="6"/>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="6"/>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="6"/>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="6"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="6"/>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="6"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B101" type="list">
-      <formula1>"Ya,Tidak"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F2:F101" type="list">
-      <formula1>lingkungan!$A$2:$A$500</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:H106"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -10465,149 +9239,149 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -11633,7 +10407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -11646,16 +10420,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -570,7 +570,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Opsional. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link). Kosong = foto bawaan situs.
+          <t xml:space="preserve">Opsional — biasanya cukup unggah foto ke folder foto Drive dengan nama yang sesuai (lihat tab petunjuk). Isi kolom ini hanya untuk menimpanya dengan tautan berbagi satu foto.
 Contoh: https://drive.google.com/file/d/…/view</t>
         </r>
       </text>
@@ -587,8 +587,8 @@
               <xdr:to>
                 <xdr:col>6</xdr:col>
                 <xdr:colOff>47</xdr:colOff>
-                <xdr:row>11</xdr:row>
-                <xdr:rowOff>14</xdr:rowOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -862,7 +862,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Opsional. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link). Kosong = foto bawaan situs.
+          <t xml:space="preserve">Opsional — biasanya cukup unggah foto ke folder foto Drive dengan nama yang sesuai (lihat tab petunjuk). Isi kolom ini hanya untuk menimpanya dengan tautan berbagi satu foto.
 Contoh: https://drive.google.com/file/d/…/view</t>
         </r>
       </text>
@@ -880,7 +880,7 @@
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>33</xdr:rowOff>
+                <xdr:rowOff>108</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1562,7 +1562,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">WAJIB untuk galeri. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link).
+          <t xml:space="preserve">Tautan satu foto Drive — atau kosongkan dan unggah foto ke folder Drive galeri/ dengan nama berkas = judul.
 Contoh: https://drive.google.com/file/d/…/view</t>
         </r>
       </text>
@@ -1627,7 +1627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="394">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -1659,22 +1659,37 @@
     <t xml:space="preserve">• Setelah mengubah data, buka halaman Cek Data: https://vercoooo.github.io/web-lahendong/cek-data.html — setiap isian yang keliru ditunjukkan beserta cara memperbaikinya.</t>
   </si>
   <si>
-    <t xml:space="preserve">FOTO DARI GOOGLE DRIVE (kolom foto &amp; kunci foto_hero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Unggah foto (JPG/PNG, sisi terpanjang sekitar 1600 piksel sudah cukup) ke folder Google Drive situs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Klik kanan foto → Bagikan → Akses umum: "Siapa saja yang memiliki link" sebagai Pelihat. (Atur sekali di folder agar semua foto di dalamnya ikut.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Klik kanan foto → Bagikan → Salin link, lalu tempel di kolom foto pada baris yang sesuai.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Buka halaman Cek Data: foto yang belum dibagikan atau tautannya salah akan ditandai.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Gunakan tautan satu foto, bukan tautan folder. Foto orang hanya dengan izin yang bersangkutan.</t>
+    <t xml:space="preserve">FOTO DARI GOOGLE DRIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cara utama: unggah foto ke folder "Foto Situs Lahendong" di Google Drive (menu Situs → Buka folder foto). Situs mengenali foto dari NAMA BERKAS dan SUBFOLDER-nya:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• beranda/hero.jpg → gambar besar di Beranda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• wisata/&lt;nama destinasi&gt;.jpg → mis. wisata/Danau Linow.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• aparat/&lt;jabatan atau nama tanpa gelar&gt;.jpg → mis. aparat/Lurah.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• lingkungan/&lt;nama kepala/wakil&gt;.jpg → mis. lingkungan/Julius Joni Rondonuwu.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• kkt/&lt;NIM atau nama&gt;.jpg → mis. kkt/230211060074.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• galeri/&lt;kategori&gt;/&lt;judul&gt;.jpg → setiap foto otomatis masuk Galeri, mis. galeri/Kegiatan/Panen Raya.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mengganti foto: hapus berkas lama, unggah yang baru dengan nama sama. Menghapus: hapus berkasnya. Huruf besar/kecil dan ekstensi (.jpg/.png/.webp) bebas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perubahan tampil paling lambat 10 menit kemudian, atau segera lewat menu Situs → Sinkronkan foto sekarang. Foto orang 3:4 (pas foto), lanskap 3:2; hanya dengan izin yang bersangkutan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolom foto di tab lain (tautan Drive satu foto) tetap bisa dipakai untuk menimpa foto dari folder. Cek Data menandai nama berkas yang tidak cocok dengan data mana pun.</t>
   </si>
   <si>
     <t xml:space="preserve">TAB</t>
@@ -1746,7 +1761,16 @@
     <t xml:space="preserve">Galeri</t>
   </si>
   <si>
-    <t xml:space="preserve">Foto tambahan (kegiatan, alam, budaya) selain foto wisata</t>
+    <t xml:space="preserve">Opsional: judul &amp; kategori lewat sheet. Foto di folder Drive galeri/ sudah otomatis masuk Galeri tanpa baris di sini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semua halaman yang berfoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diisi OTOMATIS dari folder foto Google Drive oleh skrip (menu Situs). Jangan diedit.</t>
   </si>
   <si>
     <t xml:space="preserve">ATURAN PENGISIAN</t>
@@ -1935,7 +1959,7 @@
     <t xml:space="preserve">aparat · foto</t>
   </si>
   <si>
-    <t xml:space="preserve">Opsional. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link). Kosong = foto bawaan situs.</t>
+    <t xml:space="preserve">Opsional — biasanya cukup unggah foto ke folder foto Drive dengan nama yang sesuai (lihat tab petunjuk). Isi kolom ini hanya untuk menimpanya dengan tautan berbagi satu foto.</t>
   </si>
   <si>
     <t xml:space="preserve">https://drive.google.com/file/d/…/view</t>
@@ -2163,7 +2187,7 @@
     <t xml:space="preserve">galeri · foto</t>
   </si>
   <si>
-    <t xml:space="preserve">WAJIB untuk galeri. Tautan berbagi Google Drive satu foto (Bagikan → Siapa saja yang memiliki link → Salin link).</t>
+    <t xml:space="preserve">Tautan satu foto Drive — atau kosongkan dan unggah foto ke folder Drive galeri/ dengan nama berkas = judul.</t>
   </si>
   <si>
     <t xml:space="preserve">galeri · kategori</t>
@@ -2556,9 +2580,6 @@
   </si>
   <si>
     <t xml:space="preserve">nomor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foto</t>
   </si>
   <si>
     <t xml:space="preserve">Sekretaris Kelurahan</t>
@@ -3147,7 +3168,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
@@ -3211,718 +3232,705 @@
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="3" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+    <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="2" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="2" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="2" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="2" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="2" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="3" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="3" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+    <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="4" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="4" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="2" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="2" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="2" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="B50" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>85</v>
+      <c r="A53" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>91</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C61" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>135</v>
+      <c r="A71" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>153</v>
+      <c r="A77" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>169</v>
+      <c r="A83" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>172</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>175</v>
+      <c r="A85" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="s">
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3" t="s">
+      <c r="B91" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="s">
+      <c r="C91" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3930,165 +3938,214 @@
         <v>184</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>187</v>
+      <c r="C93" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C94" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B95" s="2" t="s">
+      <c r="A95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>194</v>
+      <c r="B97" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B108" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2"/>
-    </row>
-    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="3" t="s">
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="s">
+      <c r="B109" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>215</v>
       </c>
+      <c r="B110" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2"/>
+      <c r="A111" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2"/>
+    </row>
+    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -4116,172 +4173,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4814,232 +4871,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6069,27 +6126,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>309</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
@@ -6097,26 +6154,26 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -6855,70 +6912,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7661,144 +7718,144 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>309</v>
+        <v>45</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9239,149 +9296,149 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>368</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -10420,16 +10477,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>309</v>
+        <v>45</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -570,7 +570,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Opsional — biasanya cukup unggah foto ke folder foto Drive dengan nama yang sesuai (lihat tab petunjuk). Isi kolom ini hanya untuk menimpanya dengan tautan berbagi satu foto.
+          <t xml:space="preserve">Diisi otomatis lewat menu Situs → Pasang / ganti foto (pilih barisnya dulu). Kosong = foto bawaan situs.
 Contoh: https://drive.google.com/file/d/…/view</t>
         </r>
       </text>
@@ -587,8 +587,8 @@
               <xdr:to>
                 <xdr:col>6</xdr:col>
                 <xdr:colOff>47</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -862,7 +862,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Opsional — biasanya cukup unggah foto ke folder foto Drive dengan nama yang sesuai (lihat tab petunjuk). Isi kolom ini hanya untuk menimpanya dengan tautan berbagi satu foto.
+          <t xml:space="preserve">Diisi otomatis lewat menu Situs → Pasang / ganti foto (pilih barisnya dulu). Kosong = foto bawaan situs.
 Contoh: https://drive.google.com/file/d/…/view</t>
         </r>
       </text>
@@ -880,7 +880,7 @@
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>108</xdr:rowOff>
+                <xdr:rowOff>4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1562,7 +1562,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Tautan satu foto Drive — atau kosongkan dan unggah foto ke folder Drive galeri/ dengan nama berkas = judul.
+          <t xml:space="preserve">WAJIB untuk galeri. Pilih baris ini lalu menu Situs → Pasang / ganti foto.
 Contoh: https://drive.google.com/file/d/…/view</t>
         </r>
       </text>
@@ -1579,8 +1579,8 @@
               <xdr:to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1627,7 +1627,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="387">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -1659,37 +1659,22 @@
     <t xml:space="preserve">• Setelah mengubah data, buka halaman Cek Data: https://vercoooo.github.io/web-lahendong/cek-data.html — setiap isian yang keliru ditunjukkan beserta cara memperbaikinya.</t>
   </si>
   <si>
-    <t xml:space="preserve">FOTO DARI GOOGLE DRIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cara utama: unggah foto ke folder "Foto Situs Lahendong" di Google Drive (menu Situs → Buka folder foto). Situs mengenali foto dari NAMA BERKAS dan SUBFOLDER-nya:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• beranda/hero.jpg → gambar besar di Beranda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• wisata/&lt;nama destinasi&gt;.jpg → mis. wisata/Danau Linow.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• aparat/&lt;jabatan atau nama tanpa gelar&gt;.jpg → mis. aparat/Lurah.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• lingkungan/&lt;nama kepala/wakil&gt;.jpg → mis. lingkungan/Julius Joni Rondonuwu.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• kkt/&lt;NIM atau nama&gt;.jpg → mis. kkt/230211060074.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• galeri/&lt;kategori&gt;/&lt;judul&gt;.jpg → setiap foto otomatis masuk Galeri, mis. galeri/Kegiatan/Panen Raya.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mengganti foto: hapus berkas lama, unggah yang baru dengan nama sama. Menghapus: hapus berkasnya. Huruf besar/kecil dan ekstensi (.jpg/.png/.webp) bebas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perubahan tampil paling lambat 10 menit kemudian, atau segera lewat menu Situs → Sinkronkan foto sekarang. Foto orang 3:4 (pas foto), lanskap 3:2; hanya dengan izin yang bersangkutan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kolom foto di tab lain (tautan Drive satu foto) tetap bisa dipakai untuk menimpa foto dari folder. Cek Data menandai nama berkas yang tidak cocok dengan data mana pun.</t>
+    <t xml:space="preserve">MEMASANG FOTO (menu Situs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Klik baris yang ingin diberi foto (tab wisata, aparat, galeri, atau baris foto_hero di tab profil).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Menu Situs → Pasang / ganti foto…  (panel muncul di samping kanan).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Pilih foto → Simpan foto. Selesai — tautannya ditulis otomatis ke kolom foto. Muat ulang halaman situs untuk melihatnya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Melepas foto: buka panel yang sama → Hapus foto dari baris ini. Situs kembali memakai gambar bawaan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Panel hanya ada di Google Sheets versi komputer (browser). Foto orang hanya dengan izin yang bersangkutan.</t>
   </si>
   <si>
     <t xml:space="preserve">TAB</t>
@@ -1761,16 +1746,7 @@
     <t xml:space="preserve">Galeri</t>
   </si>
   <si>
-    <t xml:space="preserve">Opsional: judul &amp; kategori lewat sheet. Foto di folder Drive galeri/ sudah otomatis masuk Galeri tanpa baris di sini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semua halaman yang berfoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diisi OTOMATIS dari folder foto Google Drive oleh skrip (menu Situs). Jangan diedit.</t>
+    <t xml:space="preserve">Foto tambahan (kegiatan, alam, budaya) selain foto wisata</t>
   </si>
   <si>
     <t xml:space="preserve">ATURAN PENGISIAN</t>
@@ -1959,7 +1935,7 @@
     <t xml:space="preserve">aparat · foto</t>
   </si>
   <si>
-    <t xml:space="preserve">Opsional — biasanya cukup unggah foto ke folder foto Drive dengan nama yang sesuai (lihat tab petunjuk). Isi kolom ini hanya untuk menimpanya dengan tautan berbagi satu foto.</t>
+    <t xml:space="preserve">Diisi otomatis lewat menu Situs → Pasang / ganti foto (pilih barisnya dulu). Kosong = foto bawaan situs.</t>
   </si>
   <si>
     <t xml:space="preserve">https://drive.google.com/file/d/…/view</t>
@@ -2187,7 +2163,7 @@
     <t xml:space="preserve">galeri · foto</t>
   </si>
   <si>
-    <t xml:space="preserve">Tautan satu foto Drive — atau kosongkan dan unggah foto ke folder Drive galeri/ dengan nama berkas = judul.</t>
+    <t xml:space="preserve">WAJIB untuk galeri. Pilih baris ini lalu menu Situs → Pasang / ganti foto.</t>
   </si>
   <si>
     <t xml:space="preserve">galeri · kategori</t>
@@ -2580,6 +2556,9 @@
   </si>
   <si>
     <t xml:space="preserve">nomor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foto</t>
   </si>
   <si>
     <t xml:space="preserve">Sekretaris Kelurahan</t>
@@ -3168,7 +3147,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
@@ -3237,22 +3216,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -3262,675 +3241,688 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="2" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="34" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="2" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="2" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="C43" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="B44" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C44" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
+      <c r="A47" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>66</v>
+      <c r="A48" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>75</v>
+      <c r="A53" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>96</v>
+      <c r="A60" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>99</v>
+      <c r="A61" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>129</v>
+      <c r="A71" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>143</v>
+      <c r="A77" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>146</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>161</v>
+      <c r="A83" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>165</v>
+      <c r="A85" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>171</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="A89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>180</v>
+      <c r="A90" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C91" s="4" t="s">
+      <c r="A91" s="3" t="s">
         <v>183</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3938,214 +3930,165 @@
         <v>184</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>111</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C94" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
+      <c r="A95" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3" t="s">
-        <v>190</v>
+      <c r="A96" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>23</v>
+      <c r="A97" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B109" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B110" s="2" t="s">
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
+    <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B111" s="2" t="s">
+    </row>
+    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
+    <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2"/>
-    </row>
-    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2"/>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4173,172 +4116,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4871,232 +4814,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6126,27 +6069,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
@@ -6154,26 +6097,26 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -6912,70 +6855,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7718,144 +7661,144 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>45</v>
+        <v>309</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9296,149 +9239,149 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -10477,16 +10420,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>45</v>
+        <v>309</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -15,7 +15,6 @@
     <sheet name="kontak" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="wisata" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="layanan" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="galeri" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -552,43 +551,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
+                <xdr:colOff>47</xdr:colOff>
                 <xdr:row>5</xdr:row>
                 <xdr:rowOff>12</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Diisi otomatis lewat menu Situs → Pasang / ganti foto (pilih barisnya dulu). Kosong = foto bawaan situs.
-Contoh: https://drive.google.com/file/d/…/view</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -794,7 +759,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">WAJIB. Nama destinasi. Hapus baris untuk menghapus destinasi.
+          <t xml:space="preserve">WAJIB. Pilih nama destinasi dari daftar — jangan diketik ulang. Destinasi baru tidak bisa ditambah dari sini karena butuh foto; hubungi pengelola situs. Menyembunyikan: tampil = Tidak.
 Contoh: Danau Linow</t>
         </r>
       </text>
@@ -811,8 +776,8 @@
               <xdr:to>
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>95</xdr:rowOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>48</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -844,7 +809,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>3</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
+                <xdr:colOff>-367</xdr:colOff>
                 <xdr:row>1</xdr:row>
                 <xdr:rowOff>110</xdr:rowOff>
               </xdr:to>
@@ -862,8 +827,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Diisi otomatis lewat menu Situs → Pasang / ganti foto (pilih barisnya dulu). Kosong = foto bawaan situs.
-Contoh: https://drive.google.com/file/d/…/view</t>
+          <t xml:space="preserve">Satu kalimat untuk kartu.
+Contoh: Danau vulkanik dengan warna air yang berubah.</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -879,8 +844,8 @@
               <xdr:to>
                 <xdr:col>4</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
-                <xdr:row>2</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>80</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -896,8 +861,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Satu kalimat untuk kartu.
-Contoh: Danau vulkanik dengan warna air yang berubah.</t>
+          <t xml:space="preserve">Uraian lengkap. Satu paragraf per baris (Ctrl+Enter).
+Contoh: (paragraf)</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -912,7 +877,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>-367</xdr:colOff>
+                <xdr:colOff>-267</xdr:colOff>
                 <xdr:row>1</xdr:row>
                 <xdr:rowOff>80</xdr:rowOff>
               </xdr:to>
@@ -930,8 +895,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Uraian lengkap. Satu paragraf per baris (Ctrl+Enter).
-Contoh: (paragraf)</t>
+          <t xml:space="preserve">Jam buka. Baris pertama tampil di kartu.
+Contoh: Setiap hari, 08.00 – 18.00 WITA</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -946,7 +911,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>6</xdr:col>
-                <xdr:colOff>-267</xdr:colOff>
+                <xdr:colOff>-367</xdr:colOff>
                 <xdr:row>1</xdr:row>
                 <xdr:rowOff>80</xdr:rowOff>
               </xdr:to>
@@ -964,8 +929,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Jam buka. Baris pertama tampil di kartu.
-Contoh: Setiap hari, 08.00 – 18.00 WITA</t>
+          <t xml:space="preserve">Harga tiket. Baris pertama tampil di kartu.
+Contoh: Rp10.000 per orang</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -998,8 +963,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Harga tiket. Baris pertama tampil di kartu.
-Contoh: Rp10.000 per orang</t>
+          <t xml:space="preserve">Dipisah koma.
+Contoh: Parkir, toilet, warung</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -1016,7 +981,7 @@
                 <xdr:col>8</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>80</xdr:rowOff>
+                <xdr:rowOff>35</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1032,8 +997,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Dipisah koma.
-Contoh: Parkir, toilet, warung</t>
+          <t xml:space="preserve">Saran waktu berkunjung, satu per baris.
+Contoh: Pagi hari</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -1050,7 +1015,7 @@
                 <xdr:col>9</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>35</xdr:rowOff>
+                <xdr:rowOff>65</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1066,8 +1031,8 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Saran waktu berkunjung, satu per baris.
-Contoh: Pagi hari</t>
+          <t xml:space="preserve">Rute, satu langkah per baris.
+Contoh: Dari pusat Kota Tomohon …</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -1084,7 +1049,7 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>65</xdr:rowOff>
+                <xdr:rowOff>80</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1093,40 +1058,6 @@
       </mc:AlternateContent>
     </comment>
     <comment ref="J1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Rute, satu langkah per baris.
-Contoh: Dari pusat Kota Tomohon …</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>-367</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>80</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1143,14 +1074,14 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>11</xdr:col>
+                <xdr:col>10</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>12</xdr:col>
-                <xdr:colOff>-284</xdr:colOff>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>-283</xdr:colOff>
                 <xdr:row>1</xdr:row>
                 <xdr:rowOff>65</xdr:rowOff>
               </xdr:to>
@@ -1160,7 +1091,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1177,13 +1108,13 @@
           <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
-                <xdr:col>12</xdr:col>
+                <xdr:col>11</xdr:col>
                 <xdr:colOff>23</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </xdr:from>
               <xdr:to>
-                <xdr:col>13</xdr:col>
+                <xdr:col>12</xdr:col>
                 <xdr:colOff>47</xdr:colOff>
                 <xdr:row>1</xdr:row>
                 <xdr:rowOff>95</xdr:rowOff>
@@ -1480,154 +1411,8 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
-  <authors>
-    <author> </author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">WAJIB. Judul foto, tampil di bawah foto.
-Contoh: Pengucapan Syukur 2026</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Ya = tampil di situs. Tidak = disembunyikan, data tetap tersimpan. Kosong dianggap Ya.
-Contoh: Ya</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">WAJIB untuk galeri. Pilih baris ini lalu menu Situs → Pasang / ganti foto.
-Contoh: https://drive.google.com/file/d/…/view</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>9</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Kelompok foto: pilih dari daftar atau ketik baru. Menjadi tombol penyaring di Galeri.
-Contoh: Kegiatan</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="364">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -1659,22 +1444,16 @@
     <t xml:space="preserve">• Setelah mengubah data, buka halaman Cek Data: https://vercoooo.github.io/web-lahendong/cek-data.html — setiap isian yang keliru ditunjukkan beserta cara memperbaikinya.</t>
   </si>
   <si>
-    <t xml:space="preserve">MEMASANG FOTO (menu Situs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Klik baris yang ingin diberi foto (tab wisata, aparat, galeri, atau baris foto_hero di tab profil).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Menu Situs → Pasang / ganti foto…  (panel muncul di samping kanan).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Pilih foto → Simpan foto. Selesai — tautannya ditulis otomatis ke kolom foto. Muat ulang halaman situs untuk melihatnya.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Melepas foto: buka panel yang sama → Hapus foto dari baris ini. Situs kembali memakai gambar bawaan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Panel hanya ada di Google Sheets versi komputer (browser). Foto orang hanya dengan izin yang bersangkutan.</t>
+    <t xml:space="preserve">FOTO &amp; DESTINASI WISATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Spreadsheet ini hanya berisi teks. Semua foto (beranda, wisata, aparat, tim KKT) disimpan di berkas situs dan diganti oleh pengelola situs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Karena itu daftar destinasi wisata tetap: pilih nama destinasi dari daftar, lalu ubah keterangannya sesuka hati. Baris dengan nama lain tidak tampil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Ingin mengganti foto atau menambah destinasi? Kirim fotonya ke pengelola situs.</t>
   </si>
   <si>
     <t xml:space="preserve">TAB</t>
@@ -1689,10 +1468,10 @@
     <t xml:space="preserve">profil</t>
   </si>
   <si>
-    <t xml:space="preserve">Profil, Kontak, Layanan, Penduduk (tahun &amp; sumber), Beranda (foto besar), header &amp; footer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; luas, ketinggian, suhu; batas wilayah; sejarah; tahun &amp; sumber data; foto hero</t>
+    <t xml:space="preserve">Profil, Kontak, Layanan, Penduduk (tahun &amp; sumber), header &amp; footer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; luas, ketinggian, suhu; batas wilayah; sejarah; tahun &amp; sumber data</t>
   </si>
   <si>
     <t xml:space="preserve">lingkungan</t>
@@ -1725,10 +1504,10 @@
     <t xml:space="preserve">wisata</t>
   </si>
   <si>
-    <t xml:space="preserve">Wisata, halaman detail wisata, Beranda, Galeri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satu baris per destinasi</t>
+    <t xml:space="preserve">Wisata, halaman detail wisata, Beranda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satu baris per destinasi. Daftar destinasinya tetap (pilih nama dari daftar); yang bisa diubah hanya keterangannya</t>
   </si>
   <si>
     <t xml:space="preserve">layanan</t>
@@ -1740,15 +1519,6 @@
     <t xml:space="preserve">Satu baris per jenis surat. syarat &amp; alur: satu butir per baris dalam sel</t>
   </si>
   <si>
-    <t xml:space="preserve">galeri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galeri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foto tambahan (kegiatan, alam, budaya) selain foto wisata</t>
-  </si>
-  <si>
     <t xml:space="preserve">ATURAN PENGISIAN</t>
   </si>
   <si>
@@ -1932,15 +1702,6 @@
     <t xml:space="preserve">0812-3456-7890</t>
   </si>
   <si>
-    <t xml:space="preserve">aparat · foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diisi otomatis lewat menu Situs → Pasang / ganti foto (pilih barisnya dulu). Kosong = foto bawaan situs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://drive.google.com/file/d/…/view</t>
-  </si>
-  <si>
     <t xml:space="preserve">kontak · nama</t>
   </si>
   <si>
@@ -1989,7 +1750,7 @@
     <t xml:space="preserve">wisata · nama</t>
   </si>
   <si>
-    <t xml:space="preserve">WAJIB. Nama destinasi. Hapus baris untuk menghapus destinasi.</t>
+    <t xml:space="preserve">WAJIB. Pilih nama destinasi dari daftar — jangan diketik ulang. Destinasi baru tidak bisa ditambah dari sini karena butuh foto; hubungi pengelola situs. Menyembunyikan: tampil = Tidak.</t>
   </si>
   <si>
     <t xml:space="preserve">Danau Linow</t>
@@ -1998,9 +1759,6 @@
     <t xml:space="preserve">wisata · tampil</t>
   </si>
   <si>
-    <t xml:space="preserve">wisata · foto</t>
-  </si>
-  <si>
     <t xml:space="preserve">wisata · ringkas</t>
   </si>
   <si>
@@ -2148,33 +1906,6 @@
     <t xml:space="preserve">Bawa dokumen asli saat pengambilan.</t>
   </si>
   <si>
-    <t xml:space="preserve">galeri · judul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAJIB. Judul foto, tampil di bawah foto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pengucapan Syukur 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">galeri · tampil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">galeri · foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAJIB untuk galeri. Pilih baris ini lalu menu Situs → Pasang / ganti foto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">galeri · kategori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelompok foto: pilih dari daftar atau ketik baru. Menjadi tombol penyaring di Galeri.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kegiatan</t>
-  </si>
-  <si>
     <t xml:space="preserve">KUNCI DI TAB PROFIL</t>
   </si>
   <si>
@@ -2262,12 +1993,6 @@
     <t xml:space="preserve">Sumber data kependudukan</t>
   </si>
   <si>
-    <t xml:space="preserve">foto_hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foto besar di Beranda (tautan Google Drive, opsional)</t>
-  </si>
-  <si>
     <t xml:space="preserve">TIDAK DIATUR DARI SPREADSHEET</t>
   </si>
   <si>
@@ -2289,7 +2014,7 @@
     <t xml:space="preserve">• Tab layanan: syarat, alur, waktu, biaya, dan catatan setiap surat perlu dicocokkan dengan ketentuan kantor kelurahan.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, kepala &amp; wakil kepala Lingkungan 7, nomor aparat, galeri.</t>
+    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, kepala &amp; wakil kepala Lingkungan 7, nomor aparat.</t>
   </si>
   <si>
     <t xml:space="preserve">kunci</t>
@@ -2369,9 +2094,6 @@
     <t xml:space="preserve">Sumber data kependudukan. Halaman Penduduk.</t>
   </si>
   <si>
-    <t xml:space="preserve">Opsional. Tautan Google Drive foto lanskap untuk gambar besar di Beranda. Kosong = ilustrasi bawaan.</t>
-  </si>
-  <si>
     <t xml:space="preserve">nama</t>
   </si>
   <si>
@@ -2556,9 +2278,6 @@
   </si>
   <si>
     <t xml:space="preserve">nomor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foto</t>
   </si>
   <si>
     <t xml:space="preserve">Sekretaris Kelurahan</t>
@@ -2827,9 +2546,6 @@
     <t xml:space="preserve">Bawa berkas ke kantor kelurahan
 Petugas memeriksa berkas
 Surat ditandatangani lurah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">judul</t>
   </si>
 </sst>
 </file>
@@ -3147,7 +2863,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
@@ -3216,742 +2932,727 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="A25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="2" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+    <row r="28" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="2" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="2" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
+      <c r="B41" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>52</v>
+      <c r="A42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>67</v>
+      <c r="A47" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>82</v>
+      <c r="A52" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>91</v>
+      <c r="A55" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B61" s="2" t="s">
+      <c r="A60" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>109</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C65" s="4" t="s">
+      <c r="A65" s="2" t="s">
         <v>121</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>138</v>
+      <c r="A72" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>153</v>
+      <c r="A77" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>160</v>
-      </c>
+      <c r="A80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>163</v>
+      <c r="A81" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B82" s="2" t="s">
+      <c r="A82" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>166</v>
+      <c r="B82" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="s">
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>58</v>
+        <v>189</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>190</v>
@@ -3966,129 +3667,49 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B97" s="2" t="s">
+    </row>
+    <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
+    <row r="100" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B98" s="2" t="s">
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="s">
+    <row r="103" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B99" s="2" t="s">
+    </row>
+    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="s">
+    <row r="105" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B100" s="2" t="s">
+    </row>
+    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2"/>
-    </row>
-    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2"/>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4107,7 +3728,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.98"/>
@@ -4116,173 +3737,169 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>211</v>
-      </c>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
-        <v>246</v>
-      </c>
+      <c r="C16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -4778,11 +4395,6 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
-    </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4814,232 +4426,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6059,767 +5671,661 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="6"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="6"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="6"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="6"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="6"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="6"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="6"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="6"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="6"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="6"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="6"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="6"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="6"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="6"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="6"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="6"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="6"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="6"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="6"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="6"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="6"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="6"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="6"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="6"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="6"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="6"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="6"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="6"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="6"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="6"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="6"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="6"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="6"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="6"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="6"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="6"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="6"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="6"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="6"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="6"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="6"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="6"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="6"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="6"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="6"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="6"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="6"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="6"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="6"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="6"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="6"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="6"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="6"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="6"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="6"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="6"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="6"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="6"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="6"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="6"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="6"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="6"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="6"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="6"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="6"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="6"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="6"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="6"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="6"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="6"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="6"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="6"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="6"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="6"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="6"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="6"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="6"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="6"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="6"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="6"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="6"/>
       <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="6"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="6"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="6"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="6"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="6"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="6"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="6"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="6"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="6"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="6"/>
       <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="6"/>
       <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="6"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="6"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="6"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="6"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="6"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="6"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="6"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6855,70 +6361,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7648,157 +7154,151 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="67.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="53.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="7" style="0" width="67.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="56.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="53.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="56.18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>330</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="D2" s="2" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>322</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>332</v>
+      </c>
       <c r="D4" s="2" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>359</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
-        <v>360</v>
+      <c r="K4" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7813,7 +7313,6 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
@@ -7827,7 +7326,6 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
@@ -7841,7 +7339,6 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -7855,7 +7352,6 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
@@ -7869,7 +7365,6 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
@@ -7883,7 +7378,6 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -7897,7 +7391,6 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
@@ -7911,7 +7404,6 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
@@ -7925,7 +7417,6 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -7939,7 +7430,6 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
@@ -7953,7 +7443,6 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
@@ -7967,7 +7456,6 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -7981,7 +7469,6 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -7995,7 +7482,6 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -8009,7 +7495,6 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -8023,7 +7508,6 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
@@ -8037,7 +7521,6 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
@@ -8051,7 +7534,6 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -8065,7 +7547,6 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -8079,7 +7560,6 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -8093,7 +7573,6 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -8107,7 +7586,6 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
@@ -8121,7 +7599,6 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
@@ -8135,7 +7612,6 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
@@ -8149,7 +7625,6 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
@@ -8163,7 +7638,6 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -8177,7 +7651,6 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -8191,7 +7664,6 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
@@ -8205,7 +7677,6 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
@@ -8219,7 +7690,6 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -8233,7 +7703,6 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -8247,7 +7716,6 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
@@ -8261,7 +7729,6 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -8275,7 +7742,6 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
@@ -8289,7 +7755,6 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
@@ -8303,7 +7768,6 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
@@ -8317,7 +7781,6 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
@@ -8331,7 +7794,6 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
@@ -8345,7 +7807,6 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
@@ -8359,7 +7820,6 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
@@ -8373,7 +7833,6 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
@@ -8387,7 +7846,6 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
@@ -8401,7 +7859,6 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
@@ -8415,7 +7872,6 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
@@ -8429,7 +7885,6 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -8443,7 +7898,6 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -8457,7 +7911,6 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -8471,7 +7924,6 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -8485,7 +7937,6 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -8499,7 +7950,6 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -8513,7 +7963,6 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -8527,7 +7976,6 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -8541,7 +7989,6 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -8555,7 +8002,6 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -8569,7 +8015,6 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -8583,7 +8028,6 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -8597,7 +8041,6 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -8611,7 +8054,6 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -8625,7 +8067,6 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -8639,7 +8080,6 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -8653,7 +8093,6 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
@@ -8667,7 +8106,6 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
@@ -8681,7 +8119,6 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
@@ -8695,7 +8132,6 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
@@ -8709,7 +8145,6 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
@@ -8723,7 +8158,6 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
@@ -8737,7 +8171,6 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
@@ -8751,7 +8184,6 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
@@ -8765,7 +8197,6 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
@@ -8779,7 +8210,6 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
@@ -8793,7 +8223,6 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
@@ -8807,7 +8236,6 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
@@ -8821,7 +8249,6 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
@@ -8835,7 +8262,6 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
@@ -8849,7 +8275,6 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
@@ -8863,7 +8288,6 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
@@ -8877,7 +8301,6 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
@@ -8891,7 +8314,6 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
@@ -8905,7 +8327,6 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
@@ -8919,7 +8340,6 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
@@ -8933,7 +8353,6 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
-      <c r="L85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
@@ -8947,7 +8366,6 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
-      <c r="L86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
@@ -8961,7 +8379,6 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
@@ -8975,7 +8392,6 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
@@ -8989,7 +8405,6 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
@@ -9003,7 +8418,6 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
@@ -9017,7 +8431,6 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
@@ -9031,7 +8444,6 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
@@ -9045,7 +8457,6 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
-      <c r="L93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
@@ -9059,7 +8470,6 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
-      <c r="L94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
@@ -9073,7 +8483,6 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
@@ -9087,7 +8496,6 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
@@ -9101,7 +8509,6 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
-      <c r="L97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
@@ -9115,7 +8522,6 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
-      <c r="L98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
@@ -9129,7 +8535,6 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
-      <c r="L99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
@@ -9143,7 +8548,6 @@
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
@@ -9157,7 +8561,6 @@
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
-      <c r="L101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
@@ -9171,7 +8574,6 @@
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
@@ -9185,7 +8587,6 @@
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
-      <c r="L103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
@@ -9199,10 +8600,13 @@
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A104" type="list">
+      <formula1>"Danau Linow,Hutan Pinus Lahendong,Mah’Watu"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B104" type="list">
       <formula1>"Ya,Tidak"</formula1>
       <formula2>0</formula2>
@@ -9239,149 +8643,149 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -10405,651 +9809,4 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="13.49"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="6"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="6"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="6"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="6"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="6"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="6"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="6"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="6"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="6"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="6"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="6"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="6"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="6"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="6"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="6"/>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="6"/>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="6"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="6"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="6"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="6"/>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="6"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="6"/>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="6"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="6"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="6"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="6"/>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="6"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="6"/>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="6"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="6"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="6"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="6"/>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="6"/>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="6"/>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="6"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="6"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="6"/>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="6"/>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="6"/>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="6"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="6"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="6"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="6"/>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="6"/>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="6"/>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="6"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="6"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="6"/>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="6"/>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="6"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="6"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="6"/>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="6"/>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="6"/>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="6"/>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="6"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="6"/>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="6"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B101" type="list">
-      <formula1>"Ya,Tidak"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Nilai ini belum ada di daftar. Tetap dipakai bila memang kategori baru." errorStyle="warning" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D101" type="list">
-      <formula1>"Kegiatan,Alam,Budaya"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -56,8 +56,8 @@
               <xdr:to>
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -74,7 +74,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Isi informasinya. Beberapa paragraf: pisahkan dengan baris baru (Ctrl+Enter).
-Contoh: Senin – Jumat, 08.00 – 15.00 WITA</t>
+Contoh: Senin – Kamis, 08.00 – 16.30 WITA / Jumat, 08.00 – 13.30 WITA</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -90,8 +90,8 @@
               <xdr:to>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
-                <xdr:row>7</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1412,7 +1412,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="365">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -1582,7 +1582,7 @@
     <t xml:space="preserve">Isi informasinya. Beberapa paragraf: pisahkan dengan baris baru (Ctrl+Enter).</t>
   </si>
   <si>
-    <t xml:space="preserve">Senin – Jumat, 08.00 – 15.00 WITA</t>
+    <t xml:space="preserve">Senin – Kamis, 08.00 – 16.30 WITA / Jumat, 08.00 – 13.30 WITA</t>
   </si>
   <si>
     <t xml:space="preserve">profil · keterangan</t>
@@ -1930,7 +1930,7 @@
     <t xml:space="preserve">Email kantor</t>
   </si>
   <si>
-    <t xml:space="preserve">Jam layanan kantor</t>
+    <t xml:space="preserve">Jam layanan per kelompok hari, dipisah / — mis. Senin – Kamis, 08.00 – 16.30 WITA / Jumat, 08.00 – 13.30 WITA / Sabtu – Minggu, Tutup. Bilah atas situs menampilkan jam hari ini.</t>
   </si>
   <si>
     <t xml:space="preserve">luas_wilayah</t>
@@ -2036,6 +2036,9 @@
   </si>
   <si>
     <t xml:space="preserve">Halaman Kontak. Kosong = tidak ditampilkan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senin – Kamis, 08.00 – 16.30 WITA / Jumat, 08.00 – 13.30 WITA / Sabtu – Minggu, Hanya keadaan mendesak</t>
   </si>
   <si>
     <t xml:space="preserve">CONTOH — ganti. Header, footer, halaman Kontak dan Layanan.</t>
@@ -3578,7 +3581,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
         <v>53</v>
       </c>
@@ -3775,15 +3778,15 @@
         <v>207</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3791,10 +3794,10 @@
         <v>173</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3802,10 +3805,10 @@
         <v>175</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3813,10 +3816,10 @@
         <v>177</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3824,10 +3827,10 @@
         <v>179</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3835,10 +3838,10 @@
         <v>181</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3846,10 +3849,10 @@
         <v>183</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3857,10 +3860,10 @@
         <v>185</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3868,10 +3871,10 @@
         <v>187</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3879,10 +3882,10 @@
         <v>189</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3890,10 +3893,10 @@
         <v>191</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4426,33 +4429,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>65</v>
@@ -4478,28 +4481,28 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4507,151 +4510,151 @@
         <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5681,16 +5684,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5705,10 +5708,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>92</v>
@@ -5720,7 +5723,7 @@
         <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>92</v>
@@ -6361,70 +6364,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7167,37 +7170,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7208,97 +7211,97 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8643,45 +8646,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>157</v>
@@ -8702,36 +8705,36 @@
         <v>148</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>157</v>
@@ -8743,22 +8746,22 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>160</v>
@@ -8767,19 +8770,19 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>157</v>

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -10,11 +10,12 @@
   <sheets>
     <sheet name="petunjuk" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="profil" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="lingkungan" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="aparat" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="kontak" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="wisata" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="layanan" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="sejarah" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="lingkungan" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="aparat" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="kontak" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="wisata" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="layanan" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -90,8 +91,8 @@
               <xdr:to>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>-367</xdr:colOff>
-                <xdr:row>8</xdr:row>
-                <xdr:rowOff>6</xdr:rowOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>57</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -138,6 +139,84 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author> </author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">WAJIB. Judul bagian sejarah. Urutan baris = urutan tampil.
+Contoh: Asal usul nama</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-367</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>33</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Isi bagian itu. Satu paragraf per baris (Ctrl+Enter); baris berawalan "- " menjadi butir daftar, dan "Label: isi" di awal butir ditebalkan labelnya.
+Contoh: - Migrasi dari Sarongsong (tahun 1750): Pada tahun 1750, …</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>106</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -419,7 +498,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -517,7 +596,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
+                <xdr:colOff>16</xdr:colOff>
                 <xdr:row>10</xdr:row>
                 <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
@@ -565,7 +644,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -745,7 +824,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -777,7 +856,7 @@
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
                 <xdr:row>2</xdr:row>
-                <xdr:rowOff>48</xdr:rowOff>
+                <xdr:rowOff>78</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1047,7 +1126,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>-367</xdr:colOff>
+                <xdr:colOff>32</xdr:colOff>
                 <xdr:row>1</xdr:row>
                 <xdr:rowOff>80</xdr:rowOff>
               </xdr:to>
@@ -1081,7 +1160,7 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>11</xdr:col>
-                <xdr:colOff>-283</xdr:colOff>
+                <xdr:colOff>-367</xdr:colOff>
                 <xdr:row>1</xdr:row>
                 <xdr:rowOff>65</xdr:rowOff>
               </xdr:to>
@@ -1129,7 +1208,7 @@
 </comments>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author> </author>
@@ -1144,7 +1223,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">WAJIB. Nama surat. Untuk menghapus surat: hapus barisnya.
-Contoh: Surat Keterangan Tidak Mampu (SKTM)</t>
+Contoh: Surat Keterangan Domisili</t>
         </r>
       </text>
       <mc:AlternateContent>
@@ -1160,8 +1239,8 @@
               <xdr:to>
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>15</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1193,9 +1272,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>3</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
-                <xdr:row>2</xdr:row>
-                <xdr:rowOff>48</xdr:rowOff>
+                <xdr:colOff>32</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>15</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1227,9 +1306,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>-300</xdr:colOff>
-                <xdr:row>2</xdr:row>
-                <xdr:rowOff>33</xdr:rowOff>
+                <xdr:colOff>-101</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>31</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1261,9 +1340,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>-367</xdr:colOff>
-                <xdr:row>2</xdr:row>
-                <xdr:rowOff>33</xdr:rowOff>
+                <xdr:colOff>-242</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>31</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1295,9 +1374,9 @@
               </xdr:from>
               <xdr:to>
                 <xdr:col>6</xdr:col>
-                <xdr:colOff>-1</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:colOff>-350</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>44</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1330,8 +1409,8 @@
               <xdr:to>
                 <xdr:col>7</xdr:col>
                 <xdr:colOff>32</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>35</xdr:rowOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1398,8 +1477,8 @@
               <xdr:to>
                 <xdr:col>9</xdr:col>
                 <xdr:colOff>47</xdr:colOff>
-                <xdr:row>2</xdr:row>
-                <xdr:rowOff>33</xdr:rowOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>31</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1412,7 +1491,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="394">
   <si>
     <t xml:space="preserve">PETUNJUK MENGELOLA DATA — Website Kelurahan Lahendong</t>
   </si>
@@ -1471,7 +1550,16 @@
     <t xml:space="preserve">Profil, Kontak, Layanan, Penduduk (tahun &amp; sumber), header &amp; footer</t>
   </si>
   <si>
-    <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; luas, ketinggian, suhu; batas wilayah; sejarah; tahun &amp; sumber data</t>
+    <t xml:space="preserve">Alamat, telepon, email &amp; jam layanan kantor; letak, koordinat, luas, ketinggian, suhu; batas wilayah; visi &amp; misi; tahun &amp; sumber data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sejarah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil (bagian Sejarah)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satu baris per bagian sejarah, urut seperti di sheet. isi: satu paragraf per baris; baris berawalan "- " menjadi butir</t>
   </si>
   <si>
     <t xml:space="preserve">lingkungan</t>
@@ -1594,6 +1682,24 @@
     <t xml:space="preserve">CONTOH — ganti</t>
   </si>
   <si>
+    <t xml:space="preserve">sejarah · judul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAJIB. Judul bagian sejarah. Urutan baris = urutan tampil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asal usul nama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sejarah · isi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isi bagian itu. Satu paragraf per baris (Ctrl+Enter); baris berawalan "- " menjadi butir daftar, dan "Label: isi" di awal butir ditebalkan labelnya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Migrasi dari Sarongsong (tahun 1750): Pada tahun 1750, …</t>
+  </si>
+  <si>
     <t xml:space="preserve">lingkungan · nama</t>
   </si>
   <si>
@@ -1846,7 +1952,7 @@
     <t xml:space="preserve">WAJIB. Nama surat. Untuk menghapus surat: hapus barisnya.</t>
   </si>
   <si>
-    <t xml:space="preserve">Surat Keterangan Tidak Mampu (SKTM)</t>
+    <t xml:space="preserve">Surat Keterangan Domisili</t>
   </si>
   <si>
     <t xml:space="preserve">layanan · tampil</t>
@@ -1975,10 +2081,28 @@
     <t xml:space="preserve">Batas barat</t>
   </si>
   <si>
-    <t xml:space="preserve">sejarah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sejarah, satu paragraf per baris</t>
+    <t xml:space="preserve">letak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uraian letak &amp; kondisi wilayah, satu paragraf per baris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">koordinat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titik koordinat, mis. 1°16′42″ LU, 124°48′51″ BT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">misi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misi, satu per baris (nomor dibuat situs)</t>
   </si>
   <si>
     <t xml:space="preserve">tahun_data</t>
@@ -2008,13 +2132,7 @@
     <t xml:space="preserve">Nilai yang belum ada data resminya ditandai "CONTOH" di kolom keterangan dan wajib diganti sebelum situs diumumkan:</t>
   </si>
   <si>
-    <t xml:space="preserve">• Tab profil: jam_layanan, luas_wilayah, ketinggian, suhu, sejarah.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Tab layanan: syarat, alur, waktu, biaya, dan catatan setiap surat perlu dicocokkan dengan ketentuan kantor kelurahan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Masih kosong: telepon_kantor, email, kepala &amp; wakil kepala Lingkungan 7, nomor aparat.</t>
+    <t xml:space="preserve">• Masih kosong: kepala &amp; wakil kepala Lingkungan 7; cara menuju lokasi Mah’Watu; pengelola tiap destinasi (isi hanya bila pasti).</t>
   </si>
   <si>
     <t xml:space="preserve">kunci</t>
@@ -2032,34 +2150,53 @@
     <t xml:space="preserve">Footer dan halaman Kontak.</t>
   </si>
   <si>
+    <t xml:space="preserve">085555555</t>
+  </si>
+  <si>
     <t xml:space="preserve">Header, footer, dan halaman Kontak. Kosong = tidak ditampilkan.</t>
   </si>
   <si>
+    <t xml:space="preserve">lahendong@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Halaman Kontak. Kosong = tidak ditampilkan.</t>
   </si>
   <si>
     <t xml:space="preserve">Senin – Kamis, 08.00 – 16.30 WITA / Jumat, 08.00 – 13.30 WITA / Sabtu – Minggu, Hanya keadaan mendesak</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTOH — ganti. Header, footer, halaman Kontak dan Layanan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTOH — ganti. Angka saja, satuan km². Beranda dan Profil.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">800–950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTOH — ganti. Satuan mdpl. Profil.</t>
+    <t xml:space="preserve">Header, footer, halaman Kontak dan Layanan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secara geografis, Kelurahan Lahendong berada di wilayah perbukitan vulkanik dan dataran tinggi, sekitar 5,2 km dari pusat Kota Tomohon dan sekitar 30 km di sebelah selatan Kota Manado.
+Dengan luas 6,8 km², Lahendong termasuk kelurahan terluas di Kecamatan Tomohon Selatan setelah Kelurahan Pinaras dan Kelurahan Pangolombian. Ketinggiannya yang mencapai 750–1.200 mdpl menjadikannya kawasan berhawa sejuk dan kaya akan manifestasi panas bumi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil, bagian Kondisi wilayah. Satu baris dalam sel = satu paragraf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1°16′42″ LU, 124°48′51″ BT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil, di bawah angka kondisi wilayah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angka saja, satuan km². Beranda dan Profil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">750–1.200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satuan mdpl. Profil.</t>
   </si>
   <si>
     <t xml:space="preserve">22–26</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTOH — ganti. Satuan °C. Profil.</t>
+    <t xml:space="preserve">Satuan °C. Profil.</t>
   </si>
   <si>
     <t xml:space="preserve">Tumatangtang 1, Kampung Jawa</t>
@@ -2077,12 +2214,20 @@
     <t xml:space="preserve">Pinaras, Rambunan</t>
   </si>
   <si>
-    <t xml:space="preserve">Lahendong tumbuh dari perkampungan kecil di sekitar sumber panas bumi alami di kaki pegunungan Tomohon.
-Nama "Lahendong" dipercaya masyarakat setempat berkaitan dengan uap panas bumi yang kerap muncul di kawasan ini sejak lama.
-Seiring waktu, wilayah ini berkembang menjadi salah satu kelurahan definitif di Kecamatan Tomohon Selatan, dengan warga yang bertumpu pada pertanian, usaha rumahan, serta pariwisata di sekitar Danau Linow dan kawasan panas bumi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTOH — ganti. Profil. Satu baris dalam sel = satu paragraf; paragraf pertama ditampilkan lebih besar.</t>
+    <t xml:space="preserve">Tomohon Maju, Berdaya Saing, dan Sejahtera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil, bagian Visi &amp; Misi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menjaga dan melestarikan Tomohon sebagai kota religius dan berbudaya
+Mewujudkan ketahanan pangan dan pembangunan berwawasan lingkungan
+Mewujudkan Tomohon sebagai kota wisata dunia
+Mewujudkan pemerintahan yang berintegritas, adaptif, dan responsif
+Meningkatkan kesejahteraan masyarakat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil, bagian Visi &amp; Misi. Satu misi per baris dalam sel (Ctrl+Enter); nomor dibuat situs.</t>
   </si>
   <si>
     <t xml:space="preserve">2026</t>
@@ -2097,6 +2242,48 @@
     <t xml:space="preserve">Sumber data kependudukan. Halaman Penduduk.</t>
   </si>
   <si>
+    <t xml:space="preserve">judul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sejarah singkat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sejarah Kelurahan Lahendong di Tomohon Selatan memiliki kaitan erat dengan kisah migrasi leluhur Minahasa, legenda alam Danau Linow, dan kekayaan ekologis wilayah tersebut.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebutan Lahendong berasal dari nama sebatang pohon besar yang dahulu tumbuh mencolok di dekat mata air wilayah tersebut, yaitu Pohon Lumahendong (atau Lahendong). Pada zaman dahulu, kulit pohon Lahendong ditumbuk oleh penduduk setempat dan dimanfaatkan sebagai bahan pakaian tradisional yang disebut Momo’.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awal mula permukiman (abad ke-17 &amp; 18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Kedatangan leluhur awal: Catatan sejarawan Belanda, Dr. J.G.F. Riedel, menyebutkan bahwa permukiman awal di kawasan Rano Lahendong dirintis oleh Penghulu Repi dari kalangan Makatelu Pitu bersama keluarganya.
+- Migrasi dari Sarongsong (tahun 1750): Pada tahun 1750, di masa kepemimpinan Mayoor Tongkotou, seorang petani bernama Mokalo Rondonuwo berjalan kaki sejauh 5 km dari Sarongsong Tulau (Wanua Ureh). Ia menemukan kawasan hutan subur yang dipenuhi hawa dingin dan aroma belerang (fumarola). Mokalo kemudian mengajak keluarga dan kerabatnya datang untuk merombak hutan dan menjadikannya lahan pertanian padi, jagung, serta area berburu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bencana Danau Linow dan perpindahan penduduk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada masa-masa awal permukiman yang mulai meluas ke arah selatan, terjadi bencana alam besar. Air Danau Linow meluap hebat seperti air bah, merusak lahan pertanian yang siap panen dan menimbulkan korban jiwa.
+Akibat bencana tersebut, penduduk sepakat bermusyawarah untuk memindahkan permukiman ke arah timur, mendekati mata air tempat Pohon Lumahendong tumbuh pesat. Di lokasi baru inilah desa berkembang secara permanen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagian dari Walak Sarongsong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalam sejarah pemerintahan adat Minahasa, Lahendong dulunya merupakan bagian dari Walak atau Distrik Sarongsong. Karena wilayahnya yang berbatasan langsung dengan Leilem (Sonder) sering memicu ketegangan antarwalak, Kepala Walak Sarongsong bernama Tamboto sengaja menempatkan kerabatnya, Manopo (cucu Waworuntu I), sebagai Hukum Kedua (Kumarua) yang berkedudukan di Lahendong untuk menjaga stabilitas perbatasan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Era modern: pusat energi panas bumi (sejak 2001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memasuki abad ke-21, Lahendong mengukir sejarah baru sebagai tonggak pengembangan energi panas bumi di wilayah timur Indonesia. Sejak tahun 2001, Pertamina Geothermal Energy (PGE) mengoperasikan Pembangkit Listrik Tenaga Panas Bumi (PLTP) Lahendong secara komersial.
+Kekayaan belerang dan manifestasi termal yang dahulu ditemukan para leluhur kini dikelola menjadi sumber listrik utama yang memasok kebutuhan energi wilayah Sulawesi Utara dan Gorontalo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">nama</t>
   </si>
   <si>
@@ -2283,15 +2470,24 @@
     <t xml:space="preserve">nomor</t>
   </si>
   <si>
+    <t xml:space="preserve">081234567890</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sekretaris Kelurahan</t>
   </si>
   <si>
     <t xml:space="preserve">Cicilia M. Karamoy, S.ST, M.Kes</t>
   </si>
   <si>
+    <t xml:space="preserve">081234567891</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marthen J. Mende, ST</t>
   </si>
   <si>
+    <t xml:space="preserve">081234567892</t>
+  </si>
+  <si>
     <t xml:space="preserve">tampil</t>
   </si>
   <si>
@@ -2325,7 +2521,16 @@
     <t xml:space="preserve">Gawat darurat medis</t>
   </si>
   <si>
-    <t xml:space="preserve">2005</t>
+    <t xml:space="preserve">118 / 119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAR/BASARNAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencarian dan pertolongan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115</t>
   </si>
   <si>
     <t xml:space="preserve">ringkas</t>
@@ -2358,8 +2563,8 @@
     <t xml:space="preserve">Danau vulkanik dengan warna air yang dapat berubah — hijau, biru, hingga kekuningan.</t>
   </si>
   <si>
-    <t xml:space="preserve">Danau Linow Lahendong merupakan danau vulkanik yang berada di wilayah Lahendong, Kota Tomohon, Sulawesi Utara. Danau ini terbentuk dari aktivitas vulkanik dan memiliki kandungan belerang serta aktivitas panas bumi di kawasan sekitarnya. Lingkungan danau dikelilingi vegetasi hijau dan perbukitan, sehingga memiliki kondisi alam yang sejuk dan asri. Selain sebagai kawasan wisata, Danau Linow juga memiliki nilai ekologis dan geologis yang berkaitan dengan karakteristik kawasan vulkanik Lahendong.
-Keunikan utamanya adalah warna air yang dapat berubah-ubah, seperti hijau, biru, dan kekuningan. Keunikan warna air serta suasana alamnya yang asri dan sejuk menjadi daya tarik utama bagi wisatawan.</t>
+    <t xml:space="preserve">Danau Linow merupakan danau vulkanik di Kelurahan Lahendong, Kecamatan Tomohon Selatan, Kota Tomohon, Sulawesi Utara. Danau ini terbentuk dari aktivitas vulkanik dan mengandung belerang, dengan aktivitas panas bumi di kawasan sekitarnya. Lingkungan danau dikelilingi vegetasi hijau dan perbukitan, sehingga suasananya sejuk dan asri.
+Keunikan utamanya adalah warna air yang dapat berubah-ubah, seperti hijau, biru, dan kekuningan. Warna air serta suasana alamnya yang asri dan sejuk menjadi daya tarik utama bagi wisatawan.</t>
   </si>
   <si>
     <t xml:space="preserve">Setiap hari, 10.00 – 20.00 WITA
@@ -2375,55 +2580,47 @@
     <t xml:space="preserve">Pagi hari atau sore menjelang matahari terbenam, untuk melihat perubahan warna air danau</t>
   </si>
   <si>
-    <t xml:space="preserve">Dari pusat Kota Manado, menuju Pineleng melalui Jl. Sam Ratulangi atau Jl. Winangun, lalu masuk ke jalur utama Jl. Raya Manado – Tomohon.
-Ikuti jalan menanjak melewati Tinoor hingga memasuki Kota Tomohon, lalu tetap lurus melewati pusat kota dan kawasan Pasar Beriman Tomohon.
-Lanjutkan ke arah selatan menuju Kelurahan Lahendong melalui Jl. Kawangkoan – Tomohon.
-Setelah melewati area pemandian air panas Lahendong, ikuti papan petunjuk di sebelah kanan menuju Danau Linow Resort hingga tiba di gerbang utama.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT Karyadeka Alam Asri
-Direktur Utama: Pengky Wewengkang
-Direktur Operasional: James Pengky Wewengkang
-Manajer Resort: Andreas Dengen</t>
+    <t xml:space="preserve">Dari Manado: lewati Jalan Sam Ratulangi lalu Jalan Raya Manado – Tomohon hingga pusat Kota Tomohon (sekitar 26 km).
+Dari pusat Kota Tomohon (sekitar Menara Alfa Omega), ikuti Jalan Raya Tomohon ke arah selatan menuju Kelurahan Lahendong.
+Setelah melewati Objek Wisata Air Panas Belerang dan Hutan Pinus di sisi kanan jalan, lanjutkan sekitar 1,5 km, lalu belok kiri mengikuti papan petunjuk Danau Linow.
+Total jarak dari pusat Kota Tomohon sekitar 7–8 km.</t>
   </si>
   <si>
     <t xml:space="preserve">https://maps.google.com/?q=Danau+Linow+Tomohon</t>
   </si>
   <si>
-    <t xml:space="preserve">Hutan Pinus Lahendong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hutan pinus sejuk yang berpadu dengan kolam sulfur beruap dan pemandian air panas alami.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hutan Pinus Lahendong adalah destinasi wisata alam unik di Tomohon yang memadukan keindahan hutan pinus hijau nan rimbun dengan fenomena geotermal berupa kolam sulfur beruap putih dan pemandian air panas alami yang kaya khasiat bagi kulit. Perpaduan uap panas bumi yang mengepul di antara deretan pepohonan pinus yang menjulang tinggi menciptakan suasana yang sejuk dan menenangkan, menjadikannya tempat ideal untuk menyegarkan pikiran, berburu spot foto, serta bersantai menikmati kedamaian alam Tomohon jauh dari hiruk-pikuk perkotaan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.00 – 18.00 WITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rp35.000 per orang, umumnya sudah termasuk kuliner ringan (kopi, teh, pisang goreng, atau jagung rebus)
-Kolam air panas: sekitar Rp5.000 – Rp10.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Area parkir, toilet, warung dan rumah makan sederhana, spot foto, jalur penjelajahan ringan (hiking), bilik rendam air panas</t>
+    <t xml:space="preserve">Objek Wisata Air Panas Belerang dan Hutan Pinus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hutan pinus sejuk yang berpadu dengan kolam sulfur beruap putih.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objek Wisata Air Panas Belerang dan Hutan Pinus Lahendong adalah destinasi wisata alam di Tomohon yang memadukan hutan pinus hijau nan rimbun dengan fenomena panas bumi berupa kolam sulfur beruap putih dan pemandian air panas alami yang dipercaya berkhasiat bagi kulit.
+Uap panas bumi yang mengepul di antara deretan pohon pinus yang menjulang menciptakan suasana sejuk dan menenangkan, sehingga cocok untuk menyegarkan pikiran, berfoto, dan bersantai menikmati alam Tomohon jauh dari hiruk-pikuk perkotaan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setiap hari, 10.00 – 18.00 WITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rp25.000 per orang, sudah termasuk kopi
+Kolam air panas: Rp15.000 per orang
+Bilik rendam air panas: Rp50.000 per ruangan (muat 3 orang)
+Kolam dan bilik air panas sementara belum beroperasi karena air berkurang di musim kemarau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area parkir, toilet, spot foto, jalur penjelajahan ringan (hiking), kolam dan bilik rendam air panas (sementara belum beroperasi)</t>
   </si>
   <si>
     <t xml:space="preserve">Pagi hari (09.00 – 11.00 WITA): uap dari kolam sulfur mengepul tebal berpadu udara pagi yang masih dingin; cocok untuk berjalan santai tanpa terik matahari.
-Sore hari (15.00 – 17.00 WITA): cahaya matahari melembut (golden hour) untuk berfoto, lalu ditutup dengan berendam air panas belerang menjelang malam.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berjarak sekitar 5,3 km dari pusat Kota Tomohon, kurang lebih 13–15 menit perjalanan.
-Dari pusat kota (sekitar Menara Alfa Omega atau Pasar Beriman), arahkan kendaraan ke selatan menuju jalur utama arah Kawangkoan/Sonder melalui Jalan Raya Tomohon.
-Lewati wilayah Walian. Setelah memasuki Kelurahan Lahendong, berbelok ke kanan masuk ke Jalan Lahendong; gerbang masuk mudah terlihat dari tepi jalan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pengelolaan bersama antara Pemerintah Kota Tomohon dan pihak swasta/masyarakat lokal.
-Dinas Pariwisata Kota Tomohon: regulasi kepariwisataan, promosi daerah, pemantauan dampak lingkungan kawasan resapan air, dan koordinasi investasi ekowisata.
-Pengelola lokal: operasional harian, pemeliharaan fasilitas (kafe, pemandian air panas, spot foto), dan penyediaan lapangan kerja bagi warga Lahendong.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://maps.google.com/?q=Hutan+Pinus+Lahendong</t>
+Sore hari (15.00 – 17.00 WITA): cahaya matahari melembut (golden hour) untuk berfoto, dan suasana hutan pinus lebih teduh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berjarak sekitar 5,3 km dari pusat Kota Tomohon, kurang lebih 10–15 menit perjalanan.
+Dari pusat Kota Tomohon (sekitar Menara Alfa Omega), ikuti Jalan Raya Tomohon ke arah selatan menuju Kelurahan Lahendong.
+Setelah memasuki Kelurahan Lahendong, gerbang masuk berada di sisi kanan jalan dan mudah terlihat; perhatikan papan petunjuknya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maps.google.com/?q=Pemandian+Air+Panas+Belerang+Pinus+Lahendong</t>
   </si>
   <si>
     <t xml:space="preserve">Mah’Watu</t>
@@ -2432,7 +2629,8 @@
     <t xml:space="preserve">Wisata alam asri dengan kafe terbuka, gazebo, dan aliran air belerang berwarna hijau toska.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mah’Watu merupakan salah satu destinasi wisata alam yang berada di Kota Tomohon, Sulawesi Utara. Tempat wisata ini menawarkan suasana yang asri dan sejuk dengan pemandangan alam yang indah, sehingga cocok dijadikan tempat untuk bersantai dan melepas penat. Keindahan lingkungan sekitar yang masih alami menjadi daya tarik tersendiri bagi pengunjung. Selain menikmati pemandangan, wisatawan juga dapat menghabiskan waktu bersama keluarga maupun teman sambil menikmati suasana yang tenang dan udara yang segar.</t>
+    <t xml:space="preserve">Mah’Watu merupakan destinasi wisata alam di Kelurahan Lahendong, Kecamatan Tomohon Selatan, Kota Tomohon. Tempat wisata ini menawarkan suasana asri dan sejuk dengan aliran air belerang berwarna hijau toska di antara tebing batu dan pepohonan, sehingga cocok untuk bersantai dan melepas penat.
+Selain menikmati pemandangan, pengunjung dapat menghabiskan waktu bersama keluarga maupun teman di kafe terbuka dan gazebo sambil menikmati suasana yang tenang dan udara yang segar.</t>
   </si>
   <si>
     <t xml:space="preserve">Senin – Sabtu, 10.00 – 18.00 WITA
@@ -2470,85 +2668,38 @@
     <t xml:space="preserve">catatan</t>
   </si>
   <si>
-    <t xml:space="preserve">Surat Keterangan Domisili</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kependudukan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotokopi KTP
-Fotokopi Kartu Keluarga
-Surat pengantar RT/lingkungan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
-Petugas memeriksa berkas
-Surat ditandatangani lurah
-Surat diambil pemohon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotokopi KTP
-Fotokopi Kartu Keluarga
-Surat pengantar RT/lingkungan
-Keterangan penghasilan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
-Petugas memeriksa berkas dan, bila perlu, melakukan survei singkat
-Surat ditandatangani lurah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1–2 hari kerja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebutkan keperluan SKTM (sekolah, kesehatan, atau bantuan sosial) saat mengajukan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surat Pengantar Nikah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotokopi KTP kedua calon mempelai
-Fotokopi Kartu Keluarga
-Surat pengantar RT/lingkungan
-Pas foto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
-Petugas memeriksa data
-Surat diteruskan ke KUA atau Dinas Kependudukan</t>
+    <t xml:space="preserve">Kartu Keluarga (KK)
+Kartu Tanda Penduduk (KTP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bawa berkas persyaratan ke kantor kelurahan
+Surat diproses dan dapat ditunggu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dapat ditunggu; lama pengerjaan menyesuaikan jenis surat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surat Keterangan Orang yang Sama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Untuk data yang berbeda di dokumen kependudukan, mis. nama di Kartu Keluarga berbeda dengan di KTP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surat Keterangan Kehilangan</t>
   </si>
   <si>
     <t xml:space="preserve">Surat Keterangan Usaha</t>
   </si>
   <si>
-    <t xml:space="preserve">Usaha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotokopi KTP
-Fotokopi Kartu Keluarga
-Foto lokasi usaha
-Surat pengantar RT/lingkungan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
-Petugas memeriksa lokasi usaha
-Surat ditandatangani lurah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1–3 hari kerja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surat Keterangan Kelahiran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotokopi KTP kedua orang tua
-Fotokopi Kartu Keluarga
-Surat keterangan lahir dari bidan atau rumah sakit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bawa berkas ke kantor kelurahan
-Petugas memeriksa berkas
-Surat ditandatangani lurah</t>
+    <t xml:space="preserve">Kartu Keluarga (KK)
+Kartu Tanda Penduduk (KTP)
+Bukti lunas pajak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surat Keterangan Berkelakuan Baik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surat Keterangan Belum Pernah Kawin</t>
   </si>
 </sst>
 </file>
@@ -2866,7 +3017,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.6"/>
@@ -3019,7 +3170,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -3031,106 +3182,106 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="A39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="4" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3146,24 +3297,24 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="4" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3179,13 +3330,13 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="4" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3200,7 +3351,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
         <v>75</v>
       </c>
@@ -3234,13 +3385,13 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="2" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3255,7 +3406,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>90</v>
       </c>
@@ -3267,28 +3418,28 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>99</v>
       </c>
@@ -3311,13 +3462,13 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="4" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3332,14 +3483,14 @@
         <v>110</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3348,43 +3499,43 @@
         <v>114</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B64" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C64" s="2" t="s">
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
         <v>120</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3454,13 +3605,13 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="2" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3469,43 +3620,43 @@
         <v>145</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C75" s="2" t="s">
+      <c r="A75" s="4" t="s">
         <v>151</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3542,177 +3693,224 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
+      <c r="A80" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="s">
-        <v>164</v>
+      <c r="A81" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B82" s="3" t="s">
+      <c r="A82" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2"/>
-    </row>
-    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>200</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2"/>
+      <c r="A101" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -3731,7 +3929,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C118"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.98"/>
@@ -3740,179 +3938,201 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="C3" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -4398,6 +4618,21 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4416,1246 +4651,468 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="56.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="67.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>62</v>
+        <v>253</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G5" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="H5" s="2" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>273</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>274</v>
-      </c>
+      <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>278</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>285</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5674,669 +5131,1248 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>288</v>
+        <v>264</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>308</v>
+      </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="6"/>
+      <c r="C10" s="2"/>
       <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="6"/>
+      <c r="C11" s="2"/>
       <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="6"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="6"/>
+      <c r="C13" s="2"/>
       <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="6"/>
+      <c r="C14" s="2"/>
       <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="6"/>
+      <c r="C15" s="2"/>
       <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="6"/>
+      <c r="C16" s="2"/>
       <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="6"/>
+      <c r="C17" s="2"/>
       <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="6"/>
+      <c r="C18" s="2"/>
       <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="6"/>
+      <c r="C19" s="2"/>
       <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="6"/>
+      <c r="C20" s="2"/>
       <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="6"/>
+      <c r="C21" s="2"/>
       <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="6"/>
+      <c r="C22" s="2"/>
       <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="6"/>
+      <c r="C23" s="2"/>
       <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="6"/>
+      <c r="C24" s="2"/>
       <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="6"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="6"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="6"/>
+      <c r="C27" s="2"/>
       <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="6"/>
+      <c r="C28" s="2"/>
       <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="6"/>
+      <c r="C29" s="2"/>
       <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="6"/>
+      <c r="C30" s="2"/>
       <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="6"/>
+      <c r="C31" s="2"/>
       <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="6"/>
+      <c r="C32" s="2"/>
       <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="6"/>
+      <c r="C33" s="2"/>
       <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="6"/>
+      <c r="C34" s="2"/>
       <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="6"/>
+      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="6"/>
+      <c r="C36" s="2"/>
       <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="6"/>
+      <c r="C37" s="2"/>
       <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="6"/>
+      <c r="C38" s="2"/>
       <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="6"/>
+      <c r="C39" s="2"/>
       <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="6"/>
+      <c r="C40" s="2"/>
       <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="6"/>
+      <c r="C41" s="2"/>
       <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="6"/>
+      <c r="C42" s="2"/>
       <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="6"/>
+      <c r="C43" s="2"/>
       <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="6"/>
+      <c r="C44" s="2"/>
       <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="6"/>
+      <c r="C45" s="2"/>
       <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="6"/>
+      <c r="C46" s="2"/>
       <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="6"/>
+      <c r="C47" s="2"/>
       <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="6"/>
+      <c r="C48" s="2"/>
       <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="6"/>
+      <c r="C49" s="2"/>
       <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="6"/>
+      <c r="C50" s="2"/>
       <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="6"/>
+      <c r="C51" s="2"/>
       <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
-      <c r="C52" s="6"/>
+      <c r="C52" s="2"/>
       <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="6"/>
+      <c r="C53" s="2"/>
       <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="6"/>
+      <c r="C54" s="2"/>
       <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="6"/>
+      <c r="C55" s="2"/>
       <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="6"/>
+      <c r="C56" s="2"/>
       <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="6"/>
+      <c r="C57" s="2"/>
       <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="6"/>
+      <c r="C58" s="2"/>
       <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="6"/>
+      <c r="C59" s="2"/>
       <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
-      <c r="C60" s="6"/>
+      <c r="C60" s="2"/>
       <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
-      <c r="C61" s="6"/>
+      <c r="C61" s="2"/>
       <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
-      <c r="C62" s="6"/>
+      <c r="C62" s="2"/>
       <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="6"/>
+      <c r="C63" s="2"/>
       <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
-      <c r="C64" s="6"/>
+      <c r="C64" s="2"/>
       <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
-      <c r="C65" s="6"/>
+      <c r="C65" s="2"/>
       <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
-      <c r="C66" s="6"/>
+      <c r="C66" s="2"/>
       <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="6"/>
+      <c r="C67" s="2"/>
       <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
-      <c r="C68" s="6"/>
+      <c r="C68" s="2"/>
       <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
-      <c r="C69" s="6"/>
+      <c r="C69" s="2"/>
       <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="6"/>
+      <c r="C70" s="2"/>
       <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="6"/>
+      <c r="C71" s="2"/>
       <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="6"/>
+      <c r="C72" s="2"/>
       <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
-      <c r="C73" s="6"/>
+      <c r="C73" s="2"/>
       <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
-      <c r="C74" s="6"/>
+      <c r="C74" s="2"/>
       <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
-      <c r="C75" s="6"/>
+      <c r="C75" s="2"/>
       <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
-      <c r="C76" s="6"/>
+      <c r="C76" s="2"/>
       <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
-      <c r="C77" s="6"/>
+      <c r="C77" s="2"/>
       <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
-      <c r="C78" s="6"/>
+      <c r="C78" s="2"/>
       <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
-      <c r="C79" s="6"/>
+      <c r="C79" s="2"/>
       <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
-      <c r="C80" s="6"/>
+      <c r="C80" s="2"/>
       <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
-      <c r="C81" s="6"/>
+      <c r="C81" s="2"/>
       <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="6"/>
+      <c r="C82" s="2"/>
       <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
-      <c r="C83" s="6"/>
+      <c r="C83" s="2"/>
       <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
-      <c r="C84" s="6"/>
+      <c r="C84" s="2"/>
       <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
-      <c r="C85" s="6"/>
+      <c r="C85" s="2"/>
       <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="6"/>
+      <c r="C86" s="2"/>
       <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
-      <c r="C87" s="6"/>
+      <c r="C87" s="2"/>
       <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="6"/>
+      <c r="C88" s="2"/>
       <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
-      <c r="C89" s="6"/>
+      <c r="C89" s="2"/>
       <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
-      <c r="C90" s="6"/>
+      <c r="C90" s="2"/>
       <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
-      <c r="C91" s="6"/>
+      <c r="C91" s="2"/>
       <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
-      <c r="C92" s="6"/>
+      <c r="C92" s="2"/>
       <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="6"/>
+      <c r="C93" s="2"/>
       <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
-      <c r="C94" s="6"/>
+      <c r="C94" s="2"/>
       <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="6"/>
+      <c r="C95" s="2"/>
       <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="6"/>
+      <c r="C96" s="2"/>
       <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="6"/>
+      <c r="C97" s="2"/>
       <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
-      <c r="C98" s="6"/>
+      <c r="C98" s="2"/>
       <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
-      <c r="C99" s="6"/>
+      <c r="C99" s="2"/>
       <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
-      <c r="C100" s="6"/>
+      <c r="C100" s="2"/>
       <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
-      <c r="C101" s="6"/>
+      <c r="C101" s="2"/>
       <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
-      <c r="C102" s="6"/>
+      <c r="C102" s="2"/>
       <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
-      <c r="C103" s="6"/>
+      <c r="C103" s="2"/>
       <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
-      <c r="C104" s="6"/>
+      <c r="C104" s="2"/>
       <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C104" type="list">
-      <formula1>aparat!$A$2:$A$500</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6353,791 +6389,673 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.73"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>227</v>
+        <v>320</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>296</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C2" s="6"/>
       <c r="D2" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>301</v>
+        <v>95</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="C6" s="6"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="C10" s="6"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="C12" s="6"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="C14" s="6"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="C16" s="6"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="6"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="C20" s="6"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="C21" s="6"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="C22" s="6"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="C23" s="6"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="C24" s="6"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="C25" s="6"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="C26" s="6"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="C27" s="6"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="C28" s="6"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="C29" s="6"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+      <c r="C30" s="6"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
+      <c r="C31" s="6"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="C32" s="6"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="C33" s="6"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+      <c r="C34" s="6"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+      <c r="C35" s="6"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
+      <c r="C36" s="6"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="C37" s="6"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
+      <c r="C38" s="6"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
+      <c r="C39" s="6"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
+      <c r="C40" s="6"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
+      <c r="C41" s="6"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
+      <c r="C42" s="6"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="C43" s="6"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="C44" s="6"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
+      <c r="C45" s="6"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
+      <c r="C46" s="6"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
+      <c r="C47" s="6"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
+      <c r="C48" s="6"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
+      <c r="C49" s="6"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
+      <c r="C50" s="6"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="C51" s="6"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
+      <c r="C52" s="6"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
+      <c r="C53" s="6"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
+      <c r="C54" s="6"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
+      <c r="C55" s="6"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
+      <c r="C56" s="6"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
+      <c r="C57" s="6"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
+      <c r="C58" s="6"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
+      <c r="C59" s="6"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
+      <c r="C60" s="6"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
+      <c r="C61" s="6"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
+      <c r="C62" s="6"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
+      <c r="C63" s="6"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
+      <c r="C64" s="6"/>
       <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="C65" s="6"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
+      <c r="C66" s="6"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
+      <c r="C67" s="6"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
+      <c r="C68" s="6"/>
       <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
+      <c r="C69" s="6"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
+      <c r="C70" s="6"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
+      <c r="C71" s="6"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
+      <c r="C72" s="6"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
+      <c r="C73" s="6"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
+      <c r="C74" s="6"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
+      <c r="C75" s="6"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
+      <c r="C76" s="6"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
+      <c r="C77" s="6"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
+      <c r="C78" s="6"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
+      <c r="C79" s="6"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
+      <c r="C80" s="6"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
+      <c r="C81" s="6"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
+      <c r="C82" s="6"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
+      <c r="C83" s="6"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
+      <c r="C84" s="6"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
+      <c r="C85" s="6"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
+      <c r="C86" s="6"/>
       <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
+      <c r="C87" s="6"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
+      <c r="C88" s="6"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
+      <c r="C89" s="6"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
+      <c r="C90" s="6"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
+      <c r="C91" s="6"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
+      <c r="C92" s="6"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
+      <c r="C93" s="6"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
+      <c r="C94" s="6"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
+      <c r="C95" s="6"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
+      <c r="C96" s="6"/>
       <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="C97" s="6"/>
       <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
+      <c r="C98" s="6"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
+      <c r="C99" s="6"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
+      <c r="C100" s="6"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
+      <c r="C101" s="6"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
+      <c r="C102" s="6"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
+      <c r="C103" s="6"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
+      <c r="C104" s="6"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B104" type="list">
-      <formula1>"Ya,Tidak"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E104" type="list">
-      <formula1>"darurat,umum"</formula1>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C104" type="list">
+      <formula1>aparat!$A$2:$A$500</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -7157,165 +7075,99 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="67.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="53.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="67.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="56.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>332</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>339</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
@@ -7323,12 +7175,6 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
@@ -7336,12 +7182,6 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -7349,12 +7189,6 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
@@ -7362,12 +7196,6 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
@@ -7375,12 +7203,6 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -7388,12 +7210,6 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
@@ -7401,12 +7217,6 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
@@ -7414,12 +7224,6 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -7427,12 +7231,6 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
@@ -7440,12 +7238,6 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
@@ -7453,12 +7245,6 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -7466,12 +7252,6 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -7479,12 +7259,6 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -7492,12 +7266,6 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -7505,12 +7273,6 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
@@ -7518,12 +7280,6 @@
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
@@ -7531,12 +7287,6 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -7544,12 +7294,6 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -7557,12 +7301,6 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -7570,12 +7308,6 @@
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -7583,12 +7315,6 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
@@ -7596,12 +7322,6 @@
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
@@ -7609,12 +7329,6 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
@@ -7622,12 +7336,6 @@
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
@@ -7635,12 +7343,6 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -7648,12 +7350,6 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -7661,12 +7357,6 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
@@ -7674,12 +7364,6 @@
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
@@ -7687,12 +7371,6 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -7700,12 +7378,6 @@
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -7713,12 +7385,6 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
@@ -7726,12 +7392,6 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -7739,12 +7399,6 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
@@ -7752,12 +7406,6 @@
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
@@ -7765,12 +7413,6 @@
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
@@ -7778,12 +7420,6 @@
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
@@ -7791,12 +7427,6 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
@@ -7804,12 +7434,6 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
@@ -7817,12 +7441,6 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
@@ -7830,12 +7448,6 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
@@ -7843,12 +7455,6 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
@@ -7856,12 +7462,6 @@
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
@@ -7869,12 +7469,6 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
@@ -7882,12 +7476,6 @@
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -7895,12 +7483,6 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -7908,12 +7490,6 @@
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -7921,12 +7497,6 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -7934,12 +7504,6 @@
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -7947,12 +7511,6 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -7960,12 +7518,6 @@
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -7973,12 +7525,6 @@
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -7986,12 +7532,6 @@
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -7999,12 +7539,6 @@
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -8012,12 +7546,6 @@
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -8025,12 +7553,6 @@
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -8038,12 +7560,6 @@
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -8051,12 +7567,6 @@
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -8064,12 +7574,6 @@
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -8077,12 +7581,6 @@
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -8090,12 +7588,6 @@
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
@@ -8103,12 +7595,6 @@
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
@@ -8116,12 +7602,6 @@
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
@@ -8129,12 +7609,6 @@
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
@@ -8142,12 +7616,6 @@
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
@@ -8155,12 +7623,6 @@
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
@@ -8168,12 +7630,6 @@
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
@@ -8181,12 +7637,6 @@
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
@@ -8194,12 +7644,6 @@
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
@@ -8207,12 +7651,6 @@
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
@@ -8220,12 +7658,6 @@
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
@@ -8233,12 +7665,6 @@
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
@@ -8246,12 +7672,6 @@
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
@@ -8259,12 +7679,6 @@
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
@@ -8272,12 +7686,6 @@
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
@@ -8285,12 +7693,6 @@
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
@@ -8298,12 +7700,6 @@
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
@@ -8311,12 +7707,6 @@
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
@@ -8324,12 +7714,6 @@
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
@@ -8337,12 +7721,6 @@
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
@@ -8350,12 +7728,6 @@
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
@@ -8363,12 +7735,6 @@
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
@@ -8376,12 +7742,6 @@
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
@@ -8389,12 +7749,6 @@
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
@@ -8402,12 +7756,6 @@
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
@@ -8415,12 +7763,6 @@
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
@@ -8428,12 +7770,6 @@
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
@@ -8441,12 +7777,6 @@
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
@@ -8454,12 +7784,6 @@
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
@@ -8467,12 +7791,6 @@
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
@@ -8480,12 +7798,6 @@
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
@@ -8493,12 +7805,6 @@
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
@@ -8506,12 +7812,6 @@
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
@@ -8519,12 +7819,6 @@
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
@@ -8532,12 +7826,6 @@
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
@@ -8545,12 +7833,6 @@
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
@@ -8558,12 +7840,6 @@
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
@@ -8571,12 +7847,6 @@
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
@@ -8584,12 +7854,6 @@
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
@@ -8597,21 +7861,22 @@
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A104" type="list">
-      <formula1>"Danau Linow,Hutan Pinus Lahendong,Mah’Watu"</formula1>
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B105" type="list">
+      <formula1>"Ya,Tidak"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B104" type="list">
-      <formula1>"Ya,Tidak"</formula1>
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E2:E105" type="list">
+      <formula1>"darurat,umum"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -8631,166 +7896,175 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="67.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="53.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="67.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="67.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>340</v>
+        <v>261</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>294</v>
+        <v>344</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>349</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>346</v>
+        <v>122</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>157</v>
+        <v>356</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>357</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>144</v>
+        <v>361</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>148</v>
+        <v>362</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>160</v>
+        <v>366</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>367</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>157</v>
+        <v>374</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>160</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>160</v>
-      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
       <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
@@ -8801,6 +8075,9 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
@@ -8811,6 +8088,9 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
@@ -8821,6 +8101,9 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
@@ -8831,6 +8114,9 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
@@ -8841,6 +8127,9 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
@@ -8851,6 +8140,9 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
@@ -8861,6 +8153,9 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
@@ -8871,6 +8166,9 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
@@ -8881,6 +8179,9 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
@@ -8891,6 +8192,9 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
@@ -8901,6 +8205,9 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
@@ -8911,6 +8218,9 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
@@ -8921,6 +8231,9 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
@@ -8931,6 +8244,9 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
@@ -8941,6 +8257,9 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
@@ -8951,6 +8270,9 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
@@ -8961,6 +8283,9 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
@@ -8971,6 +8296,9 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
@@ -8981,6 +8309,9 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
@@ -8991,6 +8322,9 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
@@ -9001,6 +8335,9 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
@@ -9011,6 +8348,9 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
@@ -9021,6 +8361,9 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
@@ -9031,6 +8374,9 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -9041,6 +8387,9 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -9051,6 +8400,9 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
@@ -9061,6 +8413,9 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
@@ -9071,6 +8426,9 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -9081,6 +8439,9 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -9091,6 +8452,9 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
@@ -9101,6 +8465,9 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
@@ -9111,6 +8478,9 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
@@ -9121,6 +8491,9 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
@@ -9131,6 +8504,9 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
@@ -9141,6 +8517,9 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
@@ -9151,6 +8530,9 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
@@ -9161,6 +8543,9 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
@@ -9171,6 +8556,9 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
@@ -9181,6 +8569,9 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2"/>
@@ -9191,6 +8582,9 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2"/>
@@ -9201,6 +8595,9 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
@@ -9211,6 +8608,9 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
@@ -9221,6 +8621,9 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -9231,6 +8634,9 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -9241,6 +8647,9 @@
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -9251,6 +8660,9 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -9261,6 +8673,9 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -9271,6 +8686,9 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -9281,6 +8699,9 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -9291,6 +8712,9 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -9301,6 +8725,9 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -9311,6 +8738,9 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -9321,6 +8751,9 @@
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -9331,6 +8764,9 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -9341,6 +8777,9 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -9351,6 +8790,9 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -9361,6 +8803,9 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -9371,6 +8816,9 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -9381,6 +8829,9 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
@@ -9391,6 +8842,9 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
@@ -9401,6 +8855,9 @@
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
@@ -9411,6 +8868,9 @@
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
@@ -9421,6 +8881,9 @@
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
@@ -9431,6 +8894,9 @@
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
@@ -9441,6 +8907,9 @@
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
@@ -9451,6 +8920,9 @@
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
@@ -9461,6 +8933,9 @@
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
@@ -9471,6 +8946,9 @@
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
@@ -9481,6 +8959,9 @@
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
@@ -9491,6 +8972,9 @@
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
@@ -9501,6 +8985,9 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
@@ -9511,6 +8998,9 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
@@ -9521,6 +9011,9 @@
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
@@ -9531,6 +9024,9 @@
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
@@ -9541,6 +9037,9 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
@@ -9551,6 +9050,9 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
@@ -9561,6 +9063,9 @@
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
@@ -9571,6 +9076,9 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
@@ -9581,6 +9089,9 @@
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
@@ -9591,6 +9102,9 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
@@ -9601,6 +9115,9 @@
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
@@ -9611,6 +9128,9 @@
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
@@ -9621,6 +9141,9 @@
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
@@ -9631,6 +9154,9 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
@@ -9641,6 +9167,9 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
@@ -9651,6 +9180,9 @@
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
@@ -9661,6 +9193,9 @@
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
@@ -9671,6 +9206,9 @@
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
@@ -9681,6 +9219,9 @@
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
@@ -9691,6 +9232,9 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
@@ -9701,6 +9245,9 @@
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
@@ -9711,6 +9258,9 @@
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
@@ -9721,6 +9271,9 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
@@ -9731,6 +9284,9 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
@@ -9741,6 +9297,9 @@
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
@@ -9751,6 +9310,9 @@
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
@@ -9761,6 +9323,9 @@
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
@@ -9771,11 +9336,1183 @@
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A104" type="list">
+      <formula1>"Danau Linow,Objek Wisata Air Panas Belerang dan Hutan Pinus,Mah’Watu"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B104" type="list">
+      <formula1>"Ya,Tidak"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H107"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="31.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="50.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="65.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="67.41"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
+      <c r="C105" s="6"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
@@ -9785,21 +10522,31 @@
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
+      <c r="C106" s="6"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B106" type="list">
+    <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B107" type="list">
       <formula1>"Ya,Tidak"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Nilai ini belum ada di daftar. Tetap dipakai bila memang kategori baru." errorStyle="warning" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C106" type="list">
-      <formula1>"Kependudukan,Sosial,Usaha"</formula1>
+    <dataValidation allowBlank="true" error="Nilai ini belum ada di daftar. Tetap dipakai bila memang kategori baru." errorStyle="warning" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C107" type="list">
+      <formula1>"Kependudukan"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">• Judul dan kalimat pengantar tiap halaman, serta ilustrasi bawaan: di berkas situs (HTML &amp; folder img/).</t>
   </si>
   <si>
-    <t xml:space="preserve">• Peta wilayah (gambar): file img/peta-wilayah.png — halaman Profil menampilkannya otomatis bila file ada.</t>
+    <t xml:space="preserve">• Peta wilayah (gambar): file img/umum/peta-wilayah.png — halaman Profil menampilkannya otomatis bila file ada.</t>
   </si>
   <si>
     <t xml:space="preserve">DATA YANG MASIH CONTOH</t>

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -2589,7 +2589,7 @@
     <t xml:space="preserve">https://maps.google.com/?q=Danau+Linow+Tomohon</t>
   </si>
   <si>
-    <t xml:space="preserve">Objek Wisata Air Panas Belerang dan Hutan Pinus</t>
+    <t xml:space="preserve">Air Panas Belerang dan Hutan Pinus</t>
   </si>
   <si>
     <t xml:space="preserve">Hutan pinus sejuk yang berpadu dengan kolam sulfur beruap putih.</t>
@@ -7899,7 +7899,7 @@
   <dimension ref="A1:K104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="67.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="53.93"/>
@@ -9343,7 +9343,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A104" type="list">
-      <formula1>"Danau Linow,Objek Wisata Air Panas Belerang dan Hutan Pinus,Mah’Watu"</formula1>
+      <formula1>"Danau Linow,Air Panas Belerang dan Hutan Pinus,Mah’Watu"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pilih salah satu dari daftar." errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B104" type="list">

--- a/data/template-data-lahendong.xlsx
+++ b/data/template-data-lahendong.xlsx
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">• Angka total (jumlah penduduk, KK, jiwa per lingkungan) tidak perlu ditulis — situs menghitungnya dari tab lingkungan.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Setelah mengubah data, buka halaman Cek Data: https://vercoooo.github.io/web-lahendong/cek-data.html — setiap isian yang keliru ditunjukkan beserta cara memperbaikinya.</t>
+    <t xml:space="preserve">• Setelah mengubah data, buka halaman Cek Data: https://kelurahan-lahendong.github.io/cek-data.html — setiap isian yang keliru ditunjukkan beserta cara memperbaikinya.</t>
   </si>
   <si>
     <t xml:space="preserve">FOTO &amp; DESTINASI WISATA</t>
@@ -3073,7 +3073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
